--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -823,7 +823,7 @@
         <v>109.18</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>18.87</v>
@@ -1279,7 +1279,7 @@
         <v>18.16</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.79</v>
@@ -1659,7 +1659,7 @@
         <v>18.85</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>7.13</v>
@@ -2875,7 +2875,7 @@
         <v>17.48</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>5.36</v>
@@ -3027,7 +3027,7 @@
         <v>13.05</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>6.04</v>
@@ -3331,7 +3331,7 @@
         <v>14.48</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.56</v>
@@ -3407,7 +3407,7 @@
         <v>104.79</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>15.65</v>
@@ -3747,7 +3747,7 @@
         <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="3">
@@ -3809,7 +3809,7 @@
         <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5">
@@ -4677,7 +4677,7 @@
         <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
@@ -4708,7 +4708,7 @@
         <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
@@ -4739,7 +4739,7 @@
         <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35">
@@ -4832,7 +4832,7 @@
         <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="38">
@@ -4863,7 +4863,7 @@
         <v>3.75</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="39">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1279,7 +1279,7 @@
         <v>18.16</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.79</v>
@@ -1355,7 +1355,7 @@
         <v>86.59</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>19.61</v>
@@ -1431,7 +1431,7 @@
         <v>89.23999999999999</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>16.5</v>
@@ -1659,7 +1659,7 @@
         <v>18.85</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>7.13</v>
@@ -2875,7 +2875,7 @@
         <v>17.48</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>5.36</v>
@@ -3027,7 +3027,7 @@
         <v>13.05</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>6.04</v>
@@ -3331,7 +3331,7 @@
         <v>14.48</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.56</v>
@@ -3840,7 +3840,7 @@
         <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="6">
@@ -3902,7 +3902,7 @@
         <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="8">
@@ -4677,7 +4677,7 @@
         <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="33">
@@ -4708,7 +4708,7 @@
         <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="34">
@@ -4739,7 +4739,7 @@
         <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35">
@@ -4832,7 +4832,7 @@
         <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="38">
@@ -4863,7 +4863,7 @@
         <v>3.75</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="39">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -737,26 +737,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>1367</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.45</v>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -813,26 +827,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>68.08</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>109.18</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>109.18</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1655</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>27.16</v>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -889,26 +917,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>88.79000000000001</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>108.35</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>108.35</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>1654</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>64.63</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>23.17</v>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -965,26 +1007,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1545</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>35.17</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>13.54</v>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1041,26 +1097,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>1453</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>6.05</v>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1117,26 +1187,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>1608</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>22.01</v>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1193,26 +1277,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>50.66</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>1547</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>17.9</v>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1269,26 +1367,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1434</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>1.6</v>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3721,1242 +3833,1354 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>109.18</v>
+        <v>104.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>109.18</v>
+        <v>104.79</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18.87</v>
+        <v>15.65</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.16</v>
+        <v>63.81</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>27.16</v>
+        <v>25.33</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1655</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2075</v>
+        <v>5166</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108.35</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>108.35</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>20.55</v>
+        <v>16.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>64.63</v>
+        <v>51.01</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>23.17</v>
+        <v>21.73</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1654</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>7220</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.8</v>
+        <v>45.04</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>104.79</v>
+        <v>89.02</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>104.79</v>
+        <v>89.02</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.65</v>
+        <v>20.24</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.81</v>
+        <v>54.64</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.33</v>
+        <v>14.14</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1648</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16.5</v>
+        <v>19.61</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>51.01</v>
+        <v>45.87</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.73</v>
+        <v>21.1</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1619</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>7656</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45.04</v>
+        <v>50.91</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89.02</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>89.02</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.24</v>
+        <v>10.28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.64</v>
+        <v>47.29</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.14</v>
+        <v>23.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1619</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>9208</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>44.43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>86.59</v>
+        <v>60.89</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>86.59</v>
+        <v>60.89</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.61</v>
+        <v>15.07</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45.87</v>
+        <v>34.36</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>21.1</v>
+        <v>11.46</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1613</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>6081</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>59.73</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.16</v>
+        <v>58.86</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.16</v>
+        <v>58.86</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>18.91</v>
+        <v>13.66</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.23</v>
+        <v>25.05</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.01</v>
+        <v>20.14</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1608</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>55.1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>51.63</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>51.63</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.28</v>
+        <v>6.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.29</v>
+        <v>27.33</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.14</v>
+        <v>17.84</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9208</v>
+        <v>8423</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>44.43</v>
+        <v>28.04</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>60.89</v>
+        <v>39.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60.89</v>
+        <v>39.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15.07</v>
+        <v>10.47</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>34.36</v>
+        <v>18.9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11.46</v>
+        <v>10.4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1555</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6081</v>
+        <v>9685</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>59.73</v>
+        <v>27.75</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>58.86</v>
+        <v>39.35</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>58.86</v>
+        <v>39.35</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.66</v>
+        <v>14.16</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>25.05</v>
+        <v>8.48</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20.14</v>
+        <v>16.71</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1550</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>9756</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50.66</v>
+        <v>29.21</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>57.35</v>
+        <v>38.47</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.35</v>
+        <v>38.47</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.65</v>
+        <v>3.62</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.81</v>
+        <v>21.23</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.9</v>
+        <v>13.63</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1547</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2771</v>
+        <v>7808</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>53.52</v>
+        <v>24.37</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>56.69</v>
+        <v>34.73</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>56.69</v>
+        <v>34.73</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7.98</v>
+        <v>6.55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>35.17</v>
+        <v>18.66</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.54</v>
+        <v>9.52</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1545</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>858</v>
+        <v>9671</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>55.1</v>
+        <v>27.39</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>51.63</v>
+        <v>34.06</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.63</v>
+        <v>34.06</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.46</v>
+        <v>11.03</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27.33</v>
+        <v>18.98</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.84</v>
+        <v>4.06</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1533</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>5501</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>31.87</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.47</v>
+        <v>6.95</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.9</v>
+        <v>17.02</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.4</v>
+        <v>7.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1504</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>23.83</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.35</v>
+        <v>31.74</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.35</v>
+        <v>31.74</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>14.16</v>
+        <v>2.91</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.48</v>
+        <v>14.95</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.71</v>
+        <v>13.87</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1503</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>8767</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.21</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>38.47</v>
+        <v>31.51</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>38.47</v>
+        <v>31.51</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3.62</v>
+        <v>4.86</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.23</v>
+        <v>17.87</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.63</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1501</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>7289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.37</v>
+        <v>33.29</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.73</v>
+        <v>28.94</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.73</v>
+        <v>28.94</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.55</v>
+        <v>11.23</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.66</v>
+        <v>7.04</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.52</v>
+        <v>10.67</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1490</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.06</v>
+        <v>27.77</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.06</v>
+        <v>27.77</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>5.14</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.98</v>
+        <v>10.09</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4.06</v>
+        <v>12.54</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1489</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5501</v>
+        <v>9566</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>31.87</v>
+        <v>39.97</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.87</v>
+        <v>26.12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.87</v>
+        <v>26.12</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.95</v>
+        <v>3.19</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.02</v>
+        <v>14.75</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1482</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>39.07</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.74</v>
+        <v>24.48</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.74</v>
+        <v>24.48</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.91</v>
+        <v>5.09</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.95</v>
+        <v>11.62</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13.87</v>
+        <v>7.77</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1482</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>7221</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.21</v>
+        <v>8.82</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.51</v>
+        <v>21.92</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.51</v>
+        <v>21.92</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.86</v>
+        <v>6.34</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17.87</v>
+        <v>7.07</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1481</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>10664</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>21.7</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.94</v>
+        <v>21.7</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.94</v>
+        <v>21.7</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.23</v>
+        <v>4.73</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.04</v>
+        <v>11.59</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.67</v>
+        <v>5.38</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1473</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>7818</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>32.45</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>27.77</v>
+        <v>20.47</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.77</v>
+        <v>20.47</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.14</v>
+        <v>6.48</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10.09</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.54</v>
+        <v>5.6</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1470</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9566</v>
+        <v>5256</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39.97</v>
+        <v>35.18</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.12</v>
+        <v>19.62</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.12</v>
+        <v>19.62</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.19</v>
+        <v>5.27</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.75</v>
+        <v>11.06</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.18</v>
+        <v>3.29</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1464</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>5980</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.07</v>
+        <v>38.55</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.48</v>
+        <v>18.85</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.48</v>
+        <v>18.85</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.09</v>
+        <v>7.13</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.62</v>
+        <v>7.76</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.77</v>
+        <v>3.97</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1458</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3234</v>
+        <v>9549</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.62</v>
+        <v>17.6</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>22.9</v>
+        <v>17.48</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22.9</v>
+        <v>17.48</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.98</v>
+        <v>5.36</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.87</v>
+        <v>10.59</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.05</v>
+        <v>1.53</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>10642</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8.82</v>
+        <v>25.63</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.92</v>
+        <v>16.51</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.92</v>
+        <v>16.51</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.34</v>
+        <v>4.64</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.07</v>
+        <v>6.37</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.51</v>
+        <v>5.5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1449</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>23.74</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.7</v>
+        <v>16.22</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.7</v>
+        <v>16.22</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.73</v>
+        <v>5.81</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.59</v>
+        <v>10.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.38</v>
+        <v>-0.39</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1448</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>10181</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>23.43</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.47</v>
+        <v>14.48</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.47</v>
+        <v>14.48</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.48</v>
+        <v>4.56</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.6</v>
+        <v>3.47</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1443</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>9638</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>35.18</v>
+        <v>22.93</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.62</v>
+        <v>13.05</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.62</v>
+        <v>13.05</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.27</v>
+        <v>6.04</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.06</v>
+        <v>3.26</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1440</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5980</v>
+        <v>7256</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>38.55</v>
+        <v>25.23</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.85</v>
+        <v>12.97</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.85</v>
+        <v>12.97</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7.13</v>
+        <v>2.57</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.76</v>
+        <v>4.96</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.97</v>
+        <v>5.45</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1437</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>4325</v>
+        <v>7658</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>32.52</v>
+        <v>14.34</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>18.16</v>
+        <v>5.84</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.16</v>
+        <v>5.84</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.79</v>
+        <v>3.29</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.77</v>
+        <v>4.91</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.6</v>
+        <v>-2.37</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1434</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>904</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1431</v>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10642</v>
+        <v>1023</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1426</v>
+          <t>Bedford Express</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>2075</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1425</v>
+          <t>Enigma Robotics</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>2771</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>1417</v>
+          <t>Code Red Robotics the Stray Dogs</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9638</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1410</v>
+          <t>Red Arrows</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>3620</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1409</v>
+          <t>Average Joes</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>3875</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1370</v>
+          <t>Red Storm Robotics</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>904</v>
+        <v>4325</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1367</v>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1279,7 +1279,7 @@
         <v>18.16</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.79</v>
@@ -1659,7 +1659,7 @@
         <v>18.85</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>7.13</v>
@@ -2723,7 +2723,7 @@
         <v>27.77</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>5.14</v>
@@ -2875,7 +2875,7 @@
         <v>17.48</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>5.36</v>
@@ -3103,7 +3103,7 @@
         <v>34.06</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>11.03</v>
@@ -3255,7 +3255,7 @@
         <v>38.47</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>3.62</v>
@@ -4212,7 +4212,7 @@
         <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
@@ -4274,7 +4274,7 @@
         <v>4.06</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="20">
@@ -4429,7 +4429,7 @@
         <v>12.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25">
@@ -4677,7 +4677,7 @@
         <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
@@ -4708,7 +4708,7 @@
         <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
@@ -4739,7 +4739,7 @@
         <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1117,26 +1117,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>1608</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>22.01</v>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1269,26 +1283,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1433</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>1.6</v>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1497,26 +1525,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>1440</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>3.29</v>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1649,26 +1691,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>1436</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>3.97</v>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1725,26 +1781,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>58.86</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>58.86</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>1550</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>20.14</v>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2105,26 +2175,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>23.14</v>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2865,26 +2949,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>1430</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>1.53</v>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -3169,26 +3267,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>1503</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>14.16</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>16.71</v>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3245,26 +3357,40 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L36" s="2" t="n">
-        <v>29.21</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>13.63</v>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3907,1056 +4033,1182 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>9208</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>44.43</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.16</v>
+        <v>60.89</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.16</v>
+        <v>60.89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>18.91</v>
+        <v>15.07</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.23</v>
+        <v>34.36</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.01</v>
+        <v>11.46</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1608</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>57.35</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>57.35</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.28</v>
+        <v>6.65</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.29</v>
+        <v>32.81</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.14</v>
+        <v>17.9</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1600</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9208</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>44.43</v>
+        <v>53.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>60.89</v>
+        <v>56.69</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60.89</v>
+        <v>56.69</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15.07</v>
+        <v>7.98</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>34.36</v>
+        <v>35.17</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11.46</v>
+        <v>13.54</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1555</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6081</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>59.73</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>58.86</v>
+        <v>51.63</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>58.86</v>
+        <v>51.63</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.66</v>
+        <v>6.46</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>25.05</v>
+        <v>27.33</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20.14</v>
+        <v>17.84</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1550</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>8423</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50.66</v>
+        <v>28.04</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>57.35</v>
+        <v>39.76</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.35</v>
+        <v>39.76</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.65</v>
+        <v>10.47</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.81</v>
+        <v>18.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.9</v>
+        <v>10.4</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1547</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2771</v>
+        <v>7808</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>53.52</v>
+        <v>24.37</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>56.69</v>
+        <v>34.73</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>56.69</v>
+        <v>34.73</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7.98</v>
+        <v>6.55</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>35.17</v>
+        <v>18.66</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.54</v>
+        <v>9.52</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1545</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>858</v>
+        <v>9671</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>55.1</v>
+        <v>27.39</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>51.63</v>
+        <v>34.06</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.63</v>
+        <v>34.06</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.46</v>
+        <v>11.03</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27.33</v>
+        <v>18.98</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.84</v>
+        <v>4.06</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1533</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>5501</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>31.87</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.76</v>
+        <v>31.87</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.47</v>
+        <v>6.95</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.9</v>
+        <v>17.02</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.4</v>
+        <v>7.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1504</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>7809</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>23.83</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.35</v>
+        <v>31.74</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.35</v>
+        <v>31.74</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>14.16</v>
+        <v>2.91</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.48</v>
+        <v>14.95</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.71</v>
+        <v>13.87</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1503</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>8767</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.21</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>38.47</v>
+        <v>31.51</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>38.47</v>
+        <v>31.51</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3.62</v>
+        <v>4.86</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.23</v>
+        <v>17.87</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.63</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1500</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>7289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.37</v>
+        <v>33.29</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.73</v>
+        <v>28.94</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.73</v>
+        <v>28.94</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.55</v>
+        <v>11.23</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.66</v>
+        <v>7.04</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.52</v>
+        <v>10.67</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1490</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.06</v>
+        <v>27.77</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.06</v>
+        <v>27.77</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>5.14</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.98</v>
+        <v>10.09</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4.06</v>
+        <v>12.54</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1488</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5501</v>
+        <v>9566</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>31.87</v>
+        <v>39.97</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.87</v>
+        <v>26.12</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.87</v>
+        <v>26.12</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.95</v>
+        <v>3.19</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.02</v>
+        <v>14.75</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1482</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>8285</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>39.07</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.74</v>
+        <v>24.48</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.74</v>
+        <v>24.48</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.91</v>
+        <v>5.09</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.95</v>
+        <v>11.62</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13.87</v>
+        <v>7.77</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1482</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>3234</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.21</v>
+        <v>22.62</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.51</v>
+        <v>22.9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.51</v>
+        <v>22.9</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.86</v>
+        <v>4.98</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17.87</v>
+        <v>11.87</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1481</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>7221</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>8.82</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.94</v>
+        <v>21.92</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.94</v>
+        <v>21.92</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.23</v>
+        <v>6.34</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.04</v>
+        <v>7.07</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.67</v>
+        <v>8.51</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1473</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>10664</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>21.7</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>27.77</v>
+        <v>21.7</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.77</v>
+        <v>21.7</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.14</v>
+        <v>4.73</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10.09</v>
+        <v>11.59</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.54</v>
+        <v>5.38</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1469</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9566</v>
+        <v>7818</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39.97</v>
+        <v>32.45</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.12</v>
+        <v>20.47</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.12</v>
+        <v>20.47</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.19</v>
+        <v>6.48</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.75</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.18</v>
+        <v>5.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1464</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>10642</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.07</v>
+        <v>25.63</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.48</v>
+        <v>16.51</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.48</v>
+        <v>16.51</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.09</v>
+        <v>4.64</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.62</v>
+        <v>6.37</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.77</v>
+        <v>5.5</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1458</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3234</v>
+        <v>11399</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.62</v>
+        <v>23.74</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>22.9</v>
+        <v>16.22</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22.9</v>
+        <v>16.22</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.98</v>
+        <v>5.81</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.87</v>
+        <v>10.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.05</v>
+        <v>-0.39</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>10181</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8.82</v>
+        <v>23.43</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.92</v>
+        <v>14.48</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.92</v>
+        <v>14.48</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.34</v>
+        <v>4.56</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.07</v>
+        <v>6.45</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.51</v>
+        <v>3.47</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1449</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>9638</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>22.93</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.7</v>
+        <v>13.05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.7</v>
+        <v>13.05</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.73</v>
+        <v>6.04</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.59</v>
+        <v>3.26</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.38</v>
+        <v>3.75</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1448</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>25.23</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.47</v>
+        <v>12.97</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.47</v>
+        <v>12.97</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.48</v>
+        <v>2.57</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>4.96</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1443</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>7658</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>35.18</v>
+        <v>14.34</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.62</v>
+        <v>5.84</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.62</v>
+        <v>5.84</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.27</v>
+        <v>3.29</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.06</v>
+        <v>4.91</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3.29</v>
+        <v>-2.37</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1440</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5980</v>
+        <v>904</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>38.55</v>
+        <v>27.91</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.85</v>
+        <v>5.38</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.85</v>
+        <v>5.38</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7.13</v>
+        <v>4.03</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.76</v>
+        <v>0.89</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.97</v>
+        <v>0.45</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1436</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>4325</v>
+        <v>3620</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1433</v>
+          <t>Average Joes</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>4325</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1430</v>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1426</v>
+          <t>Atomics</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>5980</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1425</v>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>6081</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>1417</v>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9638</v>
+        <v>7656</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1410</v>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>9549</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1409</v>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>9685</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1370</v>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>904</v>
+        <v>9756</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1367</v>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -2409,40 +2409,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L25" s="3" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>1443</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>5.6</v>
       </c>
     </row>
     <row r="26">
@@ -3335,40 +3321,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L37" s="3" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>1417</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>3.47</v>
       </c>
     </row>
     <row r="38">
@@ -3425,40 +3397,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="L38" s="2" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>104.79</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>104.79</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>1648</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>25.33</v>
       </c>
     </row>
     <row r="39">
@@ -3825,61 +3783,61 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5166</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>104.79</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>104.79</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>16.5</v>
+        <v>15.65</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>51.01</v>
+        <v>63.81</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21.73</v>
+        <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1619</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7220</v>
+        <v>5166</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>45.04</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>89.02</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>89.02</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>20.24</v>
+        <v>16.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>54.64</v>
+        <v>51.01</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>14.14</v>
+        <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1619</v>
@@ -3887,464 +3845,464 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>68.89</v>
+        <v>45.04</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>86.59</v>
+        <v>89.02</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.59</v>
+        <v>89.02</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>19.61</v>
+        <v>20.24</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>45.87</v>
+        <v>54.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>21.1</v>
+        <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1613</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3620</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>84.16</v>
+        <v>86.59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>84.16</v>
+        <v>86.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>18.91</v>
+        <v>19.61</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>43.23</v>
+        <v>45.87</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>22.01</v>
+        <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1608</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7656</v>
+        <v>3620</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>50.91</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>80.70999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80.70999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10.28</v>
+        <v>18.91</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>47.29</v>
+        <v>43.23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.14</v>
+        <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1600</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>9208</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>44.43</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>60.89</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>60.89</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>15.07</v>
+        <v>10.28</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34.36</v>
+        <v>47.29</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>11.46</v>
+        <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1555</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6081</v>
+        <v>9208</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>59.73</v>
+        <v>44.43</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>58.86</v>
+        <v>60.89</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>58.86</v>
+        <v>60.89</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13.66</v>
+        <v>15.07</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>25.05</v>
+        <v>34.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20.14</v>
+        <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1550</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>3875</v>
+        <v>6081</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>50.66</v>
+        <v>59.73</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>57.35</v>
+        <v>58.86</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>57.35</v>
+        <v>58.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6.65</v>
+        <v>13.66</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>32.81</v>
+        <v>25.05</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17.9</v>
+        <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2771</v>
+        <v>3875</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>53.52</v>
+        <v>50.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>56.69</v>
+        <v>57.35</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>56.69</v>
+        <v>57.35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7.98</v>
+        <v>6.65</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>35.17</v>
+        <v>32.81</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.54</v>
+        <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>51.63</v>
+        <v>56.69</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>51.63</v>
+        <v>56.69</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.46</v>
+        <v>7.98</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>27.33</v>
+        <v>35.17</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.84</v>
+        <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1533</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>858</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28.04</v>
+        <v>55.1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>39.76</v>
+        <v>51.63</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>39.76</v>
+        <v>51.63</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.47</v>
+        <v>6.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18.9</v>
+        <v>27.33</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.4</v>
+        <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1504</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9685</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>27.75</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>39.35</v>
+        <v>39.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.35</v>
+        <v>39.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>14.16</v>
+        <v>10.47</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.48</v>
+        <v>18.9</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16.71</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>29.21</v>
+        <v>27.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>38.47</v>
+        <v>39.35</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38.47</v>
+        <v>39.35</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3.62</v>
+        <v>14.16</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21.23</v>
+        <v>8.48</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.63</v>
+        <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7808</v>
+        <v>9756</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>24.37</v>
+        <v>29.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>34.73</v>
+        <v>38.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>34.73</v>
+        <v>38.47</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6.55</v>
+        <v>3.62</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>18.66</v>
+        <v>21.23</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>9.52</v>
+        <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1490</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9671</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.39</v>
+        <v>24.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>34.06</v>
+        <v>34.73</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.06</v>
+        <v>34.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>11.03</v>
+        <v>6.55</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18.98</v>
+        <v>18.66</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4.06</v>
+        <v>9.52</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>5501</v>
+        <v>9671</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>31.87</v>
+        <v>27.39</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>31.87</v>
+        <v>34.06</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>31.87</v>
+        <v>34.06</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.95</v>
+        <v>11.03</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17.02</v>
+        <v>18.98</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>7.9</v>
+        <v>4.06</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1482</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>5501</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>23.83</v>
+        <v>31.87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.74</v>
+        <v>31.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.74</v>
+        <v>31.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.91</v>
+        <v>6.95</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.95</v>
+        <v>17.02</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>13.87</v>
+        <v>7.9</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>1482</v>
@@ -4352,695 +4310,653 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>27.21</v>
+        <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.51</v>
+        <v>31.74</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.51</v>
+        <v>31.74</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4.86</v>
+        <v>2.91</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.87</v>
+        <v>14.95</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>13.87</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>33.29</v>
+        <v>27.21</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>28.94</v>
+        <v>31.51</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.94</v>
+        <v>31.51</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>11.23</v>
+        <v>4.86</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.04</v>
+        <v>17.87</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1473</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>21.07</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.14</v>
+        <v>11.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10.09</v>
+        <v>7.04</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12.54</v>
+        <v>10.67</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9566</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>39.97</v>
+        <v>21.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>26.12</v>
+        <v>27.77</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26.12</v>
+        <v>27.77</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3.19</v>
+        <v>5.14</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14.75</v>
+        <v>10.09</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>8.18</v>
+        <v>12.54</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5.09</v>
+        <v>3.19</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.62</v>
+        <v>14.75</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>7.77</v>
+        <v>8.18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1458</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3234</v>
+        <v>8285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22.62</v>
+        <v>39.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22.9</v>
+        <v>24.48</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22.9</v>
+        <v>24.48</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.98</v>
+        <v>5.09</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6.05</v>
+        <v>7.77</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1453</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.82</v>
+        <v>22.62</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>21.92</v>
+        <v>22.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>21.92</v>
+        <v>22.9</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.34</v>
+        <v>4.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.07</v>
+        <v>11.87</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.51</v>
+        <v>6.05</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>10664</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>21.7</v>
+        <v>8.82</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.7</v>
+        <v>21.92</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.7</v>
+        <v>21.92</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.73</v>
+        <v>6.34</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>11.59</v>
+        <v>7.07</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.38</v>
+        <v>8.51</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>5256</v>
+        <v>10664</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>35.18</v>
+        <v>21.7</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>19.62</v>
+        <v>21.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>19.62</v>
+        <v>21.7</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.27</v>
+        <v>4.73</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.06</v>
+        <v>11.59</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.29</v>
+        <v>5.38</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1440</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5980</v>
+        <v>7818</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>38.55</v>
+        <v>32.45</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>18.85</v>
+        <v>20.47</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>18.85</v>
+        <v>20.47</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>7.13</v>
+        <v>6.48</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>7.76</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3.97</v>
+        <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1436</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>4325</v>
+        <v>5256</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>32.52</v>
+        <v>35.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>18.16</v>
+        <v>19.62</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>18.16</v>
+        <v>19.62</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>7.79</v>
+        <v>5.27</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.77</v>
+        <v>11.06</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>3.29</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1433</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9549</v>
+        <v>5980</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>17.6</v>
+        <v>38.55</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17.48</v>
+        <v>18.85</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>17.48</v>
+        <v>18.85</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5.36</v>
+        <v>7.13</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.59</v>
+        <v>7.76</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.53</v>
+        <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1430</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10642</v>
+        <v>4325</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>25.63</v>
+        <v>32.52</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>16.51</v>
+        <v>18.16</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>16.51</v>
+        <v>18.16</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.64</v>
+        <v>7.79</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.37</v>
+        <v>8.77</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1426</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>11399</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.74</v>
+        <v>17.6</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>16.22</v>
+        <v>17.48</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.22</v>
+        <v>17.48</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.81</v>
+        <v>5.36</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.8</v>
+        <v>10.59</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>-0.39</v>
+        <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1425</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9638</v>
+        <v>10642</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>22.93</v>
+        <v>25.63</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>13.05</v>
+        <v>16.51</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>13.05</v>
+        <v>16.51</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6.04</v>
+        <v>4.64</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.26</v>
+        <v>6.37</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1410</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7256</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25.23</v>
+        <v>23.74</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>12.97</v>
+        <v>16.22</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12.97</v>
+        <v>16.22</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>2.57</v>
+        <v>5.81</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.96</v>
+        <v>10.8</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.45</v>
+        <v>-0.39</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1409</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7658</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>14.34</v>
+        <v>23.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.84</v>
+        <v>14.48</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>5.84</v>
+        <v>14.48</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3.29</v>
+        <v>4.56</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4.91</v>
+        <v>6.45</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-2.37</v>
+        <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1370</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>904</v>
+        <v>9638</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>27.91</v>
+        <v>22.93</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.38</v>
+        <v>13.05</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5.38</v>
+        <v>13.05</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.03</v>
+        <v>6.04</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.89</v>
+        <v>3.26</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.45</v>
+        <v>3.75</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1367</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7818</v>
+        <v>7256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1409</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10181</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>10633</v>
+        <v>904</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>D Cubed</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1367</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -3553,22 +3553,22 @@
         <v>21.7</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21.7</v>
+        <v>33.16</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>21.7</v>
+        <v>33.16</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1448</v>
+        <v>1482</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>4.73</v>
+        <v>7.11</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>11.59</v>
+        <v>17.73</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>5.38</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="41">
@@ -4279,30 +4279,30 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5501</v>
+        <v>10664</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>31.87</v>
+        <v>21.7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>31.87</v>
+        <v>33.16</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.87</v>
+        <v>33.16</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.95</v>
+        <v>7.11</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17.02</v>
+        <v>17.73</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7.9</v>
+        <v>8.32</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>1482</v>
@@ -4310,30 +4310,30 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>5501</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>23.83</v>
+        <v>31.87</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.74</v>
+        <v>31.87</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>31.74</v>
+        <v>31.87</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.91</v>
+        <v>6.95</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.95</v>
+        <v>17.02</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13.87</v>
+        <v>7.9</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1482</v>
@@ -4341,250 +4341,250 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>27.21</v>
+        <v>23.83</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.51</v>
+        <v>31.74</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.51</v>
+        <v>31.74</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.86</v>
+        <v>2.91</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17.87</v>
+        <v>14.95</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>13.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>8767</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>27.21</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.94</v>
+        <v>31.51</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>28.94</v>
+        <v>31.51</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.23</v>
+        <v>4.86</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.04</v>
+        <v>17.87</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1473</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>33.29</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.14</v>
+        <v>11.23</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10.09</v>
+        <v>7.04</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.54</v>
+        <v>10.67</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9566</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39.97</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.12</v>
+        <v>27.77</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>26.12</v>
+        <v>27.77</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.19</v>
+        <v>5.14</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14.75</v>
+        <v>10.09</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.18</v>
+        <v>12.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.09</v>
+        <v>3.19</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.62</v>
+        <v>14.75</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.77</v>
+        <v>8.18</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1458</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3234</v>
+        <v>8285</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.62</v>
+        <v>39.07</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>22.9</v>
+        <v>24.48</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22.9</v>
+        <v>24.48</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.98</v>
+        <v>5.09</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.05</v>
+        <v>7.77</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8.82</v>
+        <v>22.62</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>21.92</v>
+        <v>22.9</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.92</v>
+        <v>22.9</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.34</v>
+        <v>4.98</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.07</v>
+        <v>11.87</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.51</v>
+        <v>6.05</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>8.82</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.7</v>
+        <v>21.92</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.7</v>
+        <v>21.92</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.73</v>
+        <v>6.34</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.59</v>
+        <v>7.07</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.38</v>
+        <v>8.51</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="30">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -3553,22 +3553,22 @@
         <v>21.7</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>40.96</v>
+        <v>41.05</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>40.96</v>
+        <v>41.05</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>1502</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>9.51</v>
+        <v>8.48</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>23.96</v>
+        <v>26.5</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>7.49</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="41">
@@ -4135,19 +4135,19 @@
         <v>21.7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40.96</v>
+        <v>41.05</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>40.96</v>
+        <v>41.05</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9.51</v>
+        <v>8.48</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.96</v>
+        <v>26.5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>7.49</v>
+        <v>6.07</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1502</v>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -3553,22 +3553,22 @@
         <v>21.7</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.05</v>
+        <v>37.81</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>41.05</v>
+        <v>37.81</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1502</v>
+        <v>1493</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>8.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>26.5</v>
+        <v>23.83</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>6.07</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="41">
@@ -4124,126 +4124,126 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>10664</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>21.7</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>41.05</v>
+        <v>39.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>41.05</v>
+        <v>39.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8.48</v>
+        <v>10.47</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>26.5</v>
+        <v>18.9</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>6.07</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8423</v>
+        <v>9685</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>28.04</v>
+        <v>27.75</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.76</v>
+        <v>39.35</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.76</v>
+        <v>39.35</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10.47</v>
+        <v>14.16</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>18.9</v>
+        <v>8.48</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.4</v>
+        <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.75</v>
+        <v>29.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>39.35</v>
+        <v>38.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>39.35</v>
+        <v>38.47</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>14.16</v>
+        <v>3.62</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.48</v>
+        <v>21.23</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.71</v>
+        <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9756</v>
+        <v>10664</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>29.21</v>
+        <v>21.7</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>38.47</v>
+        <v>37.81</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.47</v>
+        <v>37.81</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3.62</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.23</v>
+        <v>23.83</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>13.63</v>
+        <v>4.35</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="19">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -671,7 +671,7 @@
         <v>51.63</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>6.46</v>
@@ -747,7 +747,7 @@
         <v>5.38</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>4.03</v>
@@ -823,7 +823,7 @@
         <v>109.18</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>18.87</v>
@@ -899,7 +899,7 @@
         <v>108.35</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>20.55</v>
@@ -975,7 +975,7 @@
         <v>56.69</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>7.98</v>
@@ -1051,7 +1051,7 @@
         <v>22.9</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>4.98</v>
@@ -1127,7 +1127,7 @@
         <v>84.16</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>18.91</v>
@@ -1203,7 +1203,7 @@
         <v>57.35</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.65</v>
@@ -1279,7 +1279,7 @@
         <v>18.16</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.79</v>
@@ -1355,7 +1355,7 @@
         <v>86.59</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>19.61</v>
@@ -1431,7 +1431,7 @@
         <v>89.23999999999999</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>16.5</v>
@@ -1507,7 +1507,7 @@
         <v>19.62</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>5.27</v>
@@ -1583,7 +1583,7 @@
         <v>31.87</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>6.95</v>
@@ -1659,7 +1659,7 @@
         <v>18.85</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>7.13</v>
@@ -1735,7 +1735,7 @@
         <v>58.86</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>13.66</v>
@@ -1811,7 +1811,7 @@
         <v>89.02</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>20.24</v>
@@ -1887,7 +1887,7 @@
         <v>21.92</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>6.34</v>
@@ -1963,7 +1963,7 @@
         <v>12.97</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.57</v>
@@ -2039,7 +2039,7 @@
         <v>28.94</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>11.23</v>
@@ -2115,7 +2115,7 @@
         <v>80.70999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.28</v>
@@ -2191,7 +2191,7 @@
         <v>5.84</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>3.29</v>
@@ -2267,7 +2267,7 @@
         <v>34.73</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>6.55</v>
@@ -2343,7 +2343,7 @@
         <v>31.74</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>2.91</v>
@@ -2419,7 +2419,7 @@
         <v>20.47</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>6.48</v>
@@ -2495,7 +2495,7 @@
         <v>24.48</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>5.09</v>
@@ -2571,7 +2571,7 @@
         <v>39.76</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>10.47</v>
@@ -2647,7 +2647,7 @@
         <v>31.51</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>4.86</v>
@@ -2723,7 +2723,7 @@
         <v>27.77</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>5.14</v>
@@ -2799,7 +2799,7 @@
         <v>60.89</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>15.07</v>
@@ -2875,7 +2875,7 @@
         <v>17.48</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>5.36</v>
@@ -2951,7 +2951,7 @@
         <v>26.12</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>3.19</v>
@@ -3027,7 +3027,7 @@
         <v>13.05</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>6.04</v>
@@ -3103,7 +3103,7 @@
         <v>34.06</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>11.03</v>
@@ -3179,7 +3179,7 @@
         <v>39.35</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>14.16</v>
@@ -3255,7 +3255,7 @@
         <v>38.47</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>3.62</v>
@@ -3331,7 +3331,7 @@
         <v>14.48</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.56</v>
@@ -3407,7 +3407,7 @@
         <v>104.79</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>15.65</v>
@@ -3483,7 +3483,7 @@
         <v>16.51</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>4.64</v>
@@ -3635,7 +3635,7 @@
         <v>16.22</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>5.81</v>
@@ -3747,7 +3747,7 @@
         <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="3">
@@ -3778,7 +3778,7 @@
         <v>23.17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="4">
@@ -3809,7 +3809,7 @@
         <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="5">
@@ -3840,7 +3840,7 @@
         <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1611</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="6">
@@ -3871,7 +3871,7 @@
         <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="7">
@@ -3902,7 +3902,7 @@
         <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="8">
@@ -3933,7 +3933,7 @@
         <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1600</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="9">
@@ -3964,7 +3964,7 @@
         <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1592</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="10">
@@ -3995,7 +3995,7 @@
         <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="11">
@@ -4026,7 +4026,7 @@
         <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="12">
@@ -4057,7 +4057,7 @@
         <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="13">
@@ -4088,7 +4088,7 @@
         <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14">
@@ -4119,7 +4119,7 @@
         <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="15">
@@ -4150,7 +4150,7 @@
         <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="16">
@@ -4181,7 +4181,7 @@
         <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="17">
@@ -4212,7 +4212,7 @@
         <v>13.63</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="18">
@@ -4274,7 +4274,7 @@
         <v>9.52</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20">
@@ -4305,7 +4305,7 @@
         <v>4.06</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="21">
@@ -4336,7 +4336,7 @@
         <v>7.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="22">
@@ -4367,7 +4367,7 @@
         <v>13.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="23">
@@ -4398,7 +4398,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="24">
@@ -4429,7 +4429,7 @@
         <v>10.67</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="25">
@@ -4460,7 +4460,7 @@
         <v>12.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         <v>8.18</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="27">
@@ -4522,7 +4522,7 @@
         <v>7.77</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
@@ -4553,7 +4553,7 @@
         <v>6.05</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="29">
@@ -4584,7 +4584,7 @@
         <v>8.51</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="30">
@@ -4615,7 +4615,7 @@
         <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="31">
@@ -4646,7 +4646,7 @@
         <v>3.29</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="32">
@@ -4677,7 +4677,7 @@
         <v>3.97</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="33">
@@ -4708,7 +4708,7 @@
         <v>1.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="34">
@@ -4739,7 +4739,7 @@
         <v>1.53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="35">
@@ -4770,7 +4770,7 @@
         <v>5.5</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="36">
@@ -4801,7 +4801,7 @@
         <v>-0.39</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="37">
@@ -4832,7 +4832,7 @@
         <v>3.47</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="38">
@@ -4863,7 +4863,7 @@
         <v>3.75</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="39">
@@ -4894,7 +4894,7 @@
         <v>5.45</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="40">
@@ -4925,7 +4925,7 @@
         <v>-2.37</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="41">
@@ -4956,7 +4956,7 @@
         <v>0.45</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -671,7 +671,7 @@
         <v>51.63</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>6.46</v>
@@ -823,7 +823,7 @@
         <v>109.18</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>18.87</v>
@@ -1203,7 +1203,7 @@
         <v>57.35</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.65</v>
@@ -1431,7 +1431,7 @@
         <v>89.23999999999999</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>16.5</v>
@@ -1735,7 +1735,7 @@
         <v>58.86</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>13.66</v>
@@ -1811,7 +1811,7 @@
         <v>89.02</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>20.24</v>
@@ -1887,7 +1887,7 @@
         <v>21.92</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>6.34</v>
@@ -2039,7 +2039,7 @@
         <v>28.94</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>11.23</v>
@@ -2115,7 +2115,7 @@
         <v>80.70999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.28</v>
@@ -2571,7 +2571,7 @@
         <v>39.76</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>10.47</v>
@@ -2951,7 +2951,7 @@
         <v>26.12</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>3.19</v>
@@ -3103,7 +3103,7 @@
         <v>34.06</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>11.03</v>
@@ -3179,7 +3179,7 @@
         <v>39.35</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>14.16</v>
@@ -3407,7 +3407,7 @@
         <v>104.79</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>15.65</v>
@@ -3559,7 +3559,7 @@
         <v>37.81</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>9.640000000000001</v>
@@ -3635,7 +3635,7 @@
         <v>16.22</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>5.81</v>
@@ -3747,7 +3747,7 @@
         <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="3">
@@ -3809,7 +3809,7 @@
         <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="5">
@@ -3840,7 +3840,7 @@
         <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="6">
@@ -3871,7 +3871,7 @@
         <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="7">
@@ -3964,7 +3964,7 @@
         <v>23.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="10">
@@ -4026,7 +4026,7 @@
         <v>20.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="12">
@@ -4057,7 +4057,7 @@
         <v>17.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13">
@@ -4119,7 +4119,7 @@
         <v>17.84</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="15">
@@ -4150,7 +4150,7 @@
         <v>10.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="16">
@@ -4181,7 +4181,7 @@
         <v>16.71</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="17">
@@ -4243,7 +4243,7 @@
         <v>4.35</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="19">
@@ -4305,7 +4305,7 @@
         <v>4.06</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="21">
@@ -4429,7 +4429,7 @@
         <v>10.67</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="25">
@@ -4491,7 +4491,7 @@
         <v>8.18</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="27">
@@ -4584,7 +4584,7 @@
         <v>8.51</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="30">
@@ -4801,7 +4801,7 @@
         <v>-0.39</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="37">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -975,7 +975,7 @@
         <v>56.69</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>7.98</v>
@@ -1127,7 +1127,7 @@
         <v>84.16</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>18.91</v>
@@ -1355,7 +1355,7 @@
         <v>86.59</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>19.61</v>
@@ -2191,7 +2191,7 @@
         <v>5.84</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>3.29</v>
@@ -3902,7 +3902,7 @@
         <v>21.1</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -3933,7 +3933,7 @@
         <v>22.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="9">
@@ -4088,7 +4088,7 @@
         <v>13.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="14">
@@ -4925,7 +4925,7 @@
         <v>-2.37</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="41">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -823,7 +823,7 @@
         <v>109.18</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>18.87</v>
@@ -899,7 +899,7 @@
         <v>108.35</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>20.55</v>
@@ -1431,7 +1431,7 @@
         <v>89.23999999999999</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>16.5</v>
@@ -1811,7 +1811,7 @@
         <v>89.02</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>20.24</v>
@@ -2343,7 +2343,7 @@
         <v>31.74</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>2.91</v>
@@ -2419,7 +2419,7 @@
         <v>20.47</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>6.48</v>
@@ -2495,7 +2495,7 @@
         <v>24.48</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>5.09</v>
@@ -2723,7 +2723,7 @@
         <v>27.77</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>5.14</v>
@@ -2799,7 +2799,7 @@
         <v>60.89</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>15.07</v>
@@ -3407,7 +3407,7 @@
         <v>104.79</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>15.65</v>
@@ -3747,7 +3747,7 @@
         <v>27.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="3">
@@ -3778,7 +3778,7 @@
         <v>23.17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="4">
@@ -3809,7 +3809,7 @@
         <v>25.33</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="5">
@@ -3840,7 +3840,7 @@
         <v>21.73</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="6">
@@ -3871,7 +3871,7 @@
         <v>14.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="7">
@@ -3995,7 +3995,7 @@
         <v>11.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="11">
@@ -4367,7 +4367,7 @@
         <v>13.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="23">
@@ -4460,7 +4460,7 @@
         <v>12.54</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="26">
@@ -4522,7 +4522,7 @@
         <v>7.77</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="28">
@@ -4615,7 +4615,7 @@
         <v>5.6</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="31">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -646,20 +646,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>55.1</v>
@@ -722,20 +716,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>27.91</v>
@@ -798,20 +786,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>68.08</v>
@@ -874,20 +856,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>88.79000000000001</v>
@@ -950,20 +926,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>53.52</v>
@@ -1026,20 +996,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>22.62</v>
@@ -1102,20 +1066,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>75.04000000000001</v>
@@ -1178,20 +1136,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>50.66</v>
@@ -1254,20 +1206,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>32.52</v>
@@ -1330,20 +1276,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>68.89</v>
@@ -1406,20 +1346,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>71.68000000000001</v>
@@ -1482,20 +1416,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>35.18</v>
@@ -1634,20 +1562,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>38.55</v>
@@ -1710,20 +1632,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>59.73</v>
@@ -1786,20 +1702,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>45.04</v>
@@ -1862,20 +1772,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>8.82</v>
@@ -1938,20 +1842,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>25.23</v>
@@ -2014,20 +1912,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>33.29</v>
@@ -2090,20 +1982,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>50.91</v>
@@ -2166,20 +2052,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>14.34</v>
@@ -2242,20 +2122,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>24.37</v>
@@ -2318,20 +2192,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>23.83</v>
@@ -2394,20 +2262,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>32.45</v>
@@ -2470,20 +2332,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>39.07</v>
@@ -2546,20 +2402,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>28.04</v>
@@ -2622,20 +2472,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>27.21</v>
@@ -2698,20 +2542,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.07</v>
@@ -2774,20 +2612,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>44.43</v>
@@ -2850,20 +2682,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>17.6</v>
@@ -2926,20 +2752,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>39.97</v>
@@ -3002,20 +2822,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>22.93</v>
@@ -3078,20 +2892,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>27.39</v>
@@ -3154,20 +2962,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>27.75</v>
@@ -3230,20 +3032,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>29.21</v>
@@ -3306,20 +3102,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>23.43</v>
@@ -3382,20 +3172,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>45.8</v>
@@ -3458,20 +3242,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>25.63</v>
@@ -3534,20 +3312,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>21.7</v>
@@ -3610,20 +3382,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>23.74</v>
@@ -5016,20 +4782,14 @@
           <t>Demons Robotics</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5041,20 +4801,14 @@
           <t>D Cubed</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5066,20 +4820,14 @@
           <t>Bedford Express</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5091,20 +4839,14 @@
           <t>Enigma Robotics</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5116,20 +4858,14 @@
           <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5141,20 +4877,14 @@
           <t>Red Arrows</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5166,20 +4896,14 @@
           <t>Average Joes</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5191,20 +4915,14 @@
           <t>Red Storm Robotics</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5216,20 +4934,14 @@
           <t>RoboRangers</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5241,20 +4953,14 @@
           <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5266,20 +4972,14 @@
           <t>Fabricators</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5291,704 +4991,536 @@
           <t>Atomics</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5501</v>
+        <v>5980</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6081</v>
+        <v>7220</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Steel Falcons</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7220</v>
+        <v>7221</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Viking Robotics</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7256</v>
+        <v>7289</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Blue Eagles</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7289</v>
+        <v>7656</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7656</v>
+        <v>7658</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalkaska Dragoneers</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>FROST BYTE  Robotics</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7809</v>
+        <v>7818</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bionic Bulldogs</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>8423</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Next Express</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Dark Horse Robotics</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>GRP Titans</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Eddies Circuit</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9208</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Robosnacks</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9671</v>
+        <v>9685</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9756</v>
+        <v>10181</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>10633</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>BeeBotics</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10633</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>11399</v>
+        <v>5501</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -7539,20 +7071,14 @@
           <t>Demons Robotics</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -7568,20 +7094,14 @@
           <t>D Cubed</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -7597,20 +7117,14 @@
           <t>Bedford Express</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -7626,20 +7140,14 @@
           <t>Enigma Robotics</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -7655,20 +7163,14 @@
           <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -7684,20 +7186,14 @@
           <t>Red Arrows</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -7713,20 +7209,14 @@
           <t>Average Joes</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -7742,20 +7232,14 @@
           <t>Red Storm Robotics</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -7771,20 +7255,14 @@
           <t>RoboRangers</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -7800,20 +7278,14 @@
           <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -7829,20 +7301,14 @@
           <t>Fabricators</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -7858,20 +7324,14 @@
           <t>Atomics</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -7880,27 +7340,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5501</v>
+        <v>5980</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -7909,27 +7363,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5980</v>
+        <v>6081</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -7938,27 +7386,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6081</v>
+        <v>7220</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Steel Falcons</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -7967,27 +7409,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7220</v>
+        <v>7221</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Viking Robotics</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -7996,27 +7432,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -8025,27 +7455,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7256</v>
+        <v>7289</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Blue Eagles</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -8054,27 +7478,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7289</v>
+        <v>7656</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -8083,27 +7501,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7656</v>
+        <v>7658</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -8112,27 +7524,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7658</v>
+        <v>7808</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalkaska Dragoneers</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -8141,27 +7547,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>FROST BYTE  Robotics</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -8170,27 +7570,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7809</v>
+        <v>7818</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -8199,27 +7593,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bionic Bulldogs</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -8228,27 +7616,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8285</v>
+        <v>8423</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Next Express</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -8257,27 +7639,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Dark Horse Robotics</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -8286,27 +7662,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>GRP Titans</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -8315,27 +7685,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9206</v>
+        <v>9208</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Eddies Circuit</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -8344,27 +7708,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9208</v>
+        <v>9549</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -8373,27 +7731,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -8402,27 +7754,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -8431,27 +7777,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Robosnacks</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -8460,27 +7800,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9671</v>
+        <v>9685</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -8489,27 +7823,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -8518,27 +7846,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>9756</v>
+        <v>10181</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -8547,27 +7869,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10181</v>
+        <v>10633</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>BeeBotics</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -8576,27 +7892,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>10633</v>
+        <v>10642</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -8605,27 +7915,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -8634,27 +7938,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>
@@ -8663,11 +7961,11 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>11399</v>
+        <v>5501</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -609,462 +609,392 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Belmont, Michigan</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>55.1</v>
+        <v>68.89</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>51.63</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>51.63</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1525</v>
+        <v>1626</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>6.46</v>
+        <v>22.33</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>27.33</v>
+        <v>53.28</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>17.84</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>904</v>
+        <v>9638</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Gobles, Michigan</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>27.91</v>
+        <v>22.93</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>5.38</v>
+        <v>25.95</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>5.38</v>
+        <v>25.95</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1363</v>
+        <v>1457</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>4.03</v>
+        <v>8.75</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.89</v>
+        <v>10.67</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.45</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bridgman, Michigan</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>109.18</v>
+        <v>117.69</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>109.18</v>
+        <v>117.69</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1644</v>
+        <v>1656</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>18.87</v>
+        <v>18.36</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>63.16</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>27.16</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>3620</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Saint Joseph, Michigan</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>108.35</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>108.35</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1643</v>
+        <v>1615</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>20.55</v>
+        <v>20.28</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>64.63</v>
+        <v>49.41</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>23.17</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2771</v>
+        <v>7256</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalamazoo, Michigan</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>53.52</v>
+        <v>25.23</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>56.69</v>
+        <v>23.05</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>56.69</v>
+        <v>23.05</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1536</v>
+        <v>1447</v>
       </c>
       <c r="P6" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="R6" s="2" t="n">
         <v>7.98</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>35.17</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>13.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3234</v>
+        <v>2771</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grandville, Michigan</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>22.62</v>
+        <v>53.52</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>22.9</v>
+        <v>66.77</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>22.9</v>
+        <v>66.77</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1447</v>
+        <v>1557</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4.98</v>
+        <v>9.35</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>11.87</v>
+        <v>41.35</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>6.05</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>11399</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Eau Claire, Michigan</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
@@ -1076,65 +1006,55 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>23.74</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>84.16</v>
+        <v>16.22</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>84.16</v>
+        <v>16.22</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1595</v>
+        <v>1419</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>18.91</v>
+        <v>5.81</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>43.23</v>
+        <v>10.8</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>22.01</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>7289</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Fowler, Michigan</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0</v>
@@ -1146,65 +1066,55 @@
         <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>50.66</v>
+        <v>33.29</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>57.35</v>
+        <v>28.94</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>57.35</v>
+        <v>28.94</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1538</v>
+        <v>1467</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.65</v>
+        <v>11.23</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>32.81</v>
+        <v>7.04</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>17.9</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4325</v>
+        <v>1023</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Temperance, Michigan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -1213,1124 +1123,958 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>32.52</v>
+        <v>68.08</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18.16</v>
+        <v>109.18</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>18.16</v>
+        <v>109.18</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1428</v>
+        <v>1644</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>7.79</v>
+        <v>18.87</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>8.77</v>
+        <v>63.16</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1.6</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>4967</v>
+        <v>9206</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grand Rapids, Michigan</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>68.89</v>
+        <v>21.07</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>86.59</v>
+        <v>29.71</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>86.59</v>
+        <v>29.71</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1600</v>
+        <v>1469</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>19.61</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>45.87</v>
+        <v>11.51</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.1</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5166</v>
+        <v>10642</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalamazoo, Michigan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>25.63</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>18.44</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>89.23999999999999</v>
+        <v>18.44</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1605</v>
+        <v>1429</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>16.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>51.01</v>
+        <v>7.79</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>21.73</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>5256</v>
+        <v>7656</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Michigan Center, Michigan</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>35.18</v>
+        <v>50.91</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>19.62</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>19.62</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1434</v>
+        <v>1591</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>5.27</v>
+        <v>9.34</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>11.06</v>
+        <v>48.71</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>3.29</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5501</v>
+        <v>3875</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Burr Oak, Michigan</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kentwood, Michigan</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>23.67</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>31.87</v>
+        <v>50.66</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>31.87</v>
+        <v>59.32</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>31.87</v>
+        <v>59.32</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1476</v>
+        <v>1541</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>6.95</v>
+        <v>6.01</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>17.02</v>
+        <v>34.21</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>7.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>5980</v>
+        <v>9549</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Covert, Michigan</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>38.55</v>
+        <v>17.6</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.85</v>
+        <v>19.45</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>18.85</v>
+        <v>19.45</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>7.13</v>
+        <v>4.73</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>7.76</v>
+        <v>11.98</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>3.97</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6081</v>
+        <v>7808</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalkaska, Michigan</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>59.73</v>
+        <v>24.37</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>58.86</v>
+        <v>36.69</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>58.86</v>
+        <v>36.69</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1541</v>
+        <v>1488</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>13.66</v>
+        <v>5.91</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>25.05</v>
+        <v>20.06</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>20.14</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7220</v>
+        <v>10664</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Muskegon, Michigan</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>45.04</v>
+        <v>21.7</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>89.02</v>
+        <v>33</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>89.02</v>
+        <v>33</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1605</v>
+        <v>1478</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>20.24</v>
+        <v>9.84</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>54.64</v>
+        <v>19.3</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>14.14</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7221</v>
+        <v>9685</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bay City, Michigan</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.82</v>
+        <v>27.75</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21.92</v>
+        <v>34.54</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>21.92</v>
+        <v>34.54</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1443</v>
+        <v>1483</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.34</v>
+        <v>14.36</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>7.07</v>
+        <v>3.95</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>8.51</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7256</v>
+        <v>7220</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Brighton, Michigan</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>25.23</v>
+        <v>45.04</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>12.97</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>12.97</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1404</v>
+        <v>1594</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.57</v>
+        <v>20.44</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>4.96</v>
+        <v>50.11</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>5.45</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7289</v>
+        <v>7221</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Jackson, Michigan</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>33.29</v>
+        <v>8.82</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>28.94</v>
+        <v>22.69</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>28.94</v>
+        <v>22.69</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1467</v>
+        <v>1445</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>11.23</v>
+        <v>7.23</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>7.04</v>
+        <v>5.91</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>10.67</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7656</v>
+        <v>2075</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grand Rapids, Michigan</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>50.91</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>109.12</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>109.12</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1588</v>
+        <v>1643</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.28</v>
+        <v>21.44</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>47.29</v>
+        <v>63.46</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>23.14</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7658</v>
+        <v>4325</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Cassopolis, Michigan</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>14.34</v>
+        <v>32.52</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5.84</v>
+        <v>18.94</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.84</v>
+        <v>18.94</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1366</v>
+        <v>1431</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>3.29</v>
+        <v>8.68</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>4.91</v>
+        <v>7.61</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>-2.37</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7808</v>
+        <v>858</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Wyoming, Michigan</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>24.37</v>
+        <v>55.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>34.73</v>
+        <v>56.12</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>34.73</v>
+        <v>56.12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1484</v>
+        <v>1534</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.55</v>
+        <v>6.92</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>18.66</v>
+        <v>29.84</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>9.52</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Fife Lake, Michigan</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>23.83</v>
+        <v>23.43</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>31.74</v>
+        <v>18.98</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>31.74</v>
+        <v>18.98</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1475</v>
+        <v>1431</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>2.91</v>
+        <v>5.02</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>14.95</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>13.87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7818</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Ravenna, Michigan</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>32.45</v>
+        <v>39.07</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>20.47</v>
+        <v>28.97</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>20.47</v>
+        <v>28.97</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>6.48</v>
+        <v>5.55</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>14.13</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>5.6</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kentwood, Michigan</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
@@ -2342,65 +2086,55 @@
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>5.09</v>
+        <v>3.19</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>11.62</v>
+        <v>14.75</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>7.77</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8423</v>
+        <v>6081</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Manchester, Michigan</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
@@ -2409,68 +2143,58 @@
         <v>0</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>28.04</v>
+        <v>59.73</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>39.76</v>
+        <v>58.86</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>39.76</v>
+        <v>58.86</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1497</v>
+        <v>1541</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.47</v>
+        <v>13.66</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>18.9</v>
+        <v>25.05</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>10.4</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8767</v>
+        <v>904</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grand Rapids, Michigan</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
@@ -2482,669 +2206,579 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>27.21</v>
+        <v>27.91</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>31.51</v>
+        <v>5.38</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>31.51</v>
+        <v>5.38</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1475</v>
+        <v>1363</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>17.87</v>
+        <v>0.89</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9206</v>
+        <v>7818</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Williamston, Michigan</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>21.07</v>
+        <v>32.45</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>27.77</v>
+        <v>20.28</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>27.77</v>
+        <v>20.28</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1463</v>
+        <v>1436</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.14</v>
+        <v>5.92</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>10.09</v>
+        <v>8.66</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>12.54</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9208</v>
+        <v>8767</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>North Branch, Michigan</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>44.43</v>
+        <v>27.21</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>60.89</v>
+        <v>31.32</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>60.89</v>
+        <v>31.32</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1545</v>
+        <v>1474</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>15.07</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>34.36</v>
+        <v>18.14</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>11.46</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9549</v>
+        <v>5980</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grand Rapids, Michigan</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>17.6</v>
+        <v>38.55</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>17.48</v>
+        <v>18.66</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>17.48</v>
+        <v>18.66</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>5.36</v>
+        <v>6.56</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>10.59</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>1.53</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Kalamazoo, Michigan</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>39.97</v>
+        <v>14.34</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>26.12</v>
+        <v>4.34</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>26.12</v>
+        <v>4.34</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1458</v>
+        <v>1358</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>3.19</v>
+        <v>3.43</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>14.75</v>
+        <v>3.71</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>8.18</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Grand Rapids, Michigan</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>22.93</v>
+        <v>27.39</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13.05</v>
+        <v>32.57</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>13.05</v>
+        <v>32.57</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1404</v>
+        <v>1477</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6.04</v>
+        <v>11.17</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>3.26</v>
+        <v>17.77</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9671</v>
+        <v>9756</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Hesperia, Michigan</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>27.39</v>
+        <v>29.21</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>34.06</v>
+        <v>36.98</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>34.06</v>
+        <v>36.98</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>11.03</v>
+        <v>3.75</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>18.98</v>
+        <v>20.02</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>4.06</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9685</v>
+        <v>9208</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Edwardsburg, Michigan</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>27.75</v>
+        <v>44.43</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>39.35</v>
+        <v>55.86</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>39.35</v>
+        <v>55.86</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1496</v>
+        <v>1534</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>14.16</v>
+        <v>14.61</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>8.48</v>
+        <v>31.54</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>16.71</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9756</v>
+        <v>7809</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Bangor, Michigan</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>29.21</v>
+        <v>23.83</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>38.47</v>
+        <v>26.7</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>38.47</v>
+        <v>26.7</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1494</v>
+        <v>1459</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>21.23</v>
+        <v>12.14</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>13.63</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Lowell, Michigan</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>14.48</v>
+        <v>17.86</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>14.48</v>
+        <v>17.86</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1411</v>
+        <v>1426</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>6.45</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>3.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3182,39 +2816,39 @@
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>45.8</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>104.79</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>104.79</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1637</v>
+        <v>1605</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>15.65</v>
+        <v>16.5</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>63.81</v>
+        <v>51.01</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>25.33</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3252,39 +2886,39 @@
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>25.63</v>
+        <v>35.18</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>16.51</v>
+        <v>19.62</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>16.51</v>
+        <v>19.62</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1421</v>
+        <v>1434</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.64</v>
+        <v>5.27</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>6.37</v>
+        <v>11.06</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>5.5</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>10664</v>
+        <v>5501</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Burr Oak, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3312,49 +2946,55 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>21.7</v>
+        <v>31.87</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37.81</v>
+        <v>31.87</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>37.81</v>
+        <v>31.87</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1492</v>
+        <v>1476</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>23.83</v>
+        <v>17.02</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>4.35</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>11399</v>
+        <v>8423</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3392,25 +3032,25 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>23.74</v>
+        <v>28.04</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>16.22</v>
+        <v>39.76</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>16.22</v>
+        <v>39.76</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1419</v>
+        <v>1497</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>5.81</v>
+        <v>10.47</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>10.8</v>
+        <v>18.9</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.39</v>
+        <v>10.4</v>
       </c>
     </row>
   </sheetData>
@@ -3487,219 +3127,219 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>109.18</v>
+        <v>117.69</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>109.18</v>
+        <v>117.69</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18.87</v>
+        <v>18.36</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.16</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>27.16</v>
+        <v>28.12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1644</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108.35</v>
+        <v>109.18</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>108.35</v>
+        <v>109.18</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>20.55</v>
+        <v>18.87</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>64.63</v>
+        <v>63.16</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>23.17</v>
+        <v>27.16</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.8</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>104.79</v>
+        <v>109.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>104.79</v>
+        <v>109.12</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.65</v>
+        <v>21.44</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.81</v>
+        <v>63.46</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.33</v>
+        <v>24.22</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1637</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5166</v>
+        <v>4967</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16.5</v>
+        <v>22.33</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>51.01</v>
+        <v>53.28</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21.73</v>
+        <v>23.89</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1605</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89.02</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>89.02</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.24</v>
+        <v>20.28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.64</v>
+        <v>49.41</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.14</v>
+        <v>24.55</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1605</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4967</v>
+        <v>5166</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>68.89</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>86.59</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>86.59</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19.61</v>
+        <v>16.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45.87</v>
+        <v>51.01</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>21.1</v>
+        <v>21.73</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1600</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.16</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.16</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>18.91</v>
+        <v>20.44</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.23</v>
+        <v>50.11</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.01</v>
+        <v>13.66</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="9">
@@ -3715,81 +3355,81 @@
         <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.28</v>
+        <v>9.34</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.29</v>
+        <v>48.71</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23.14</v>
+        <v>24.59</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1588</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9208</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>44.43</v>
+        <v>53.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>60.89</v>
+        <v>66.77</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60.89</v>
+        <v>66.77</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15.07</v>
+        <v>9.35</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>34.36</v>
+        <v>41.35</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11.46</v>
+        <v>16.08</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1545</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6081</v>
+        <v>3875</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>59.73</v>
+        <v>50.66</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>58.86</v>
+        <v>59.32</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>58.86</v>
+        <v>59.32</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.66</v>
+        <v>6.01</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>25.05</v>
+        <v>34.21</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>20.14</v>
+        <v>19.1</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1541</v>
@@ -3797,95 +3437,95 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3875</v>
+        <v>6081</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50.66</v>
+        <v>59.73</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>57.35</v>
+        <v>58.86</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.35</v>
+        <v>58.86</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.65</v>
+        <v>13.66</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.81</v>
+        <v>25.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.9</v>
+        <v>20.14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1538</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>56.69</v>
+        <v>56.12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>56.69</v>
+        <v>56.12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7.98</v>
+        <v>6.92</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>35.17</v>
+        <v>29.84</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.54</v>
+        <v>19.37</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>858</v>
+        <v>9208</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>55.1</v>
+        <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>51.63</v>
+        <v>55.86</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.63</v>
+        <v>55.86</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.46</v>
+        <v>14.61</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27.33</v>
+        <v>31.54</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.84</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1525</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="15">
@@ -3921,126 +3561,126 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>9756</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>27.75</v>
+        <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.35</v>
+        <v>36.98</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39.35</v>
+        <v>36.98</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>14.16</v>
+        <v>3.75</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.48</v>
+        <v>20.02</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16.71</v>
+        <v>13.21</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1496</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9756</v>
+        <v>7808</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.21</v>
+        <v>24.37</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>38.47</v>
+        <v>36.69</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>38.47</v>
+        <v>36.69</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3.62</v>
+        <v>5.91</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>21.23</v>
+        <v>20.06</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.63</v>
+        <v>10.72</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1494</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>10664</v>
+        <v>9685</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>21.7</v>
+        <v>27.75</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>37.81</v>
+        <v>34.54</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.81</v>
+        <v>34.54</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>14.36</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23.83</v>
+        <v>3.95</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4.35</v>
+        <v>16.23</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1492</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7808</v>
+        <v>10664</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>24.37</v>
+        <v>21.7</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.73</v>
+        <v>33</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>34.73</v>
+        <v>33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.55</v>
+        <v>9.84</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.66</v>
+        <v>19.3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>9.52</v>
+        <v>3.87</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1484</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="20">
@@ -4056,22 +3696,22 @@
         <v>27.39</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.06</v>
+        <v>32.57</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.06</v>
+        <v>32.57</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>11.03</v>
+        <v>11.17</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.98</v>
+        <v>17.77</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4.06</v>
+        <v>3.64</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1482</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="21">
@@ -4107,92 +3747,92 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7809</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>23.83</v>
+        <v>27.21</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.74</v>
+        <v>31.32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.74</v>
+        <v>31.32</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2.91</v>
+        <v>4.3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14.95</v>
+        <v>18.14</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>13.87</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>27.21</v>
+        <v>21.07</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.51</v>
+        <v>29.71</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.51</v>
+        <v>29.71</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.86</v>
+        <v>4.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>17.87</v>
+        <v>11.51</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>13.99</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1475</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7289</v>
+        <v>8285</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33.29</v>
+        <v>39.07</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.94</v>
+        <v>28.97</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.94</v>
+        <v>28.97</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>11.23</v>
+        <v>5.55</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7.04</v>
+        <v>14.13</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>1467</v>
@@ -4200,529 +3840,529 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>33.29</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>27.77</v>
+        <v>28.94</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5.14</v>
+        <v>11.23</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.09</v>
+        <v>7.04</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.54</v>
+        <v>10.67</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1463</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9566</v>
+        <v>7809</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>39.97</v>
+        <v>23.83</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.12</v>
+        <v>26.7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.12</v>
+        <v>26.7</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>14.75</v>
+        <v>12.14</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.18</v>
+        <v>12.11</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>39.07</v>
+        <v>39.97</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.48</v>
+        <v>26.12</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.09</v>
+        <v>3.19</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.62</v>
+        <v>14.75</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.77</v>
+        <v>8.18</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1452</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3234</v>
+        <v>9638</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>22.62</v>
+        <v>22.93</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>22.9</v>
+        <v>25.95</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>22.9</v>
+        <v>25.95</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.98</v>
+        <v>8.75</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>11.87</v>
+        <v>10.67</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.05</v>
+        <v>6.54</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1447</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>7256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.82</v>
+        <v>25.23</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>21.92</v>
+        <v>23.05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.92</v>
+        <v>23.05</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.34</v>
+        <v>3.94</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.07</v>
+        <v>11.13</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.51</v>
+        <v>7.98</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1443</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7818</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32.45</v>
+        <v>8.82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.47</v>
+        <v>22.69</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.47</v>
+        <v>22.69</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.48</v>
+        <v>7.23</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.6</v>
+        <v>9.56</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1437</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>35.18</v>
+        <v>32.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.62</v>
+        <v>20.28</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.62</v>
+        <v>20.28</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5.27</v>
+        <v>5.92</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.06</v>
+        <v>8.66</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>3.29</v>
+        <v>5.71</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1434</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5980</v>
+        <v>5256</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>38.55</v>
+        <v>35.18</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.85</v>
+        <v>19.62</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.85</v>
+        <v>19.62</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7.13</v>
+        <v>5.27</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.76</v>
+        <v>11.06</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.97</v>
+        <v>3.29</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>4325</v>
+        <v>9549</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>32.52</v>
+        <v>17.6</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>18.16</v>
+        <v>19.45</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.16</v>
+        <v>19.45</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.79</v>
+        <v>4.73</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.77</v>
+        <v>11.98</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.6</v>
+        <v>2.74</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1428</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>10181</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>17.6</v>
+        <v>23.43</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.48</v>
+        <v>18.98</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.48</v>
+        <v>18.98</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.36</v>
+        <v>5.02</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.59</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.53</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10642</v>
+        <v>4325</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.63</v>
+        <v>32.52</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>16.51</v>
+        <v>18.94</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>16.51</v>
+        <v>18.94</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.64</v>
+        <v>8.68</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6.37</v>
+        <v>7.61</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1421</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>5980</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.74</v>
+        <v>38.55</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.22</v>
+        <v>18.66</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.22</v>
+        <v>18.66</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.81</v>
+        <v>6.56</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10.8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>-0.39</v>
+        <v>4.08</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1419</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>10642</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.43</v>
+        <v>25.63</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>14.48</v>
+        <v>18.44</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>14.48</v>
+        <v>18.44</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.56</v>
+        <v>3.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6.45</v>
+        <v>7.79</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3.47</v>
+        <v>6.95</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1411</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9638</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.93</v>
+        <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.05</v>
+        <v>17.86</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.05</v>
+        <v>17.86</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6.04</v>
+        <v>4.52</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.26</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.75</v>
+        <v>4.29</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1404</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>11399</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>25.23</v>
+        <v>23.74</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12.97</v>
+        <v>16.22</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.97</v>
+        <v>16.22</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2.57</v>
+        <v>5.81</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.96</v>
+        <v>10.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>5.45</v>
+        <v>-0.39</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1404</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>14.34</v>
+        <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5.84</v>
+        <v>5.38</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5.84</v>
+        <v>5.38</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3.29</v>
+        <v>4.03</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.91</v>
+        <v>0.89</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-2.37</v>
+        <v>0.45</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.91</v>
+        <v>14.34</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>5.38</v>
+        <v>4.34</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5.38</v>
+        <v>4.34</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4.03</v>
+        <v>3.43</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.89</v>
+        <v>3.71</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.45</v>
+        <v>-2.79</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1363</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>
@@ -4775,420 +4415,420 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>904</v>
+        <v>9638</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2771</v>
+        <v>3620</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3620</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>4325</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4325</v>
+        <v>7221</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>4967</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5166</v>
+        <v>8285</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>5256</v>
+        <v>10181</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5980</v>
+        <v>7656</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>6081</v>
+        <v>9206</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7220</v>
+        <v>10642</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7221</v>
+        <v>3875</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7256</v>
+        <v>7808</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7289</v>
+        <v>9549</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7656</v>
+        <v>7220</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7658</v>
+        <v>9685</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7808</v>
+        <v>10664</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7809</v>
+        <v>5980</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
     </row>
     <row r="24">
@@ -5201,155 +4841,155 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>8767</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8423</v>
+        <v>7658</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8767</v>
+        <v>9671</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9206</v>
+        <v>9756</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9208</v>
+        <v>3234</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9549</v>
+        <v>7809</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9566</v>
+        <v>9208</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9638</v>
+        <v>904</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -5364,11 +5004,11 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9671</v>
+        <v>1023</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -5378,16 +5018,16 @@
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9685</v>
+        <v>5166</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -5402,11 +5042,11 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9756</v>
+        <v>5256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -5421,11 +5061,11 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10181</v>
+        <v>6081</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -5435,16 +5075,16 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10633</v>
+        <v>7289</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -5459,11 +5099,11 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>8423</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -5478,11 +5118,11 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10664</v>
+        <v>9566</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -5600,1263 +5240,903 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
+        <v>4967</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>That ONE Team-OurNextEngineers</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>9638</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tigers, Bro!</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10633</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BeeBotics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3620</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Average Joes</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7256</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Irish Robotics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2771</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Code Red Robotics the Stray Dogs</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11399</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Timber Tech</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>7289</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Blue Eagles</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Bedford Express</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9206</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>GRP Titans</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10642</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Comstock Colts</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>7656</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>MC Hammers</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3875</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Red Storm Robotics</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9549</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>The Mechadogs</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>7808</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Kalkaska Dragoneers</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10664</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Big Reds</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9685</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Crystal Oscillators</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7220</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Steel Falcons</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7221</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Viking Robotics</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2075</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Enigma Robotics</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>RoboRangers</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>858</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Demons Robotics</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>10181</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ProtoWarriors</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8285</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Bionic Bulldogs</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>9566</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Red Storm Rookies</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6081</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Digital Dislocators</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>904</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>D Cubed</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Bedford Express</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2075</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Enigma Robotics</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2771</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Code Red Robotics the Stray Dogs</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7818</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Williamston High School Vespidae</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>8767</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Dark Horse Robotics</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>East Grand Rapids Robotics</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>7658</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>MagiTech</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>9671</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Robosnacks</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>9756</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Robo Panthers</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>9208</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Eddies Circuit</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>7809</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>FROST BYTE  Robotics</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>3234</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Red Arrows</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3620</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Average Joes</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>3875</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Red Storm Robotics</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>4325</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>RoboRangers</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>4967</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>That ONE Team-OurNextEngineers</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Fabricators</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>5256</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Atomics</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>5501</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Bobcats</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>5980</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>East Grand Rapids Robotics</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>6081</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Digital Dislocators</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>7220</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Steel Falcons</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>7221</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Viking Robotics</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>7256</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Irish Robotics</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>7289</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Blue Eagles</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>7656</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>MC Hammers</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>7658</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>MagiTech</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>7808</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Kalkaska Dragoneers</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>7809</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>FROST BYTE  Robotics</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>7818</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Williamston High School Vespidae</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>8285</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Bionic Bulldogs</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>8423</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Next Express</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>8767</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Dark Horse Robotics</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>9206</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>GRP Titans</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>9208</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Eddies Circuit</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>9549</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>The Mechadogs</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>9566</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Red Storm Rookies</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>9638</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Tigers, Bro!</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>9671</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Robosnacks</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>9685</v>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Crystal Oscillators</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>9756</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Robo Panthers</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>10181</v>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>ProtoWarriors</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6866,11 +6146,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -6901,11 +6181,11 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6936,11 +6216,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>10664</v>
+        <v>5501</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -6971,11 +6251,11 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>11399</v>
+        <v>8423</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -7064,21 +6344,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -7087,21 +6367,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>904</v>
+        <v>9638</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -7110,21 +6390,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>79.33</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -7133,21 +6413,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2075</v>
+        <v>2771</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -7156,21 +6436,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2771</v>
+        <v>3620</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -7179,21 +6459,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -7202,21 +6482,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3620</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -7225,21 +6505,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3875</v>
+        <v>4325</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -7248,21 +6528,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4325</v>
+        <v>7221</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>132.67</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>-79.33</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -7271,21 +6551,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4967</v>
+        <v>858</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -7294,21 +6574,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5166</v>
+        <v>8285</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -7317,21 +6597,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5256</v>
+        <v>10181</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>52.67</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>101.67</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -7340,21 +6620,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5980</v>
+        <v>7656</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -7363,21 +6643,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>6081</v>
+        <v>9206</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -7386,21 +6666,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7220</v>
+        <v>10642</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -7409,21 +6689,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7221</v>
+        <v>3875</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -7432,21 +6712,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7256</v>
+        <v>7808</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -7455,21 +6735,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7289</v>
+        <v>9549</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -7478,21 +6758,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7656</v>
+        <v>7220</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -7501,21 +6781,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7658</v>
+        <v>9685</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -7524,21 +6804,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7808</v>
+        <v>10664</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>17.67</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -7547,21 +6827,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7809</v>
+        <v>5980</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -7578,13 +6858,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -7593,21 +6873,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8285</v>
+        <v>8767</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>-23.67</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -7616,21 +6896,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8423</v>
+        <v>7658</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -7639,21 +6919,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8767</v>
+        <v>9671</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -7662,21 +6942,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>9206</v>
+        <v>9756</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>36.33</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>-17.67</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -7685,21 +6965,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9208</v>
+        <v>3234</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -7708,21 +6988,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9549</v>
+        <v>7809</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -7731,21 +7011,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9566</v>
+        <v>9208</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>51.33</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -7754,11 +7034,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9638</v>
+        <v>904</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -7777,11 +7057,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9671</v>
+        <v>1023</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -7791,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7800,11 +7080,11 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9685</v>
+        <v>5166</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -7823,11 +7103,11 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9756</v>
+        <v>5256</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -7846,11 +7126,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>10181</v>
+        <v>6081</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -7860,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7869,11 +7149,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10633</v>
+        <v>7289</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -7892,11 +7172,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>10642</v>
+        <v>8423</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -7915,11 +7195,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>10664</v>
+        <v>9566</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,37 +634,37 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>212.62</v>
+        <v>201.9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-15.86</v>
+        <v>-10.48</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>228.49</v>
+        <v>212.39</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>126.18</v>
+        <v>128.5</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>126.18</v>
+        <v>128.5</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.21</v>
+        <v>27.16</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>69.73</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>31.24</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="3">
@@ -685,7 +685,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>1</v>
@@ -694,37 +694,37 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>125.36</v>
+        <v>146.6</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>101.91</v>
+        <v>101.47</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>23.46</v>
+        <v>45.14</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>113.57</v>
+        <v>120.09</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>113.57</v>
+        <v>120.09</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>27.31</v>
+        <v>27.43</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>19.66</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="4">
@@ -757,13 +757,13 @@
         <v>24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>102.42</v>
+        <v>103.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35.78</v>
+        <v>39.76</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>66.64</v>
+        <v>63.63</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>50.91</v>
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -814,111 +814,111 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>10.17</v>
+        <v>12.31</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-47.3</v>
+        <v>-56.08</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>57.47</v>
+        <v>68.39</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>24.37</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>39.89</v>
+        <v>37.87</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>39.89</v>
+        <v>37.87</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>5.37</v>
+        <v>5.52</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>22.68</v>
+        <v>20.61</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>11.84</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>142.25</v>
+        <v>106.59</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28.04</v>
+        <v>30.01</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>114.21</v>
+        <v>76.58</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>68.08</v>
+        <v>53.52</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>124.83</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>124.83</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1661</v>
+        <v>1581</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>21.41</v>
+        <v>7.81</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>73.97</v>
+        <v>51.37</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>29.45</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2771</v>
+        <v>2075</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -928,57 +928,57 @@
         <v>5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>100.52</v>
+        <v>98.48</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>34.01</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>66.52</v>
+        <v>27.59</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>53.52</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>70.09</v>
+        <v>115.51</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>70.09</v>
+        <v>115.51</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1561</v>
+        <v>1648</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.99</v>
+        <v>25.75</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>44.97</v>
+        <v>63.95</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>16.13</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -997,48 +997,48 @@
         <v>19</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>142.13</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>82.86</v>
+        <v>-10.34</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>152.47</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>115.05</v>
+        <v>105.05</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>115.05</v>
+        <v>105.05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1648</v>
+        <v>1632</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>25.89</v>
+        <v>24.29</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>63.31</v>
+        <v>55.97</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>25.85</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>4967</v>
+        <v>10633</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1057,34 +1057,34 @@
         <v>19</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>150.58</v>
+        <v>180.95</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-23.63</v>
+        <v>49.45</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>174.21</v>
+        <v>131.5</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>68.89</v>
+        <v>45.8</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>105.05</v>
+        <v>123.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105.05</v>
+        <v>123.2</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1632</v>
+        <v>1659</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>24.29</v>
+        <v>21.49</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>55.97</v>
+        <v>68.55</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.79</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="10">
@@ -1117,13 +1117,13 @@
         <v>19</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>160.41</v>
+        <v>153.01</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>78.5</v>
+        <v>93.13</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>81.91</v>
+        <v>59.88</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>50.66</v>
@@ -1149,83 +1149,83 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7289</v>
+        <v>1023</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>63.37</v>
+        <v>131.85</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>22.67</v>
+        <v>41.71</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>40.7</v>
+        <v>90.14</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>33.29</v>
+        <v>68.08</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>32.42</v>
+        <v>120.67</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>32.42</v>
+        <v>120.67</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1475</v>
+        <v>1654</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>13.7</v>
+        <v>23.32</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>7.68</v>
+        <v>70.67</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>11.04</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>2</v>
@@ -1234,37 +1234,37 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>176.96</v>
+        <v>102.15</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>52.41</v>
+        <v>16.44</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>124.55</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>45.8</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>122.17</v>
+        <v>95.72</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>122.17</v>
+        <v>95.72</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1657</v>
+        <v>1612</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>21.02</v>
+        <v>16.87</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>69.78</v>
+        <v>57.21</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>31.38</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="13">
@@ -1285,7 +1285,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2</v>
@@ -1294,58 +1294,58 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>10.97</v>
+        <v>20.96</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-5.91</v>
+        <v>-1.01</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>16.88</v>
+        <v>21.96</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>44.43</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>58.95</v>
+        <v>59.41</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>58.95</v>
+        <v>59.41</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>16.68</v>
+        <v>16.54</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>31.41</v>
+        <v>32.05</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5166</v>
+        <v>7289</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>2</v>
@@ -1354,58 +1354,58 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>116.97</v>
+        <v>58.84</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>25.68</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>103.97</v>
+        <v>33.16</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>33.29</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>97.73999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>97.73999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1617</v>
+        <v>1476</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>16.72</v>
+        <v>14.36</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>59.29</v>
+        <v>7.39</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>21.74</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>858</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>2</v>
@@ -1414,61 +1414,61 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>132.21</v>
+        <v>64.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>48.32</v>
+        <v>-53.04</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>83.89</v>
+        <v>117.52</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>55.1</v>
+        <v>28.04</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>70.34</v>
+        <v>55.87</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>70.34</v>
+        <v>55.87</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1561</v>
+        <v>1530</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.16</v>
+        <v>12.62</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>37.01</v>
+        <v>28.68</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>23.16</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -1477,55 +1477,55 @@
         <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>58</v>
+        <v>78.39</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-13.94</v>
+        <v>37.2</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>71.94</v>
+        <v>41.19</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>27.75</v>
+        <v>38.55</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>43.71</v>
+        <v>33.3</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>43.71</v>
+        <v>33.3</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1504</v>
+        <v>1477</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>18.1</v>
+        <v>7.8</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>8.94</v>
+        <v>19.04</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>16.66</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>2</v>
@@ -1534,51 +1534,51 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>27.34</v>
+        <v>10.92</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.95</v>
+        <v>-41.76</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-70.59999999999999</v>
+        <v>52.68</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>22.93</v>
+        <v>21.07</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>29.72</v>
+        <v>28.68</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>29.72</v>
+        <v>28.68</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>10.44</v>
+        <v>3.59</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>12.48</v>
+        <v>14</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>6.79</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8423</v>
+        <v>858</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1588,64 +1588,64 @@
         <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>73.98</v>
+        <v>148.67</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-24.99</v>
+        <v>70.11</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>98.97</v>
+        <v>78.56</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>28.04</v>
+        <v>55.1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>57.57</v>
+        <v>78.39</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>57.57</v>
+        <v>78.39</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1535</v>
+        <v>1577</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>29.46</v>
+        <v>39.84</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>15.12</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>3</v>
@@ -1654,51 +1654,51 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>77.45999999999999</v>
+        <v>24.89</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>39.17</v>
+        <v>66.17</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>38.28</v>
+        <v>-41.28</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>38.55</v>
+        <v>27.21</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>31.92</v>
+        <v>40.7</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>31.92</v>
+        <v>40.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1474</v>
+        <v>1496</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>5.76</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>16.91</v>
+        <v>23.05</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>6.88</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>9638</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1708,57 +1708,57 @@
         <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>18.79</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>55.06</v>
+        <v>66.91</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-45.6</v>
+        <v>-48.12</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>27.21</v>
+        <v>22.93</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34.57</v>
+        <v>27.28</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>34.57</v>
+        <v>27.28</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1481</v>
+        <v>1460</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>3.88</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>22.6</v>
+        <v>11.58</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>8.08</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1768,57 +1768,57 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-34.32</v>
+        <v>-4.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-20.18</v>
+        <v>114.64</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-14.14</v>
+        <v>-118.74</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.7</v>
+        <v>23.74</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>24.08</v>
+        <v>18.85</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>24.08</v>
+        <v>18.85</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1449</v>
+        <v>1429</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8.94</v>
+        <v>5.46</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>14.25</v>
+        <v>9.84</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.89</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9206</v>
+        <v>5256</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1828,64 +1828,64 @@
         <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10.98</v>
+        <v>23.05</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-39.63</v>
+        <v>6.73</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>50.62</v>
+        <v>16.32</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>21.07</v>
+        <v>35.18</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>27.3</v>
+        <v>26.66</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>27.3</v>
+        <v>26.66</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>3.92</v>
+        <v>6.39</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>11.87</v>
+        <v>15.52</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>11.51</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>4325</v>
+        <v>6081</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4</v>
@@ -1894,58 +1894,58 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>57.27</v>
+        <v>57.34</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>160.05</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-102.78</v>
+        <v>-27.06</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>32.52</v>
+        <v>59.73</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>38.66</v>
+        <v>58.22</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>38.66</v>
+        <v>58.22</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1491</v>
+        <v>1535</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>10.67</v>
+        <v>17.47</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>20.94</v>
+        <v>20.02</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.05</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5256</v>
+        <v>9685</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>3</v>
@@ -1954,178 +1954,178 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11.51</v>
+        <v>35.76</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12.02</v>
+        <v>-11.29</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-0.52</v>
+        <v>47.06</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>35.18</v>
+        <v>27.75</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>26.68</v>
+        <v>41.65</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>26.68</v>
+        <v>41.65</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1458</v>
+        <v>1498</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.63</v>
+        <v>18.71</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>15.76</v>
+        <v>6.78</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>5.28</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-2.07</v>
+        <v>-0.03</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>58.53</v>
+        <v>60.93</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-60.6</v>
+        <v>-60.95</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.6</v>
+        <v>25.63</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>26.39</v>
+        <v>20.76</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>26.39</v>
+        <v>20.76</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>6.97</v>
+        <v>6.64</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>14.54</v>
+        <v>7.02</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>4.87</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9756</v>
+        <v>7221</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>47.45</v>
+        <v>11.64</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>58.42</v>
+        <v>58.56</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-10.97</v>
+        <v>-46.93</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>29.21</v>
+        <v>8.82</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45.94</v>
+        <v>23.4</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>45.94</v>
+        <v>23.4</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1509</v>
+        <v>1446</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>6.44</v>
+        <v>6.31</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>25.74</v>
+        <v>10.22</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>13.76</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>3</v>
@@ -2134,51 +2134,51 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.95</v>
+        <v>-24.59</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>-15.71</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-81.56</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>25.63</v>
+        <v>21.7</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>17.37</v>
+        <v>24.36</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>17.37</v>
+        <v>24.36</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1423</v>
+        <v>1450</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.62</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>6.12</v>
+        <v>13.9</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>5.63</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>11399</v>
+        <v>4325</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2188,117 +2188,117 @@
         <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-11.75</v>
+        <v>50.45</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>142.98</v>
+        <v>172.75</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-154.73</v>
+        <v>-122.3</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>23.74</v>
+        <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17.82</v>
+        <v>39.03</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>17.82</v>
+        <v>39.03</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1425</v>
+        <v>1492</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>4.98</v>
+        <v>12.08</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>11.07</v>
+        <v>20.4</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>1.77</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.89</v>
+        <v>-0.39</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>67.16</v>
+        <v>81.28</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-64.27</v>
+        <v>-81.67</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.82</v>
+        <v>22.62</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>19.32</v>
+        <v>14.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.32</v>
+        <v>14.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1431</v>
+        <v>1410</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>7.01</v>
+        <v>4.71</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>6.29</v>
+        <v>8.42</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>6.02</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2317,48 +2317,48 @@
         <v>10</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>65.56</v>
+        <v>61.69</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>78.61</v>
+        <v>63.83</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-13.05</v>
+        <v>-2.15</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>59.73</v>
+        <v>29.21</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>55.89</v>
+        <v>46.22</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>55.89</v>
+        <v>46.22</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1531</v>
+        <v>1509</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>15.52</v>
+        <v>6.54</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>20.48</v>
+        <v>25.4</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>19.89</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3234</v>
+        <v>9549</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2368,43 +2368,43 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.51</v>
+        <v>-15.62</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>62.11</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-64.64</v>
+        <v>-77.73</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>22.62</v>
+        <v>17.6</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>17.07</v>
+        <v>19.8</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>17.07</v>
+        <v>19.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>3.88</v>
+        <v>8.09</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.84</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="32">
@@ -2425,60 +2425,60 @@
         <v>31</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.78</v>
+        <v>30.86</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>96.58</v>
+        <v>76.47</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-79.81</v>
+        <v>-45.61</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>23.43</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>18.51</v>
+        <v>16.53</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>18.51</v>
+        <v>16.53</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>7.54</v>
+        <v>6.32</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>6.39</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2488,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -2497,34 +2497,34 @@
         <v>6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.08</v>
+        <v>33.68</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>66.56</v>
+        <v>145.56</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-63.48</v>
+        <v>-111.88</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>27.91</v>
+        <v>23.83</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-0.19</v>
+        <v>32.97</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>-0.19</v>
+        <v>32.97</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1333</v>
+        <v>1476</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.24</v>
+        <v>4.71</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>-4.81</v>
+        <v>13.29</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-0.62</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="34">
@@ -2548,43 +2548,43 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-31.69</v>
+        <v>-21.93</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>191.23</v>
+        <v>191.64</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-222.92</v>
+        <v>-213.58</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>25.23</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10.79</v>
+        <v>13.74</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>10.79</v>
+        <v>13.74</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1393</v>
+        <v>1407</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>4.19</v>
+        <v>5.45</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>0.83</v>
+        <v>1.99</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>5.77</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="35">
@@ -2617,13 +2617,13 @@
         <v>6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-3.99</v>
+        <v>-14.94</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-84.09</v>
+        <v>-97.13</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>32.45</v>
@@ -2649,16 +2649,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9566</v>
+        <v>904</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2674,118 +2674,118 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>115.52</v>
+        <v>75.06</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-98.06999999999999</v>
+        <v>-66.75</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>39.97</v>
+        <v>27.91</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>20.27</v>
+        <v>0.09</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>20.27</v>
+        <v>0.09</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1435</v>
+        <v>1333</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>7.72</v>
+        <v>-5.16</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7809</v>
+        <v>7658</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
         <v>36</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>25.55</v>
+        <v>-12.72</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>178.62</v>
+        <v>48.41</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-153.07</v>
+        <v>-61.13</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>23.83</v>
+        <v>14.34</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>34.68</v>
+        <v>7.33</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>34.68</v>
+        <v>7.33</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1481</v>
+        <v>1375</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>5.1</v>
+        <v>3.99</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>14.07</v>
+        <v>5.32</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>15.51</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7658</v>
+        <v>9566</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>5</v>
@@ -2794,58 +2794,58 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-4.98</v>
+        <v>18.11</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>64.93000000000001</v>
+        <v>120.13</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-69.92</v>
+        <v>-102.02</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>14.34</v>
+        <v>39.97</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7.43</v>
+        <v>20.27</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>7.43</v>
+        <v>20.27</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1376</v>
+        <v>1435</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>2.86</v>
+        <v>3.43</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>6.68</v>
+        <v>7.72</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-2.11</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>38</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>5</v>
@@ -2854,51 +2854,51 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>9.91</v>
+        <v>18.94</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>26.62</v>
+        <v>104.16</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-16.71</v>
+        <v>-85.22</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>27.39</v>
+        <v>39.07</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>3.76</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>12.82</v>
+        <v>10.09</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>4.04</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2908,43 +2908,43 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.1</v>
+        <v>3.87</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>101.15</v>
+        <v>17.91</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-84.05</v>
+        <v>-14.05</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>39.07</v>
+        <v>27.39</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22.72</v>
+        <v>29.46</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>22.72</v>
+        <v>29.46</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1444</v>
+        <v>1466</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>3.61</v>
+        <v>10.91</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>12.17</v>
+        <v>13.98</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>6.94</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="41">
@@ -3108,146 +3108,146 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>126.18</v>
+        <v>128.5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>126.18</v>
+        <v>128.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>25.21</v>
+        <v>27.16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>69.73</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>31.24</v>
+        <v>32.08</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1023</v>
+        <v>10633</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>68.08</v>
+        <v>45.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>124.83</v>
+        <v>123.2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>124.83</v>
+        <v>123.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.41</v>
+        <v>21.49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>73.97</v>
+        <v>68.55</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>29.45</v>
+        <v>33.16</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>10633</v>
+        <v>1023</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.8</v>
+        <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>122.17</v>
+        <v>120.67</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>122.17</v>
+        <v>120.67</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21.02</v>
+        <v>23.32</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>69.78</v>
+        <v>70.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>31.38</v>
+        <v>26.69</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1657</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>7220</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>115.05</v>
+        <v>120.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>115.05</v>
+        <v>120.09</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>25.89</v>
+        <v>27.43</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>63.31</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25.85</v>
+        <v>21.23</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1648</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45.04</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>113.57</v>
+        <v>115.51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>113.57</v>
+        <v>115.51</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27.31</v>
+        <v>25.75</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>63.95</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.66</v>
+        <v>25.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="7">
@@ -3294,22 +3294,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>97.73999999999999</v>
+        <v>95.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>97.73999999999999</v>
+        <v>95.72</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>16.72</v>
+        <v>16.87</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.29</v>
+        <v>57.21</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>21.74</v>
+        <v>21.63</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1617</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="9">
@@ -3376,64 +3376,64 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>70.34</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>70.34</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>10.16</v>
+        <v>7.81</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>37.01</v>
+        <v>51.37</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>23.16</v>
+        <v>21.13</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1561</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2771</v>
+        <v>858</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>53.52</v>
+        <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>70.09</v>
+        <v>78.39</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>70.09</v>
+        <v>78.39</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.99</v>
+        <v>12.83</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44.97</v>
+        <v>39.84</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>16.13</v>
+        <v>25.72</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1561</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="13">
@@ -3449,50 +3449,50 @@
         <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>58.95</v>
+        <v>59.41</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>58.95</v>
+        <v>59.41</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>16.68</v>
+        <v>16.54</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>31.41</v>
+        <v>32.05</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28.04</v>
+        <v>59.73</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>57.57</v>
+        <v>58.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>57.57</v>
+        <v>58.22</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13</v>
+        <v>17.47</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>29.46</v>
+        <v>20.02</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.12</v>
+        <v>20.73</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1535</v>
@@ -3500,33 +3500,33 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>6081</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>59.73</v>
+        <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>55.89</v>
+        <v>55.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>55.89</v>
+        <v>55.87</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>15.52</v>
+        <v>12.62</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>20.48</v>
+        <v>28.68</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>19.89</v>
+        <v>14.57</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="16">
@@ -3542,19 +3542,19 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45.94</v>
+        <v>46.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45.94</v>
+        <v>46.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6.44</v>
+        <v>6.54</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>25.74</v>
+        <v>25.4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.76</v>
+        <v>14.29</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>1509</v>
@@ -3573,53 +3573,53 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>43.71</v>
+        <v>41.65</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>43.71</v>
+        <v>41.65</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>18.1</v>
+        <v>18.71</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.94</v>
+        <v>6.78</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.66</v>
+        <v>16.15</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1504</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7808</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.37</v>
+        <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>39.89</v>
+        <v>40.7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>39.89</v>
+        <v>40.7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.37</v>
+        <v>5.76</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>22.68</v>
+        <v>23.05</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.84</v>
+        <v>11.89</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="19">
@@ -3635,146 +3635,146 @@
         <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38.66</v>
+        <v>39.03</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>38.66</v>
+        <v>39.03</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.67</v>
+        <v>12.08</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.94</v>
+        <v>20.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>7.05</v>
+        <v>6.56</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>7808</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>23.83</v>
+        <v>24.37</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.68</v>
+        <v>37.87</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34.68</v>
+        <v>37.87</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.1</v>
+        <v>5.52</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14.07</v>
+        <v>20.61</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>15.51</v>
+        <v>11.74</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>27.21</v>
+        <v>38.55</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>34.57</v>
+        <v>33.3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>34.57</v>
+        <v>33.3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3.88</v>
+        <v>7.8</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>22.6</v>
+        <v>19.04</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>8.08</v>
+        <v>6.46</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7289</v>
+        <v>7809</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>33.29</v>
+        <v>23.83</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32.42</v>
+        <v>32.97</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.42</v>
+        <v>32.97</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>13.7</v>
+        <v>4.71</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.68</v>
+        <v>13.29</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>11.04</v>
+        <v>14.96</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5980</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>38.55</v>
+        <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.92</v>
+        <v>32.8</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>31.92</v>
+        <v>32.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>14.36</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16.91</v>
+        <v>7.39</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.88</v>
+        <v>11.06</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="24">
@@ -3810,33 +3810,33 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>22.93</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>29.72</v>
+        <v>29.46</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>29.72</v>
+        <v>29.46</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10.44</v>
+        <v>10.91</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12.48</v>
+        <v>13.98</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>6.79</v>
+        <v>4.57</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="26">
@@ -3852,363 +3852,363 @@
         <v>21.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>27.3</v>
+        <v>28.68</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>27.3</v>
+        <v>28.68</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>3.92</v>
+        <v>3.59</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.87</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>11.51</v>
+        <v>11.1</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>5256</v>
+        <v>9638</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.18</v>
+        <v>22.93</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>26.68</v>
+        <v>27.28</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>26.68</v>
+        <v>27.28</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.63</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>15.76</v>
+        <v>11.58</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.28</v>
+        <v>6.08</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1458</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9671</v>
+        <v>5256</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>27.39</v>
+        <v>35.18</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>26.5</v>
+        <v>26.66</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.5</v>
+        <v>26.66</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>6.39</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>12.82</v>
+        <v>15.52</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4.04</v>
+        <v>4.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>9549</v>
+        <v>10664</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>17.6</v>
+        <v>21.7</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>26.39</v>
+        <v>24.36</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>26.39</v>
+        <v>24.36</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.97</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.54</v>
+        <v>13.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.87</v>
+        <v>1.42</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1457</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>10664</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>21.7</v>
+        <v>8.82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>24.08</v>
+        <v>23.4</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>24.08</v>
+        <v>23.4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>8.94</v>
+        <v>6.31</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>14.25</v>
+        <v>10.22</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.89</v>
+        <v>6.87</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8285</v>
+        <v>10642</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>39.07</v>
+        <v>25.63</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.72</v>
+        <v>20.76</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22.72</v>
+        <v>20.76</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.61</v>
+        <v>6.64</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12.17</v>
+        <v>7.02</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1444</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.97</v>
+        <v>39.07</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.27</v>
+        <v>20.7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.27</v>
+        <v>20.7</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3.43</v>
+        <v>3.76</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.72</v>
+        <v>10.09</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7221</v>
+        <v>9566</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>8.82</v>
+        <v>39.97</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.32</v>
+        <v>20.27</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.32</v>
+        <v>20.27</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.01</v>
+        <v>3.43</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.29</v>
+        <v>7.72</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>6.02</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1431</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>17.6</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.51</v>
+        <v>19.8</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.51</v>
+        <v>19.8</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.57</v>
+        <v>8.09</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.54</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.39</v>
+        <v>2.1</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1428</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>32.45</v>
+        <v>23.74</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>17.96</v>
+        <v>18.85</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.96</v>
+        <v>18.85</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5.95</v>
+        <v>5.46</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4.48</v>
+        <v>9.84</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>7.53</v>
+        <v>3.55</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1426</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>11399</v>
+        <v>7818</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.74</v>
+        <v>32.45</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.82</v>
+        <v>17.96</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.82</v>
+        <v>17.96</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.98</v>
+        <v>5.95</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.07</v>
+        <v>4.48</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.77</v>
+        <v>7.53</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.63</v>
+        <v>23.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>17.37</v>
+        <v>16.53</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>17.37</v>
+        <v>16.53</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.62</v>
+        <v>4.38</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6.12</v>
+        <v>6.32</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>5.63</v>
+        <v>5.83</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="38">
@@ -4224,22 +4224,22 @@
         <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.07</v>
+        <v>14.3</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.07</v>
+        <v>14.3</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>3.88</v>
+        <v>4.71</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9.35</v>
+        <v>8.42</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.84</v>
+        <v>1.18</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1422</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="39">
@@ -4255,22 +4255,22 @@
         <v>25.23</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>10.79</v>
+        <v>13.74</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10.79</v>
+        <v>13.74</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.19</v>
+        <v>5.45</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.83</v>
+        <v>1.99</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>5.77</v>
+        <v>6.31</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1393</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="40">
@@ -4286,22 +4286,22 @@
         <v>14.34</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7.43</v>
+        <v>7.33</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>7.43</v>
+        <v>7.33</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2.86</v>
+        <v>3.99</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6.68</v>
+        <v>5.32</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-2.11</v>
+        <v>-1.98</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="41">
@@ -4317,19 +4317,19 @@
         <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.09</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-4.81</v>
+        <v>-5.16</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.09</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>1333</v>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>212.62</v>
+        <v>201.9</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-15.86</v>
+        <v>-10.48</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>228.49</v>
+        <v>212.39</v>
       </c>
     </row>
     <row r="3">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>176.96</v>
+        <v>180.95</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>52.41</v>
+        <v>49.45</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>124.55</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="4">
@@ -4431,108 +4431,108 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>160.41</v>
+        <v>153.01</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>78.5</v>
+        <v>93.13</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>81.91</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4967</v>
+        <v>858</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>150.58</v>
+        <v>148.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-23.63</v>
+        <v>70.11</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>174.21</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>7220</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>142.25</v>
+        <v>146.6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>28.04</v>
+        <v>101.47</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>114.21</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>132.21</v>
+        <v>142.13</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>48.32</v>
+        <v>-10.34</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>83.89</v>
+        <v>152.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7220</v>
+        <v>1023</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>125.36</v>
+        <v>131.85</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>101.91</v>
+        <v>41.71</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>23.46</v>
+        <v>90.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5166</v>
+        <v>2771</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>116.97</v>
+        <v>106.59</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13</v>
+        <v>30.01</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>103.97</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="10">
@@ -4545,32 +4545,32 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>102.42</v>
+        <v>103.4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35.78</v>
+        <v>39.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>66.64</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>100.52</v>
+        <v>102.15</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>34.01</v>
+        <v>16.44</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>66.52</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4583,13 +4583,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>98.48</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>82.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="13">
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>77.45999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>39.17</v>
+        <v>37.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>38.28</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="14">
@@ -4621,32 +4621,32 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>73.98</v>
+        <v>64.48</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-24.99</v>
+        <v>-53.04</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>98.97</v>
+        <v>117.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>65.56</v>
+        <v>61.69</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>78.61</v>
+        <v>63.83</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-13.05</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="16">
@@ -4659,32 +4659,32 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>63.37</v>
+        <v>58.84</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>22.67</v>
+        <v>25.68</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40.7</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>6081</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>58</v>
+        <v>57.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-13.94</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>71.94</v>
+        <v>-27.06</v>
       </c>
     </row>
     <row r="18">
@@ -4697,336 +4697,336 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>57.27</v>
+        <v>50.45</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>160.05</v>
+        <v>172.75</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-102.78</v>
+        <v>-122.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>47.45</v>
+        <v>35.76</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>58.42</v>
+        <v>-11.29</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-10.97</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9638</v>
+        <v>7809</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.34</v>
+        <v>33.68</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>97.95</v>
+        <v>145.56</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-70.59999999999999</v>
+        <v>-111.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>25.55</v>
+        <v>30.86</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>178.62</v>
+        <v>76.47</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-153.07</v>
+        <v>-45.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9566</v>
+        <v>8767</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>17.45</v>
+        <v>24.89</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>115.52</v>
+        <v>66.17</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-98.06999999999999</v>
+        <v>-41.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17.1</v>
+        <v>23.05</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>101.15</v>
+        <v>6.73</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-84.05</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>10181</v>
+        <v>9208</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>16.78</v>
+        <v>20.96</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>96.58</v>
+        <v>-1.01</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-79.81</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>5256</v>
+        <v>8285</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>11.51</v>
+        <v>18.94</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>12.02</v>
+        <v>104.16</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.52</v>
+        <v>-85.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9206</v>
+        <v>9638</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10.98</v>
+        <v>18.79</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-39.63</v>
+        <v>66.91</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>50.62</v>
+        <v>-48.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9208</v>
+        <v>9566</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>10.97</v>
+        <v>18.11</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.91</v>
+        <v>120.13</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>16.88</v>
+        <v>-102.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3234</v>
+        <v>7808</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10.51</v>
+        <v>12.31</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>75.15000000000001</v>
+        <v>-56.08</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-64.64</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7808</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.17</v>
+        <v>11.64</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-47.3</v>
+        <v>58.56</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>57.47</v>
+        <v>-46.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9.91</v>
+        <v>10.92</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>26.62</v>
+        <v>-41.76</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-16.71</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>8767</v>
+        <v>904</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>55.06</v>
+        <v>75.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-45.6</v>
+        <v>-66.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>904</v>
+        <v>9671</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3.08</v>
+        <v>3.87</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>66.56</v>
+        <v>17.91</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-63.48</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7221</v>
+        <v>10642</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2.89</v>
+        <v>-0.03</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>67.16</v>
+        <v>60.93</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-64.27</v>
+        <v>-60.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-2.07</v>
+        <v>-0.39</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>58.53</v>
+        <v>81.28</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-60.6</v>
+        <v>-81.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-3.99</v>
+        <v>-4.1</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>114.64</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-84.09</v>
+        <v>-118.74</v>
       </c>
     </row>
     <row r="36">
@@ -5039,51 +5039,51 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-4.98</v>
+        <v>-12.72</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>64.93000000000001</v>
+        <v>48.41</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-69.92</v>
+        <v>-61.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-10.95</v>
+        <v>-14.94</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-81.56</v>
+        <v>-97.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>11399</v>
+        <v>9549</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-11.75</v>
+        <v>-15.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>142.98</v>
+        <v>62.11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-154.73</v>
+        <v>-77.73</v>
       </c>
     </row>
     <row r="39">
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-31.69</v>
+        <v>-21.93</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>191.23</v>
+        <v>191.64</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-222.92</v>
+        <v>-213.58</v>
       </c>
     </row>
     <row r="40">
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-34.32</v>
+        <v>-24.59</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-20.18</v>
+        <v>-15.71</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-14.14</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -5314,24 +5314,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -5339,24 +5339,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2771</v>
+        <v>2075</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -5364,11 +5364,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>4967</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -5389,11 +5389,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4967</v>
+        <v>10633</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -5439,24 +5439,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7289</v>
+        <v>1023</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -5464,15 +5464,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10633</v>
+        <v>5166</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -5514,15 +5514,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5166</v>
+        <v>7289</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -5539,15 +5539,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>858</v>
+        <v>8423</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>2</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -5564,18 +5564,18 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -5589,15 +5589,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>2</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -5614,24 +5614,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8423</v>
+        <v>858</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -5639,15 +5639,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>3</v>
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -5664,24 +5664,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8767</v>
+        <v>9638</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -5689,24 +5689,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10664</v>
+        <v>11399</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -5714,24 +5714,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9206</v>
+        <v>5256</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -5739,15 +5739,15 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4325</v>
+        <v>6081</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -5764,15 +5764,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5256</v>
+        <v>9685</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>3</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -5789,24 +5789,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -5814,24 +5814,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9756</v>
+        <v>7221</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -5839,15 +5839,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>3</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -5864,24 +5864,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>11399</v>
+        <v>4325</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7221</v>
+        <v>3234</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -5914,11 +5914,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5939,24 +5939,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3234</v>
+        <v>9549</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -5972,16 +5972,16 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -5989,18 +5989,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
@@ -6025,13 +6025,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -6064,11 +6064,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>9566</v>
+        <v>904</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -6089,24 +6089,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7809</v>
+        <v>7658</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -6114,15 +6114,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7658</v>
+        <v>9566</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>5</v>
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -6139,15 +6139,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>5</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -6164,24 +6164,24 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>212.62</v>
+        <v>201.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-15.86</v>
+        <v>-10.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>228.49</v>
+        <v>212.39</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>176.96</v>
+        <v>180.95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>52.41</v>
+        <v>49.45</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>124.55</v>
+        <v>131.5</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6338,13 +6338,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>160.41</v>
+        <v>153.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>78.5</v>
+        <v>93.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>81.91</v>
+        <v>59.88</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6353,21 +6353,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4967</v>
+        <v>858</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>150.58</v>
+        <v>148.67</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-23.63</v>
+        <v>70.11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>174.21</v>
+        <v>78.56</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1023</v>
+        <v>7220</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>142.25</v>
+        <v>146.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.04</v>
+        <v>101.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>114.21</v>
+        <v>45.14</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6399,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>858</v>
+        <v>4967</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>132.21</v>
+        <v>142.13</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48.32</v>
+        <v>-10.34</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>83.89</v>
+        <v>152.47</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6422,21 +6422,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7220</v>
+        <v>1023</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>125.36</v>
+        <v>131.85</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>101.91</v>
+        <v>41.71</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>23.46</v>
+        <v>90.14</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5166</v>
+        <v>2771</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>116.97</v>
+        <v>106.59</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>13</v>
+        <v>30.01</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>103.97</v>
+        <v>76.58</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>102.42</v>
+        <v>103.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35.78</v>
+        <v>39.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>66.64</v>
+        <v>63.63</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>100.52</v>
+        <v>102.15</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>34.01</v>
+        <v>16.44</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>66.52</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>98.48</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>82.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>27.59</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>77.45999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>39.17</v>
+        <v>37.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>38.28</v>
+        <v>41.19</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6568,13 +6568,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>73.98</v>
+        <v>64.48</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-24.99</v>
+        <v>-53.04</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>98.97</v>
+        <v>117.52</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>65.56</v>
+        <v>61.69</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>78.61</v>
+        <v>63.83</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-13.05</v>
+        <v>-2.15</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>63.37</v>
+        <v>58.84</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22.67</v>
+        <v>25.68</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>40.7</v>
+        <v>33.16</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6629,21 +6629,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9685</v>
+        <v>6081</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>58</v>
+        <v>57.34</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-13.94</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>71.94</v>
+        <v>-27.06</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6660,13 +6660,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>57.27</v>
+        <v>50.45</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>160.05</v>
+        <v>172.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-102.78</v>
+        <v>-122.3</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6675,21 +6675,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9756</v>
+        <v>9685</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>47.45</v>
+        <v>35.76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>58.42</v>
+        <v>-11.29</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-10.97</v>
+        <v>47.06</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9638</v>
+        <v>7809</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>27.34</v>
+        <v>33.68</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>97.95</v>
+        <v>145.56</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-70.59999999999999</v>
+        <v>-111.88</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>25.55</v>
+        <v>30.86</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>178.62</v>
+        <v>76.47</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-153.07</v>
+        <v>-45.61</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9566</v>
+        <v>8767</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>17.45</v>
+        <v>24.89</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>115.52</v>
+        <v>66.17</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-98.06999999999999</v>
+        <v>-41.28</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>8285</v>
+        <v>5256</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>17.1</v>
+        <v>23.05</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>101.15</v>
+        <v>6.73</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-84.05</v>
+        <v>16.32</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10181</v>
+        <v>9208</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>16.78</v>
+        <v>20.96</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>96.58</v>
+        <v>-1.01</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-79.81</v>
+        <v>21.96</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5256</v>
+        <v>8285</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>11.51</v>
+        <v>18.94</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>12.02</v>
+        <v>104.16</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.52</v>
+        <v>-85.22</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9206</v>
+        <v>9638</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10.98</v>
+        <v>18.79</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-39.63</v>
+        <v>66.91</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>50.62</v>
+        <v>-48.12</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9208</v>
+        <v>9566</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10.97</v>
+        <v>18.11</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.91</v>
+        <v>120.13</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>16.88</v>
+        <v>-102.02</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3234</v>
+        <v>7808</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10.51</v>
+        <v>12.31</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>75.15000000000001</v>
+        <v>-56.08</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-64.64</v>
+        <v>68.39</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7808</v>
+        <v>7221</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10.17</v>
+        <v>11.64</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-47.3</v>
+        <v>58.56</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>57.47</v>
+        <v>-46.93</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9.91</v>
+        <v>10.92</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>26.62</v>
+        <v>-41.76</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-16.71</v>
+        <v>52.68</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>8767</v>
+        <v>904</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>55.06</v>
+        <v>75.06</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-45.6</v>
+        <v>-66.75</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>904</v>
+        <v>9671</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3.08</v>
+        <v>3.87</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>66.56</v>
+        <v>17.91</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-63.48</v>
+        <v>-14.05</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7221</v>
+        <v>10642</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.89</v>
+        <v>-0.03</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>67.16</v>
+        <v>60.93</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-64.27</v>
+        <v>-60.95</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9549</v>
+        <v>3234</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-2.07</v>
+        <v>-0.39</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>58.53</v>
+        <v>81.28</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-60.6</v>
+        <v>-81.67</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7818</v>
+        <v>11399</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-3.99</v>
+        <v>-4.1</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>114.64</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-84.09</v>
+        <v>-118.74</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7074,13 +7074,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-4.98</v>
+        <v>-12.72</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>64.93000000000001</v>
+        <v>48.41</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-69.92</v>
+        <v>-61.13</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-10.95</v>
+        <v>-14.94</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-81.56</v>
+        <v>-97.13</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>11399</v>
+        <v>9549</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-11.75</v>
+        <v>-15.62</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>142.98</v>
+        <v>62.11</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-154.73</v>
+        <v>-77.73</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-31.69</v>
+        <v>-21.93</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>191.23</v>
+        <v>191.64</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-222.92</v>
+        <v>-213.58</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-34.32</v>
+        <v>-24.59</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-20.18</v>
+        <v>-15.71</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-14.14</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -637,13 +637,13 @@
         <v>29</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>201.9</v>
+        <v>202.64</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-10.48</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>212.39</v>
+        <v>211.43</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
@@ -697,13 +697,13 @@
         <v>28</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>146.6</v>
+        <v>146.62</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>101.47</v>
+        <v>80.87</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>45.14</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
@@ -729,16 +729,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7656</v>
+        <v>4967</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -748,64 +748,64 @@
         <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>103.4</v>
+        <v>133.98</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39.76</v>
+        <v>16.87</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>63.63</v>
+        <v>117.12</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>50.91</v>
+        <v>68.89</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>88.72</v>
+        <v>112.5</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>88.72</v>
+        <v>112.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1599</v>
+        <v>1643</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>10.89</v>
+        <v>24.28</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>53.14</v>
+        <v>62.18</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>24.69</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>7808</v>
+        <v>7656</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -814,51 +814,51 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>12.31</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-56.08</v>
+        <v>17.32</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>68.39</v>
+        <v>71.72</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24.37</v>
+        <v>50.91</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>37.87</v>
+        <v>81.06</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>37.87</v>
+        <v>81.06</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1489</v>
+        <v>1582</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>5.52</v>
+        <v>9.68</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>20.61</v>
+        <v>48.63</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>11.74</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -868,64 +868,64 @@
         <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>106.59</v>
+        <v>115.06</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30.01</v>
+        <v>3.46</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>76.58</v>
+        <v>111.6</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>53.52</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>80.31999999999999</v>
+        <v>109.88</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>80.31999999999999</v>
+        <v>109.88</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1581</v>
+        <v>1639</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>7.81</v>
+        <v>20.41</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>51.37</v>
+        <v>65.11</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>21.13</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>2</v>
@@ -934,58 +934,58 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>98.48</v>
+        <v>194.35</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>6.46</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>27.59</v>
+        <v>187.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>115.51</v>
+        <v>137.46</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>115.51</v>
+        <v>137.46</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1648</v>
+        <v>1676</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>25.75</v>
+        <v>26.22</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>63.95</v>
+        <v>76.59</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.81</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4967</v>
+        <v>2075</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
@@ -994,58 +994,58 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>142.13</v>
+        <v>100.21</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-10.34</v>
+        <v>63.13</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>152.47</v>
+        <v>37.08</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>68.89</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>105.05</v>
+        <v>116.95</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>105.05</v>
+        <v>116.95</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1632</v>
+        <v>1649</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>24.29</v>
+        <v>24.31</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>55.97</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.79</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>2</v>
@@ -1054,178 +1054,178 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>180.95</v>
+        <v>139.06</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>49.45</v>
+        <v>29.74</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>131.5</v>
+        <v>109.32</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>45.8</v>
+        <v>50.66</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>123.2</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>123.2</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1659</v>
+        <v>1592</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.49</v>
+        <v>10.23</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>68.55</v>
+        <v>51.87</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>33.16</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3875</v>
+        <v>1023</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>153.01</v>
+        <v>128.47</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>93.13</v>
+        <v>52.69</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>59.88</v>
+        <v>75.78</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>50.66</v>
+        <v>68.08</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>87.52</v>
+        <v>120.13</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>87.52</v>
+        <v>120.13</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1596</v>
+        <v>1653</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>10.56</v>
+        <v>22.95</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>51.15</v>
+        <v>70.84</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>25.8</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>131.85</v>
+        <v>103.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>41.71</v>
+        <v>57.65</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>90.14</v>
+        <v>46.25</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>68.08</v>
+        <v>53.52</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>120.67</v>
+        <v>75.88</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>120.67</v>
+        <v>75.88</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1654</v>
+        <v>1571</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>23.32</v>
+        <v>6.92</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>70.67</v>
+        <v>47.11</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>26.69</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5166</v>
+        <v>7808</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>2</v>
@@ -1234,58 +1234,58 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>102.15</v>
+        <v>12.86</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16.44</v>
+        <v>3.55</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>85.70999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>24.37</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>95.72</v>
+        <v>33.43</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>95.72</v>
+        <v>33.43</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1612</v>
+        <v>1477</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>16.87</v>
+        <v>4.63</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>57.21</v>
+        <v>16.35</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>21.63</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9208</v>
+        <v>7289</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Edwardsburg, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2</v>
@@ -1294,51 +1294,51 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>20.96</v>
+        <v>53.58</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-1.01</v>
+        <v>-2.71</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>21.96</v>
+        <v>56.29</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>44.43</v>
+        <v>33.29</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>59.41</v>
+        <v>34.23</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>59.41</v>
+        <v>34.23</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1538</v>
+        <v>1479</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>16.54</v>
+        <v>12.91</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>32.05</v>
+        <v>9.4</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>10.81</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7289</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1354,157 +1354,157 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>58.84</v>
+        <v>60.63</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25.68</v>
+        <v>-17.16</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33.16</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>33.29</v>
+        <v>28.04</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>32.8</v>
+        <v>56.76</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>32.8</v>
+        <v>56.76</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1476</v>
+        <v>1532</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>14.36</v>
+        <v>11.18</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>7.39</v>
+        <v>31.44</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>11.06</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Edwardsburg, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>64.48</v>
+        <v>27.37</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-53.04</v>
+        <v>36.94</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>117.52</v>
+        <v>-9.58</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>28.04</v>
+        <v>44.43</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>55.87</v>
+        <v>59.01</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>55.87</v>
+        <v>59.01</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>12.62</v>
+        <v>15.49</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>28.68</v>
+        <v>30.97</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>14.57</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5980</v>
+        <v>858</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>78.39</v>
+        <v>145.77</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>37.2</v>
+        <v>77.73</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>41.19</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>38.55</v>
+        <v>55.1</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>33.3</v>
+        <v>84.95</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>33.3</v>
+        <v>84.95</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1477</v>
+        <v>1590</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>7.8</v>
+        <v>14.25</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>19.04</v>
+        <v>43.29</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>6.46</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="17">
@@ -1525,70 +1525,70 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>10.92</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-41.76</v>
+        <v>33.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>52.68</v>
+        <v>-13.96</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>21.07</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>28.68</v>
+        <v>29.18</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>28.68</v>
+        <v>29.18</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.59</v>
+        <v>1.1</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>14</v>
+        <v>15.67</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>858</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -1597,48 +1597,48 @@
         <v>16</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>148.67</v>
+        <v>22.88</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>70.11</v>
+        <v>73.05</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>78.56</v>
+        <v>-50.17</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>55.1</v>
+        <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>78.39</v>
+        <v>40.7</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>78.39</v>
+        <v>40.7</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1577</v>
+        <v>1496</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>12.83</v>
+        <v>5.76</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>39.84</v>
+        <v>23.05</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>25.72</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>10642</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1648,57 +1648,57 @@
         <v>4</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>24.89</v>
+        <v>-3.79</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>66.17</v>
+        <v>26.38</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-41.28</v>
+        <v>-30.18</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.21</v>
+        <v>25.63</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>40.7</v>
+        <v>20.22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>40.7</v>
+        <v>20.22</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1496</v>
+        <v>1435</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>5.76</v>
+        <v>6.27</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.05</v>
+        <v>7.19</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11.89</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9638</v>
+        <v>6081</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1708,57 +1708,57 @@
         <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.79</v>
+        <v>58.35</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>66.91</v>
+        <v>77.06</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-48.12</v>
+        <v>-18.71</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>22.93</v>
+        <v>59.73</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27.28</v>
+        <v>58.22</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>27.28</v>
+        <v>58.22</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1460</v>
+        <v>1535</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>17.47</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>11.58</v>
+        <v>20.02</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>6.08</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>11399</v>
+        <v>9756</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Eau Claire, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1768,57 +1768,57 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-4.1</v>
+        <v>65.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>114.64</v>
+        <v>58.94</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-118.74</v>
+        <v>6.56</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>23.74</v>
+        <v>29.21</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.85</v>
+        <v>47.65</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.85</v>
+        <v>47.65</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1429</v>
+        <v>1512</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>5.46</v>
+        <v>5.09</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>9.84</v>
+        <v>27.41</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>3.55</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5256</v>
+        <v>5980</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1828,64 +1828,64 @@
         <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.05</v>
+        <v>73.37</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>16.32</v>
+        <v>66.66</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>35.18</v>
+        <v>38.55</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26.66</v>
+        <v>33.08</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>26.66</v>
+        <v>33.08</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1458</v>
+        <v>1476</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>6.39</v>
+        <v>7.21</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>15.52</v>
+        <v>20.33</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>4.76</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>6081</v>
+        <v>11399</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>Eau Claire, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>4</v>
@@ -1894,61 +1894,61 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>57.34</v>
+        <v>-11.76</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-27.06</v>
+        <v>-91.62</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>59.73</v>
+        <v>23.74</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>58.22</v>
+        <v>15.38</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>58.22</v>
+        <v>15.38</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1535</v>
+        <v>1414</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>17.47</v>
+        <v>4.46</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>20.02</v>
+        <v>8.44</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>20.73</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9685</v>
+        <v>10181</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -1957,55 +1957,55 @@
         <v>14</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>35.76</v>
+        <v>33.21</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-11.29</v>
+        <v>51.84</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>47.06</v>
+        <v>-18.63</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>27.75</v>
+        <v>23.43</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41.65</v>
+        <v>23.18</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>41.65</v>
+        <v>23.18</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>18.71</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>6.78</v>
+        <v>9.9</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>16.15</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>10642</v>
+        <v>9685</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>4</v>
@@ -2014,51 +2014,51 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0.03</v>
+        <v>39.94</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>60.93</v>
+        <v>10.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-60.95</v>
+        <v>29.24</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>25.63</v>
+        <v>27.75</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>20.76</v>
+        <v>40.56</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>20.76</v>
+        <v>40.56</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1437</v>
+        <v>1495</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>6.64</v>
+        <v>18.86</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>7.02</v>
+        <v>5.15</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>7.11</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7221</v>
+        <v>5256</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -2074,118 +2074,118 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.64</v>
+        <v>10.11</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>58.56</v>
+        <v>21.13</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-46.93</v>
+        <v>-11.01</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8.82</v>
+        <v>35.18</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23.4</v>
+        <v>19.01</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>23.4</v>
+        <v>19.01</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1446</v>
+        <v>1430</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>6.31</v>
+        <v>5.17</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>10.22</v>
+        <v>11.01</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>6.87</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10664</v>
+        <v>4325</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-24.59</v>
+        <v>58.68</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-15.71</v>
+        <v>196.18</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-137.5</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>21.7</v>
+        <v>32.52</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>24.36</v>
+        <v>38.63</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>24.36</v>
+        <v>38.63</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1450</v>
+        <v>1491</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>13.9</v>
+        <v>19.32</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.42</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4325</v>
+        <v>9638</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>5</v>
@@ -2194,51 +2194,51 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>50.45</v>
+        <v>25.51</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>172.75</v>
+        <v>62.41</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-122.3</v>
+        <v>-36.91</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>32.52</v>
+        <v>22.93</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>39.03</v>
+        <v>24.42</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>39.03</v>
+        <v>24.42</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1492</v>
+        <v>1450</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>12.08</v>
+        <v>7.99</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>20.4</v>
+        <v>10.93</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>6.56</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>3234</v>
+        <v>7221</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2248,57 +2248,57 @@
         <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.39</v>
+        <v>14.84</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>81.28</v>
+        <v>72.08</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-81.67</v>
+        <v>-57.23</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>22.62</v>
+        <v>8.82</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.3</v>
+        <v>22.31</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.3</v>
+        <v>22.31</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1410</v>
+        <v>1442</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.71</v>
+        <v>6.46</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.42</v>
+        <v>8.59</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.18</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9756</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2308,67 +2308,67 @@
         <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>61.69</v>
+        <v>-12.68</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>63.83</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-2.15</v>
+        <v>-78.86</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>29.21</v>
+        <v>17.6</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>46.22</v>
+        <v>19.8</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>46.22</v>
+        <v>19.8</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1509</v>
+        <v>1433</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>6.54</v>
+        <v>8.09</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>25.4</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>14.29</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9549</v>
+        <v>10664</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -2377,55 +2377,55 @@
         <v>11</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-15.62</v>
+        <v>-27.94</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>62.11</v>
+        <v>31.11</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-77.73</v>
+        <v>-59.05</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>17.6</v>
+        <v>21.7</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.8</v>
+        <v>19.92</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>19.8</v>
+        <v>19.92</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>1433</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8.09</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>5</v>
@@ -2434,58 +2434,58 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.86</v>
+        <v>1.49</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>76.47</v>
+        <v>80.02</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-45.61</v>
+        <v>-78.53</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>16.53</v>
+        <v>13.21</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>16.53</v>
+        <v>13.21</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1420</v>
+        <v>1404</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4.38</v>
+        <v>4.86</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>6.32</v>
+        <v>6.79</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>5.83</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>5</v>
@@ -2494,171 +2494,171 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>33.68</v>
+        <v>0.18</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>145.56</v>
+        <v>48.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-111.88</v>
+        <v>-48.11</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>23.83</v>
+        <v>27.91</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>32.97</v>
+        <v>-0.74</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>32.97</v>
+        <v>-0.74</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1476</v>
+        <v>1328</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.71</v>
+        <v>5.37</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>13.29</v>
+        <v>-4.61</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>14.96</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7256</v>
+        <v>7818</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-21.93</v>
+        <v>3.67</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>191.64</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-213.58</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>25.23</v>
+        <v>32.45</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>13.74</v>
+        <v>22.92</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>13.74</v>
+        <v>22.92</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1407</v>
+        <v>1445</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5.45</v>
+        <v>7.02</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>1.99</v>
+        <v>6.98</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>6.31</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-14.94</v>
+        <v>21.67</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>82.19</v>
+        <v>94.14</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-97.13</v>
+        <v>-72.45999999999999</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>32.45</v>
+        <v>39.97</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>17.96</v>
+        <v>25.52</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.96</v>
+        <v>25.52</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1426</v>
+        <v>1454</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5.95</v>
+        <v>5.39</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>4.48</v>
+        <v>11.49</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>7.53</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -2677,43 +2677,43 @@
         <v>6</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>30.51</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>75.06</v>
+        <v>158.88</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-66.75</v>
+        <v>-128.36</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>27.91</v>
+        <v>23.83</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.09</v>
+        <v>31.58</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.09</v>
+        <v>31.58</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1333</v>
+        <v>1472</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>-5.16</v>
+        <v>13.49</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-0.09</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7658</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2737,48 +2737,48 @@
         <v>6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-12.72</v>
+        <v>-17.66</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>48.41</v>
+        <v>165.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-61.13</v>
+        <v>-183.27</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>14.34</v>
+        <v>25.23</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>7.33</v>
+        <v>13.52</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>7.33</v>
+        <v>13.52</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1375</v>
+        <v>1406</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.99</v>
+        <v>4.86</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>5.32</v>
+        <v>3.28</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>-1.98</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2788,43 +2788,43 @@
         <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.11</v>
+        <v>-13.53</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>120.13</v>
+        <v>42.2</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-102.02</v>
+        <v>-55.73</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>39.97</v>
+        <v>14.34</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20.27</v>
+        <v>7.33</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>20.27</v>
+        <v>7.33</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1435</v>
+        <v>1375</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>3.43</v>
+        <v>3.99</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>7.72</v>
+        <v>5.32</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="39">
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2857,34 +2857,34 @@
         <v>5</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>18.94</v>
+        <v>16.23</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>104.16</v>
+        <v>87.73</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-85.22</v>
+        <v>-71.5</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>39.07</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>10.09</v>
+        <v>10.29</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>6.84</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="40">
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         <v>2</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3.87</v>
+        <v>-10.51</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17.91</v>
+        <v>31.18</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-14.05</v>
+        <v>-41.69</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>27.39</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>29.46</v>
+        <v>21.81</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>29.46</v>
+        <v>21.81</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1466</v>
+        <v>1441</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>10.91</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>13.98</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>4.57</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="41">
@@ -3097,64 +3097,64 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3620</v>
+        <v>10633</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>75.04000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>128.5</v>
+        <v>137.46</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>128.5</v>
+        <v>137.46</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>27.16</v>
+        <v>26.22</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>69.26000000000001</v>
+        <v>76.59</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32.08</v>
+        <v>34.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1665</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>10633</v>
+        <v>3620</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>45.8</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>123.2</v>
+        <v>128.5</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>123.2</v>
+        <v>128.5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>21.49</v>
+        <v>27.16</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>68.55</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>33.16</v>
+        <v>32.08</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1659</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="4">
@@ -3170,22 +3170,22 @@
         <v>68.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>120.67</v>
+        <v>120.13</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>120.67</v>
+        <v>120.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23.32</v>
+        <v>22.95</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70.67</v>
+        <v>70.84</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>26.69</v>
+        <v>26.34</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="5">
@@ -3232,22 +3232,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>115.51</v>
+        <v>116.95</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>115.51</v>
+        <v>116.95</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>25.75</v>
+        <v>24.31</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.95</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.81</v>
+        <v>26.67</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="7">
@@ -3263,22 +3263,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>105.05</v>
+        <v>112.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>105.05</v>
+        <v>112.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.29</v>
+        <v>24.28</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>55.97</v>
+        <v>62.18</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>24.79</v>
+        <v>26.04</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1632</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="8">
@@ -3294,146 +3294,146 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95.72</v>
+        <v>109.88</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>95.72</v>
+        <v>109.88</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>16.87</v>
+        <v>20.41</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.21</v>
+        <v>65.11</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>21.63</v>
+        <v>24.36</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1612</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>88.72</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>88.72</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.89</v>
+        <v>10.23</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>53.14</v>
+        <v>51.87</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.69</v>
+        <v>24.04</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1599</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3875</v>
+        <v>858</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.66</v>
+        <v>55.1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>87.52</v>
+        <v>84.95</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>87.52</v>
+        <v>84.95</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.56</v>
+        <v>14.25</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>51.15</v>
+        <v>43.29</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.8</v>
+        <v>27.4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1596</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>7656</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>53.52</v>
+        <v>50.91</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>80.31999999999999</v>
+        <v>81.06</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>80.31999999999999</v>
+        <v>81.06</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.81</v>
+        <v>9.68</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.37</v>
+        <v>48.63</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>21.13</v>
+        <v>22.75</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>858</v>
+        <v>2771</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55.1</v>
+        <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>78.39</v>
+        <v>75.88</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>78.39</v>
+        <v>75.88</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.83</v>
+        <v>6.92</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>39.84</v>
+        <v>47.11</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>25.72</v>
+        <v>21.85</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1577</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="13">
@@ -3449,22 +3449,22 @@
         <v>44.43</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>59.41</v>
+        <v>59.01</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>59.41</v>
+        <v>59.01</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>16.54</v>
+        <v>15.49</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>32.05</v>
+        <v>30.97</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.81</v>
+        <v>12.55</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14">
@@ -3511,22 +3511,22 @@
         <v>28.04</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>55.87</v>
+        <v>56.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>55.87</v>
+        <v>56.76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>12.62</v>
+        <v>11.18</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>28.68</v>
+        <v>31.44</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>14.57</v>
+        <v>14.14</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="16">
@@ -3542,84 +3542,84 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46.22</v>
+        <v>47.65</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46.22</v>
+        <v>47.65</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6.54</v>
+        <v>5.09</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>25.4</v>
+        <v>27.41</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.29</v>
+        <v>15.14</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9685</v>
+        <v>8767</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>27.75</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>41.65</v>
+        <v>40.7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>41.65</v>
+        <v>40.7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>18.71</v>
+        <v>5.76</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6.78</v>
+        <v>23.05</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.15</v>
+        <v>11.89</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8767</v>
+        <v>9685</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>40.7</v>
+        <v>40.56</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>40.7</v>
+        <v>40.56</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.76</v>
+        <v>18.86</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23.05</v>
+        <v>5.15</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.89</v>
+        <v>16.54</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="19">
@@ -3635,81 +3635,81 @@
         <v>32.52</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.03</v>
+        <v>38.63</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.03</v>
+        <v>38.63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>12.08</v>
+        <v>11.03</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.4</v>
+        <v>19.32</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>6.56</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7808</v>
+        <v>7289</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>24.37</v>
+        <v>33.29</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.87</v>
+        <v>34.23</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.87</v>
+        <v>34.23</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.52</v>
+        <v>12.91</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.61</v>
+        <v>9.4</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.74</v>
+        <v>11.91</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1489</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>5980</v>
+        <v>7808</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>38.55</v>
+        <v>24.37</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>33.3</v>
+        <v>33.43</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>33.3</v>
+        <v>33.43</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>7.8</v>
+        <v>4.63</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>19.04</v>
+        <v>16.35</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.46</v>
+        <v>12.45</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1477</v>
@@ -3717,30 +3717,30 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7809</v>
+        <v>5980</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>23.83</v>
+        <v>38.55</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32.97</v>
+        <v>33.08</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.97</v>
+        <v>33.08</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.71</v>
+        <v>7.21</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.29</v>
+        <v>20.33</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>14.96</v>
+        <v>5.54</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1476</v>
@@ -3748,30 +3748,30 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>7289</v>
+        <v>5501</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Bobcats</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33.29</v>
+        <v>31.87</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>32.8</v>
+        <v>31.87</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>32.8</v>
+        <v>31.87</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14.36</v>
+        <v>6.95</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.39</v>
+        <v>17.02</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11.06</v>
+        <v>7.9</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1476</v>
@@ -3779,95 +3779,95 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5501</v>
+        <v>7809</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bobcats</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>31.87</v>
+        <v>23.83</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>31.87</v>
+        <v>31.58</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>31.87</v>
+        <v>31.58</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6.95</v>
+        <v>4.05</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>17.02</v>
+        <v>13.49</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7.9</v>
+        <v>14.03</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>29.46</v>
+        <v>29.18</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>29.46</v>
+        <v>29.18</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10.91</v>
+        <v>1.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>13.98</v>
+        <v>15.67</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.57</v>
+        <v>12.4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9206</v>
+        <v>9566</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>21.07</v>
+        <v>39.97</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>28.68</v>
+        <v>25.52</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>28.68</v>
+        <v>25.52</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>3.59</v>
+        <v>5.39</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>14</v>
+        <v>11.49</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>11.1</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="27">
@@ -3883,84 +3883,84 @@
         <v>22.93</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>27.28</v>
+        <v>24.42</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>27.28</v>
+        <v>24.42</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11.58</v>
+        <v>10.93</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.08</v>
+        <v>5.5</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1460</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5256</v>
+        <v>10181</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>35.18</v>
+        <v>23.43</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>26.66</v>
+        <v>23.18</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.66</v>
+        <v>23.18</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6.39</v>
+        <v>7</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.52</v>
+        <v>9.9</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4.76</v>
+        <v>6.28</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1458</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>21.7</v>
+        <v>32.45</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>24.36</v>
+        <v>22.92</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>24.36</v>
+        <v>22.92</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.9</v>
+        <v>6.98</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.42</v>
+        <v>8.92</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1450</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="30">
@@ -3976,115 +3976,115 @@
         <v>8.82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>23.4</v>
+        <v>22.31</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>23.4</v>
+        <v>22.31</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.31</v>
+        <v>6.46</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.22</v>
+        <v>8.59</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6.87</v>
+        <v>7.26</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>10642</v>
+        <v>9671</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>25.63</v>
+        <v>27.39</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.76</v>
+        <v>21.81</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>20.76</v>
+        <v>21.81</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.64</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7.02</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>7.11</v>
+        <v>2.64</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8285</v>
+        <v>10642</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.07</v>
+        <v>25.63</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.7</v>
+        <v>20.22</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.7</v>
+        <v>20.22</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3.76</v>
+        <v>6.27</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.09</v>
+        <v>7.19</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.84</v>
+        <v>6.76</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>39.97</v>
+        <v>21.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.27</v>
+        <v>19.92</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.27</v>
+        <v>19.92</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>3.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>7.72</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
@@ -4120,157 +4120,157 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>11399</v>
+        <v>8285</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>23.74</v>
+        <v>39.07</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>18.85</v>
+        <v>19.3</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.85</v>
+        <v>19.3</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>5.46</v>
+        <v>3.1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9.84</v>
+        <v>10.29</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3.55</v>
+        <v>5.91</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>32.45</v>
+        <v>35.18</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.96</v>
+        <v>19.01</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.96</v>
+        <v>19.01</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.95</v>
+        <v>5.17</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.48</v>
+        <v>11.01</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>7.53</v>
+        <v>2.83</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1426</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10181</v>
+        <v>11399</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.43</v>
+        <v>23.74</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>16.53</v>
+        <v>15.38</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>16.53</v>
+        <v>15.38</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6.32</v>
+        <v>8.44</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>5.83</v>
+        <v>2.48</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1420</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3234</v>
+        <v>7256</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.62</v>
+        <v>25.23</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>14.3</v>
+        <v>13.52</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>14.3</v>
+        <v>13.52</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.71</v>
+        <v>4.86</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.42</v>
+        <v>3.28</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.18</v>
+        <v>5.38</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>3234</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>25.23</v>
+        <v>22.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.74</v>
+        <v>13.21</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.74</v>
+        <v>13.21</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5.45</v>
+        <v>4.86</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1.99</v>
+        <v>6.79</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>6.31</v>
+        <v>1.57</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="40">
@@ -4317,22 +4317,22 @@
         <v>27.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.74</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.74</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-5.16</v>
+        <v>-4.61</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.09</v>
+        <v>-1.5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1333</v>
+        <v>1328</v>
       </c>
     </row>
   </sheetData>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>201.9</v>
+        <v>202.64</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-10.48</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>212.39</v>
+        <v>211.43</v>
       </c>
     </row>
     <row r="3">
@@ -4412,32 +4412,32 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>180.95</v>
+        <v>194.35</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>49.45</v>
+        <v>6.46</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>131.5</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3875</v>
+        <v>7220</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>153.01</v>
+        <v>146.62</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>93.13</v>
+        <v>80.87</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>59.88</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -4450,32 +4450,32 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>148.67</v>
+        <v>145.77</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>70.11</v>
+        <v>77.73</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>78.56</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7220</v>
+        <v>3875</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>146.6</v>
+        <v>139.06</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>101.47</v>
+        <v>29.74</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45.14</v>
+        <v>109.32</v>
       </c>
     </row>
     <row r="7">
@@ -4488,13 +4488,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>142.13</v>
+        <v>133.98</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-10.34</v>
+        <v>16.87</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>152.47</v>
+        <v>117.12</v>
       </c>
     </row>
     <row r="8">
@@ -4507,89 +4507,89 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>131.85</v>
+        <v>128.47</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.71</v>
+        <v>52.69</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>90.14</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>106.59</v>
+        <v>115.06</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30.01</v>
+        <v>3.46</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>76.58</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>39.76</v>
+        <v>57.65</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>63.63</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>5166</v>
+        <v>2075</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>102.15</v>
+        <v>100.21</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16.44</v>
+        <v>63.13</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2075</v>
+        <v>7656</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>98.48</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>17.32</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.59</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="13">
@@ -4602,70 +4602,70 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>78.39</v>
+        <v>73.37</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>37.2</v>
+        <v>6.71</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>41.19</v>
+        <v>66.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>64.48</v>
+        <v>65.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-53.04</v>
+        <v>58.94</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>117.52</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>61.69</v>
+        <v>60.63</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>63.83</v>
+        <v>-17.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-2.15</v>
+        <v>77.79000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>58.84</v>
+        <v>58.68</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>25.68</v>
+        <v>196.18</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33.16</v>
+        <v>-137.5</v>
       </c>
     </row>
     <row r="17">
@@ -4678,32 +4678,32 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>57.34</v>
+        <v>58.35</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-27.06</v>
+        <v>-18.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>50.45</v>
+        <v>53.58</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>172.75</v>
+        <v>-2.71</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-122.3</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="19">
@@ -4716,374 +4716,374 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>35.76</v>
+        <v>39.94</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-11.29</v>
+        <v>10.7</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>47.06</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>33.68</v>
+        <v>33.21</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>145.56</v>
+        <v>51.84</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-111.88</v>
+        <v>-18.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>30.86</v>
+        <v>30.51</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>76.47</v>
+        <v>158.88</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-45.61</v>
+        <v>-128.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8767</v>
+        <v>9208</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>24.89</v>
+        <v>27.37</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>66.17</v>
+        <v>36.94</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-41.28</v>
+        <v>-9.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5256</v>
+        <v>9638</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23.05</v>
+        <v>25.51</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.73</v>
+        <v>62.41</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>16.32</v>
+        <v>-36.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9208</v>
+        <v>8767</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>20.96</v>
+        <v>22.88</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-1.01</v>
+        <v>73.05</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>21.96</v>
+        <v>-50.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>18.94</v>
+        <v>21.67</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>104.16</v>
+        <v>94.14</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-85.22</v>
+        <v>-72.45999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>18.79</v>
+        <v>19.14</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>66.91</v>
+        <v>33.1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-48.12</v>
+        <v>-13.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.11</v>
+        <v>16.23</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>120.13</v>
+        <v>87.73</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-102.02</v>
+        <v>-71.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7808</v>
+        <v>7221</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>12.31</v>
+        <v>14.84</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-56.08</v>
+        <v>72.08</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>68.39</v>
+        <v>-57.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>7808</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11.64</v>
+        <v>12.86</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>58.56</v>
+        <v>3.55</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-46.93</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9206</v>
+        <v>5256</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10.92</v>
+        <v>10.11</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-41.76</v>
+        <v>21.13</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>52.68</v>
+        <v>-11.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.67</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>75.06</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-66.75</v>
+        <v>-84.43000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9671</v>
+        <v>3234</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3.87</v>
+        <v>1.49</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17.91</v>
+        <v>80.02</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-14.05</v>
+        <v>-78.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10642</v>
+        <v>904</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>60.93</v>
+        <v>48.3</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-60.95</v>
+        <v>-48.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-0.39</v>
+        <v>-3.79</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>81.28</v>
+        <v>26.38</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-81.67</v>
+        <v>-30.18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-4.1</v>
+        <v>-10.51</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>114.64</v>
+        <v>31.18</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-118.74</v>
+        <v>-41.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-12.72</v>
+        <v>-11.76</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>48.41</v>
+        <v>79.87</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-61.13</v>
+        <v>-91.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7818</v>
+        <v>9549</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-14.94</v>
+        <v>-12.68</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>82.19</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-97.13</v>
+        <v>-78.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9549</v>
+        <v>7658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-15.62</v>
+        <v>-13.53</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>62.11</v>
+        <v>42.2</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-77.73</v>
+        <v>-55.73</v>
       </c>
     </row>
     <row r="39">
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-21.93</v>
+        <v>-17.66</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>191.64</v>
+        <v>165.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-213.58</v>
+        <v>-183.27</v>
       </c>
     </row>
     <row r="40">
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-24.59</v>
+        <v>-27.94</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-15.71</v>
+        <v>31.11</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-8.880000000000001</v>
+        <v>-59.05</v>
       </c>
     </row>
     <row r="41">
@@ -5264,24 +5264,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7656</v>
+        <v>4967</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -5289,15 +5289,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7808</v>
+        <v>7656</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -5306,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -5314,24 +5314,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -5339,15 +5339,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -5364,15 +5364,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4967</v>
+        <v>2075</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2</v>
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -5389,15 +5389,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10633</v>
+        <v>3875</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -5414,24 +5414,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3875</v>
+        <v>1023</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -5439,24 +5439,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -5464,15 +5464,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5166</v>
+        <v>7808</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -5489,15 +5489,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9208</v>
+        <v>7289</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -5514,11 +5514,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7289</v>
+        <v>8423</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -5539,24 +5539,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -5564,24 +5564,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5980</v>
+        <v>858</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -5597,16 +5597,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -5614,18 +5614,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>858</v>
+        <v>8767</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -5639,24 +5639,24 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8767</v>
+        <v>10642</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -5664,24 +5664,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9638</v>
+        <v>6081</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -5689,24 +5689,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>11399</v>
+        <v>9756</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -5714,24 +5714,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5256</v>
+        <v>5980</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -5739,15 +5739,15 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6081</v>
+        <v>11399</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -5764,18 +5764,18 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9685</v>
+        <v>10181</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -5789,15 +5789,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10642</v>
+        <v>9685</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>4</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -5814,11 +5814,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7221</v>
+        <v>5256</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -5839,24 +5839,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10664</v>
+        <v>4325</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -5864,15 +5864,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4325</v>
+        <v>9638</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>5</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -5889,24 +5889,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3234</v>
+        <v>7221</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -5914,24 +5914,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9756</v>
+        <v>9549</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -5939,18 +5939,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9549</v>
+        <v>10664</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -5964,15 +5964,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>10181</v>
+        <v>3234</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>5</v>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -5989,15 +5989,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7809</v>
+        <v>904</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>5</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -6014,24 +6014,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7256</v>
+        <v>7818</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -6039,24 +6039,24 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>7818</v>
+        <v>9566</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -6064,18 +6064,18 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
@@ -6089,11 +6089,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7658</v>
+        <v>7256</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -6114,24 +6114,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>9566</v>
+        <v>7658</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -6150,7 +6150,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>201.9</v>
+        <v>202.64</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-10.48</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>212.39</v>
+        <v>211.43</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>180.95</v>
+        <v>194.35</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>49.45</v>
+        <v>6.46</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>131.5</v>
+        <v>187.9</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6330,21 +6330,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3875</v>
+        <v>7220</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>153.01</v>
+        <v>146.62</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>93.13</v>
+        <v>80.87</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.88</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6361,13 +6361,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>148.67</v>
+        <v>145.77</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>70.11</v>
+        <v>77.73</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>78.56</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6376,21 +6376,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7220</v>
+        <v>3875</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>146.6</v>
+        <v>139.06</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>101.47</v>
+        <v>29.74</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45.14</v>
+        <v>109.32</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6407,13 +6407,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>142.13</v>
+        <v>133.98</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-10.34</v>
+        <v>16.87</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>152.47</v>
+        <v>117.12</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>131.85</v>
+        <v>128.47</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.71</v>
+        <v>52.69</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>90.14</v>
+        <v>75.78</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6445,21 +6445,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2771</v>
+        <v>5166</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>106.59</v>
+        <v>115.06</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30.01</v>
+        <v>3.46</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>76.58</v>
+        <v>111.6</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6468,21 +6468,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>39.76</v>
+        <v>57.65</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>63.63</v>
+        <v>46.25</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6491,21 +6491,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5166</v>
+        <v>2075</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.15</v>
+        <v>100.21</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.44</v>
+        <v>63.13</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>37.08</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6514,21 +6514,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2075</v>
+        <v>7656</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>98.48</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>17.32</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>27.59</v>
+        <v>71.72</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>78.39</v>
+        <v>73.37</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>37.2</v>
+        <v>6.71</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>41.19</v>
+        <v>66.66</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6560,21 +6560,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>64.48</v>
+        <v>65.5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-53.04</v>
+        <v>58.94</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>117.52</v>
+        <v>6.56</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6583,21 +6583,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>61.69</v>
+        <v>60.63</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>63.83</v>
+        <v>-17.16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-2.15</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6606,21 +6606,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7289</v>
+        <v>4325</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58.84</v>
+        <v>58.68</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>25.68</v>
+        <v>196.18</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33.16</v>
+        <v>-137.5</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>57.34</v>
+        <v>58.35</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-27.06</v>
+        <v>-18.71</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6652,21 +6652,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4325</v>
+        <v>7289</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>50.45</v>
+        <v>53.58</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>172.75</v>
+        <v>-2.71</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-122.3</v>
+        <v>56.29</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.76</v>
+        <v>39.94</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-11.29</v>
+        <v>10.7</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>47.06</v>
+        <v>29.24</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6698,21 +6698,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7809</v>
+        <v>10181</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33.68</v>
+        <v>33.21</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>145.56</v>
+        <v>51.84</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-111.88</v>
+        <v>-18.63</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6721,21 +6721,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10181</v>
+        <v>7809</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.86</v>
+        <v>30.51</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>76.47</v>
+        <v>158.88</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-45.61</v>
+        <v>-128.36</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6744,21 +6744,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>8767</v>
+        <v>9208</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>24.89</v>
+        <v>27.37</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>66.17</v>
+        <v>36.94</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-41.28</v>
+        <v>-9.58</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6767,21 +6767,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5256</v>
+        <v>9638</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>23.05</v>
+        <v>25.51</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.73</v>
+        <v>62.41</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16.32</v>
+        <v>-36.91</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6790,21 +6790,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9208</v>
+        <v>8767</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20.96</v>
+        <v>22.88</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-1.01</v>
+        <v>73.05</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>21.96</v>
+        <v>-50.17</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6813,21 +6813,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8285</v>
+        <v>9566</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>18.94</v>
+        <v>21.67</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>104.16</v>
+        <v>94.14</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-85.22</v>
+        <v>-72.45999999999999</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6836,21 +6836,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9638</v>
+        <v>9206</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>18.79</v>
+        <v>19.14</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>66.91</v>
+        <v>33.1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-48.12</v>
+        <v>-13.96</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6859,21 +6859,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9566</v>
+        <v>8285</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>18.11</v>
+        <v>16.23</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>120.13</v>
+        <v>87.73</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-102.02</v>
+        <v>-71.5</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6882,21 +6882,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7808</v>
+        <v>7221</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.31</v>
+        <v>14.84</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-56.08</v>
+        <v>72.08</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>68.39</v>
+        <v>-57.23</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6905,21 +6905,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7221</v>
+        <v>7808</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.64</v>
+        <v>12.86</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>58.56</v>
+        <v>3.55</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-46.93</v>
+        <v>9.31</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6928,21 +6928,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9206</v>
+        <v>5256</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>10.92</v>
+        <v>10.11</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-41.76</v>
+        <v>21.13</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>52.68</v>
+        <v>-11.01</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6951,21 +6951,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.67</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>75.06</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-66.75</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6974,21 +6974,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9671</v>
+        <v>3234</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3.87</v>
+        <v>1.49</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>17.91</v>
+        <v>80.02</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-14.05</v>
+        <v>-78.53</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6997,21 +6997,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10642</v>
+        <v>904</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>60.93</v>
+        <v>48.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-60.95</v>
+        <v>-48.11</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -7020,21 +7020,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-0.39</v>
+        <v>-3.79</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>81.28</v>
+        <v>26.38</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-81.67</v>
+        <v>-30.18</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -7043,21 +7043,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>11399</v>
+        <v>9671</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-4.1</v>
+        <v>-10.51</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>114.64</v>
+        <v>31.18</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-118.74</v>
+        <v>-41.69</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -7066,21 +7066,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7658</v>
+        <v>11399</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-12.72</v>
+        <v>-11.76</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>48.41</v>
+        <v>79.87</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-61.13</v>
+        <v>-91.62</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -7089,21 +7089,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7818</v>
+        <v>9549</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-14.94</v>
+        <v>-12.68</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>82.19</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-97.13</v>
+        <v>-78.86</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -7112,21 +7112,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>9549</v>
+        <v>7658</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-15.62</v>
+        <v>-13.53</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>62.11</v>
+        <v>42.2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-77.73</v>
+        <v>-55.73</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-21.93</v>
+        <v>-17.66</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>191.64</v>
+        <v>165.6</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-213.58</v>
+        <v>-183.27</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-24.59</v>
+        <v>-27.94</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-15.71</v>
+        <v>31.11</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-8.880000000000001</v>
+        <v>-59.05</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -609,122 +609,122 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Brighton, Michigan</t>
+          <t>Saint Joseph, Michigan</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>158.02</v>
+        <v>181.24</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>59.14</v>
+        <v>-22.29</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>98.88</v>
+        <v>203.53</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>129.36</v>
+        <v>130.31</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>129.36</v>
+        <v>130.31</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>28.97</v>
+        <v>24.54</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>79.77</v>
+        <v>72.12</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>20.62</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph, Michigan</t>
+          <t>Brighton, Michigan</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>181.7</v>
+        <v>151.84</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-17.86</v>
+        <v>65.48</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>199.56</v>
+        <v>86.36</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>130.31</v>
+        <v>130.08</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>130.31</v>
+        <v>130.08</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.54</v>
+        <v>30.8</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>72.12</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>33.64</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -754,51 +754,51 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>90.05</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-14.17</v>
+        <v>-2.84</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>104.21</v>
+        <v>99.77</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>50.91</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80.11</v>
+        <v>88.45</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>80.11</v>
+        <v>88.45</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1579</v>
+        <v>1595</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>10.13</v>
+        <v>12.89</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>48.97</v>
+        <v>51.94</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>21.02</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -817,34 +817,34 @@
         <v>31</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>125.06</v>
+        <v>197.56</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>49.06</v>
+        <v>19.53</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>76</v>
+        <v>178.03</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>127.64</v>
+        <v>145.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>127.64</v>
+        <v>145.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1662</v>
+        <v>1686</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.67</v>
+        <v>28.98</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>72.75</v>
+        <v>79.56</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>30.22</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="6">
@@ -865,7 +865,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2</v>
@@ -874,58 +874,58 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>115.72</v>
+        <v>115.95</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-7.64</v>
+        <v>-0.96</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>123.37</v>
+        <v>116.91</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>71.68000000000001</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>109.88</v>
+        <v>111.29</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>109.88</v>
+        <v>111.29</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>20.41</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>65.11</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>24.36</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>2</v>
@@ -934,37 +934,37 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>190.62</v>
+        <v>126.85</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>16.27</v>
+        <v>51.73</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>174.35</v>
+        <v>75.12</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>45.8</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>137.46</v>
+        <v>127.64</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>137.46</v>
+        <v>127.64</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1675</v>
+        <v>1662</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>26.22</v>
+        <v>24.67</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76.59</v>
+        <v>72.75</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>34.66</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="8">
@@ -985,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
@@ -994,37 +994,37 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>128.02</v>
+        <v>130.6</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31.83</v>
+        <v>28.77</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>96.19</v>
+        <v>101.83</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>50.66</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>86.15000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>86.15000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>51.87</v>
+        <v>52.66</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.04</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="9">
@@ -1057,13 +1057,13 @@
         <v>29</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>130.02</v>
+        <v>131.61</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>35.69</v>
+        <v>28.77</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>94.33</v>
+        <v>102.84</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>68.89</v>
@@ -1117,13 +1117,13 @@
         <v>29</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>126.2</v>
+        <v>127.36</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48.5</v>
+        <v>40.82</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>77.7</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>68.08</v>
@@ -1165,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>2</v>
@@ -1174,37 +1174,37 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>100.26</v>
+        <v>102.87</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>27.09</v>
+        <v>43.34</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>53.52</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>75.88</v>
+        <v>78.41</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>75.88</v>
+        <v>78.41</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.92</v>
+        <v>6.05</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>47.11</v>
+        <v>51.16</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.85</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="12">
@@ -1237,13 +1237,13 @@
         <v>26</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.94</v>
+        <v>32.65</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33.62</v>
+        <v>25.37</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.68</v>
+        <v>7.29</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>44.43</v>
@@ -1269,76 +1269,76 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7289</v>
+        <v>858</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>44.97</v>
+        <v>118.36</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-1.26</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46.22</v>
+        <v>23.14</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>33.29</v>
+        <v>55.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>34.23</v>
+        <v>78.95</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>34.23</v>
+        <v>78.95</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1479</v>
+        <v>1576</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>12.91</v>
+        <v>13.31</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>9.4</v>
+        <v>39.02</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>11.91</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>858</v>
+        <v>6081</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Manchester, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1354,51 +1354,51 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>122.56</v>
+        <v>71.72</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>69.53</v>
+        <v>56.6</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>53.03</v>
+        <v>15.12</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>55.1</v>
+        <v>59.73</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>80.68000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>80.68000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1580</v>
+        <v>1558</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>13.02</v>
+        <v>18.13</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>40.37</v>
+        <v>32.41</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>27.28</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>7808</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1408,57 +1408,57 @@
         <v>5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17.51</v>
+        <v>74.97</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>32.14</v>
+        <v>27.12</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-14.62</v>
+        <v>47.84</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>24.37</v>
+        <v>29.21</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>35.2</v>
+        <v>56.69</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>35.2</v>
+        <v>56.69</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1482</v>
+        <v>1531</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>4.17</v>
+        <v>6.66</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>16.5</v>
+        <v>35.67</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>14.53</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9756</v>
+        <v>7808</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Kalkaska, Michigan</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1477,48 +1477,48 @@
         <v>23</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29.82</v>
+        <v>56.29</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>43.58</v>
+        <v>-42.96</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>29.21</v>
+        <v>24.37</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>56.69</v>
+        <v>33.47</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>56.69</v>
+        <v>33.47</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1531</v>
+        <v>1477</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>6.66</v>
+        <v>4.45</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>35.67</v>
+        <v>15.15</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>14.36</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1537,115 +1537,115 @@
         <v>23</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>19.22</v>
+        <v>42.23</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>30.7</v>
+        <v>16.75</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-11.48</v>
+        <v>25.48</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>21.07</v>
+        <v>33.29</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>30.99</v>
+        <v>33.24</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>30.99</v>
+        <v>33.24</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.51</v>
+        <v>12.54</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>19.43</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>11.05</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8423</v>
+        <v>9206</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>65.12</v>
+        <v>13.8</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.01</v>
+        <v>54.23</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>51.1</v>
+        <v>-40.43</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>28.04</v>
+        <v>21.07</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>55.16</v>
+        <v>29.26</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>55.16</v>
+        <v>29.26</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1528</v>
+        <v>1465</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>10.29</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>29.95</v>
+        <v>18.07</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>14.92</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>6081</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Manchester, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>4</v>
@@ -1654,51 +1654,51 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>68.84999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>68.3</v>
+        <v>19.93</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>11.17</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>59.73</v>
+        <v>27.21</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>41.12</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>41.12</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1553</v>
+        <v>1496</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>19</v>
+        <v>6.03</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>28.36</v>
+        <v>23.96</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>20.13</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1714,37 +1714,37 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.65</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>23.33</v>
+        <v>34.84</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>8.33</v>
+        <v>29.9</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>27.21</v>
+        <v>28.04</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>41.12</v>
+        <v>54.17</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>41.12</v>
+        <v>54.17</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1496</v>
+        <v>1526</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>6.03</v>
+        <v>9.91</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>23.96</v>
+        <v>28.99</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>11.13</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="21">
@@ -1777,13 +1777,13 @@
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.76</v>
+        <v>11.58</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>76.87</v>
+        <v>71.08</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-65.11</v>
+        <v>-59.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>23.74</v>
@@ -1825,7 +1825,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>4</v>
@@ -1834,37 +1834,37 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>40.79</v>
+        <v>48.93</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18.67</v>
+        <v>22.08</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>22.12</v>
+        <v>26.85</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>27.75</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>42.36</v>
+        <v>50.7</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>42.36</v>
+        <v>50.7</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1499</v>
+        <v>1518</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>18.27</v>
+        <v>21.03</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>8.91</v>
+        <v>11.88</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>15.19</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="23">
@@ -1897,13 +1897,13 @@
         <v>17</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-3.62</v>
+        <v>-4.4</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>45.62</v>
+        <v>39.69</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-49.25</v>
+        <v>-44.09</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>25.63</v>
@@ -1948,43 +1948,43 @@
         <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>60.73</v>
+        <v>58.38</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>47.94</v>
+        <v>45.38</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>38.55</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>34.84</v>
+        <v>35.57</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>34.84</v>
+        <v>35.57</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>6.74</v>
+        <v>8.58</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>20.49</v>
+        <v>19.82</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>7.62</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="25">
@@ -2017,13 +2017,13 @@
         <v>16</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>23.23</v>
+        <v>22.83</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>70.17</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-45.47</v>
+        <v>-47.34</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.62</v>
@@ -2077,13 +2077,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>55.81</v>
+        <v>55.23</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>164.72</v>
+        <v>162.55</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-108.91</v>
+        <v>-107.32</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>32.52</v>
@@ -2137,13 +2137,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>28.15</v>
+        <v>26.71</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>52.33</v>
+        <v>53.64</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-24.18</v>
+        <v>-26.93</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>23.43</v>
@@ -2197,13 +2197,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11.43</v>
+        <v>9.85</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>94.45999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-83.03</v>
+        <v>-82.06</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>8.82</v>
@@ -2257,13 +2257,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.81</v>
+        <v>-10.51</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>123.5</v>
+        <v>118.28</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-132.31</v>
+        <v>-128.78</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>25.23</v>
@@ -2317,13 +2317,13 @@
         <v>13</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.65</v>
+        <v>32.98</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>59.71</v>
+        <v>60.84</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-27.06</v>
+        <v>-27.87</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>22.93</v>
@@ -2377,13 +2377,13 @@
         <v>13</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-56.17</v>
+        <v>-55.91</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>35.18</v>
@@ -2437,13 +2437,13 @@
         <v>13</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4.12</v>
+        <v>5.18</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>64.23</v>
+        <v>59.36</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-60.11</v>
+        <v>-54.18</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>39.97</v>
@@ -2469,16 +2469,16 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>9549</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -2488,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -2497,48 +2497,48 @@
         <v>11</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>-3.41</v>
+        <v>-0.61</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46.86</v>
+        <v>105.87</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-50.27</v>
+        <v>-106.48</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>17.6</v>
+        <v>32.45</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>20.44</v>
+        <v>22.68</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>20.44</v>
+        <v>22.68</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>7.46</v>
+        <v>6.57</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>9.99</v>
+        <v>6.27</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>2.99</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7818</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2557,34 +2557,34 @@
         <v>11</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-0.19</v>
+        <v>-5.04</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>107.73</v>
+        <v>62.26</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-107.92</v>
+        <v>-67.3</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>32.45</v>
+        <v>17.6</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22.68</v>
+        <v>19.45</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>22.68</v>
+        <v>19.45</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1444</v>
+        <v>1432</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>6.57</v>
+        <v>7.08</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>6.27</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>9.84</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="35">
@@ -2617,13 +2617,13 @@
         <v>11</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-29.97</v>
+        <v>-30.65</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>53.62</v>
+        <v>49.31</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-83.59</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.7</v>
@@ -2649,16 +2649,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,57 +2668,57 @@
         <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.23</v>
+        <v>34.28</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>60.46</v>
+        <v>150.17</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-60.23</v>
+        <v>-115.89</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>27.91</v>
+        <v>23.83</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.1</v>
+        <v>36.62</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1</v>
+        <v>36.62</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1332</v>
+        <v>1485</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>4.74</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>-4.23</v>
+        <v>18.85</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-0.61</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2737,115 +2737,115 @@
         <v>10</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>36.95</v>
+        <v>-1.72</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>146.99</v>
+        <v>34.21</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-110.03</v>
+        <v>-35.93</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>23.83</v>
+        <v>27.39</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>36.62</v>
+        <v>29.29</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>36.62</v>
+        <v>29.29</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1485</v>
+        <v>1465</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.2</v>
+        <v>8.31</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>18.85</v>
+        <v>16.04</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>15.57</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-2.67</v>
+        <v>-4.89</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28.2</v>
+        <v>63.41</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-30.87</v>
+        <v>-68.3</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>14.34</v>
+        <v>27.91</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9.35</v>
+        <v>0.63</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>9.35</v>
+        <v>0.63</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1385</v>
+        <v>1337</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>3.19</v>
+        <v>6.58</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>6.27</v>
+        <v>-4.9</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-0.11</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>38</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>7</v>
@@ -2854,51 +2854,51 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-2.41</v>
+        <v>22</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>27.78</v>
+        <v>100.99</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-30.2</v>
+        <v>-78.98</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>27.39</v>
+        <v>39.07</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>27.88</v>
+        <v>20.23</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>27.88</v>
+        <v>20.23</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1461</v>
+        <v>1434</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>15.26</v>
+        <v>12.84</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>4.32</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8285</v>
+        <v>7658</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2908,43 +2908,43 @@
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="I40" s="2" t="n">
-        <v>18.26</v>
+        <v>-1.23</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>122.36</v>
+        <v>23.68</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-104.1</v>
+        <v>-24.91</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>39.07</v>
+        <v>14.34</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>17.71</v>
+        <v>9.35</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>17.71</v>
+        <v>9.35</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1424</v>
+        <v>1385</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2.21</v>
+        <v>3.19</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.27</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>6.7</v>
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>137.46</v>
+        <v>145.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>137.46</v>
+        <v>145.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26.22</v>
+        <v>28.98</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>76.59</v>
+        <v>79.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34.66</v>
+        <v>37.27</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1675</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="3">
@@ -3094,22 +3094,22 @@
         <v>45.04</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>129.36</v>
+        <v>130.08</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>129.36</v>
+        <v>130.08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.97</v>
+        <v>30.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>79.77</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20.62</v>
+        <v>20.18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5">
@@ -3218,115 +3218,115 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>109.88</v>
+        <v>111.29</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>109.88</v>
+        <v>111.29</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>20.41</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.11</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.36</v>
+        <v>24.98</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>88.45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>88.45</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10.23</v>
+        <v>12.89</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.87</v>
+        <v>51.94</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>24.04</v>
+        <v>23.63</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1591</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>858</v>
+        <v>3875</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>55.1</v>
+        <v>50.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>80.68000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>80.68000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13.02</v>
+        <v>10.24</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.37</v>
+        <v>52.66</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>27.28</v>
+        <v>24.66</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1580</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7656</v>
+        <v>858</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>50.91</v>
+        <v>55.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>80.11</v>
+        <v>78.95</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>80.11</v>
+        <v>78.95</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>10.13</v>
+        <v>13.31</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>48.97</v>
+        <v>39.02</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>21.02</v>
+        <v>26.62</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="12">
@@ -3342,22 +3342,22 @@
         <v>53.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>75.88</v>
+        <v>78.41</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75.88</v>
+        <v>78.41</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6.92</v>
+        <v>6.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>47.11</v>
+        <v>51.16</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.85</v>
+        <v>21.2</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1570</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="13">
@@ -3373,22 +3373,22 @@
         <v>59.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>19</v>
+        <v>18.13</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.36</v>
+        <v>32.41</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>20.13</v>
+        <v>19.48</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1553</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="14">
@@ -3466,22 +3466,22 @@
         <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>55.16</v>
+        <v>54.17</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>55.16</v>
+        <v>54.17</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10.29</v>
+        <v>9.91</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>29.95</v>
+        <v>28.99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.92</v>
+        <v>15.27</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="17">
@@ -3497,22 +3497,22 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42.36</v>
+        <v>50.7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>42.36</v>
+        <v>50.7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>18.27</v>
+        <v>21.03</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.91</v>
+        <v>11.88</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>15.19</v>
+        <v>17.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1499</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="18">
@@ -3610,64 +3610,64 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7808</v>
+        <v>5980</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>24.37</v>
+        <v>38.55</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>35.2</v>
+        <v>35.57</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>35.2</v>
+        <v>35.57</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4.17</v>
+        <v>8.58</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16.5</v>
+        <v>19.82</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.53</v>
+        <v>7.18</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5980</v>
+        <v>7808</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>38.55</v>
+        <v>24.37</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>34.84</v>
+        <v>33.47</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>34.84</v>
+        <v>33.47</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6.74</v>
+        <v>4.45</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20.49</v>
+        <v>15.15</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>7.62</v>
+        <v>13.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="23">
@@ -3683,84 +3683,84 @@
         <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>34.23</v>
+        <v>33.24</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>34.23</v>
+        <v>33.24</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.91</v>
+        <v>12.54</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>9.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11.91</v>
+        <v>12.26</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>30.99</v>
+        <v>29.29</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30.99</v>
+        <v>29.29</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.51</v>
+        <v>8.31</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>19.43</v>
+        <v>16.04</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.05</v>
+        <v>4.94</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1470</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>21.07</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>27.88</v>
+        <v>29.26</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>27.88</v>
+        <v>29.26</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>15.26</v>
+        <v>18.07</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.32</v>
+        <v>10.39</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1461</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26">
@@ -3951,33 +3951,33 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9549</v>
+        <v>8285</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>17.6</v>
+        <v>39.07</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.44</v>
+        <v>20.23</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.44</v>
+        <v>20.23</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7.46</v>
+        <v>1.33</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.99</v>
+        <v>12.84</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>2.99</v>
+        <v>6.06</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="33">
@@ -4013,33 +4013,33 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8285</v>
+        <v>9549</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>39.07</v>
+        <v>17.6</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.71</v>
+        <v>19.45</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.71</v>
+        <v>19.45</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2.21</v>
+        <v>7.08</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.7</v>
+        <v>3.34</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1424</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="35">
@@ -4210,22 +4210,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.63</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.63</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4.74</v>
+        <v>6.58</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-4.23</v>
+        <v>-4.9</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-0.61</v>
+        <v>-1.05</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
   </sheetData>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>190.62</v>
+        <v>197.56</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16.27</v>
+        <v>19.53</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>174.35</v>
+        <v>178.03</v>
       </c>
     </row>
     <row r="3">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>181.7</v>
+        <v>181.24</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-17.86</v>
+        <v>-22.29</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>199.56</v>
+        <v>203.53</v>
       </c>
     </row>
     <row r="4">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>158.02</v>
+        <v>151.84</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>59.14</v>
+        <v>65.48</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>98.88</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="5">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>130.02</v>
+        <v>131.61</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>35.69</v>
+        <v>28.77</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>94.33</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="6">
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>128.02</v>
+        <v>130.6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>31.83</v>
+        <v>28.77</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>96.19</v>
+        <v>101.83</v>
       </c>
     </row>
     <row r="7">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>126.2</v>
+        <v>127.36</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>48.5</v>
+        <v>40.82</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>77.7</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>125.06</v>
+        <v>126.85</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>49.06</v>
+        <v>51.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>76</v>
+        <v>75.12</v>
       </c>
     </row>
     <row r="9">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>122.56</v>
+        <v>118.36</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>69.53</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>53.03</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="10">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115.72</v>
+        <v>115.95</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-7.64</v>
+        <v>-0.96</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>123.37</v>
+        <v>116.91</v>
       </c>
     </row>
     <row r="11">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>100.26</v>
+        <v>102.87</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>27.09</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="12">
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>90.05</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-14.17</v>
+        <v>-2.84</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>104.21</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="13">
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>43.58</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="14">
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>68.84999999999999</v>
+        <v>71.72</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>68.3</v>
+        <v>56.6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="15">
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>65.12</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14.01</v>
+        <v>34.84</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>51.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="16">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>60.73</v>
+        <v>58.38</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>47.94</v>
+        <v>45.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -4571,51 +4571,51 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>55.81</v>
+        <v>55.23</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>164.72</v>
+        <v>162.55</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-108.91</v>
+        <v>-107.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7289</v>
+        <v>9685</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>44.97</v>
+        <v>48.93</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-1.26</v>
+        <v>22.08</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46.22</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9685</v>
+        <v>7289</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.79</v>
+        <v>42.23</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>18.67</v>
+        <v>16.75</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>22.12</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="20">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>36.95</v>
+        <v>34.28</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>146.99</v>
+        <v>150.17</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-110.03</v>
+        <v>-115.89</v>
       </c>
     </row>
     <row r="21">
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>32.65</v>
+        <v>32.98</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>59.71</v>
+        <v>60.84</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-27.06</v>
+        <v>-27.87</v>
       </c>
     </row>
     <row r="22">
@@ -4666,13 +4666,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>31.94</v>
+        <v>32.65</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>33.62</v>
+        <v>25.37</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-1.68</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="23">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>31.65</v>
+        <v>31.1</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>23.33</v>
+        <v>19.93</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8.33</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="24">
@@ -4704,13 +4704,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>28.15</v>
+        <v>26.71</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>52.33</v>
+        <v>53.64</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-24.18</v>
+        <v>-26.93</v>
       </c>
     </row>
     <row r="25">
@@ -4723,51 +4723,51 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>23.23</v>
+        <v>22.83</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>70.17</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-45.47</v>
+        <v>-47.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9206</v>
+        <v>8285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19.22</v>
+        <v>22</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>30.7</v>
+        <v>100.99</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-11.48</v>
+        <v>-78.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.26</v>
+        <v>13.8</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>122.36</v>
+        <v>54.23</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-104.1</v>
+        <v>-40.43</v>
       </c>
     </row>
     <row r="28">
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>17.51</v>
+        <v>13.33</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>32.14</v>
+        <v>56.29</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-14.62</v>
+        <v>-42.96</v>
       </c>
     </row>
     <row r="29">
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11.76</v>
+        <v>11.58</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>76.87</v>
+        <v>71.08</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-65.11</v>
+        <v>-59.5</v>
       </c>
     </row>
     <row r="30">
@@ -4818,13 +4818,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>11.43</v>
+        <v>9.85</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>94.45999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-83.03</v>
+        <v>-82.06</v>
       </c>
     </row>
     <row r="31">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>10</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-56.17</v>
+        <v>-55.91</v>
       </c>
     </row>
     <row r="32">
@@ -4856,51 +4856,51 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4.12</v>
+        <v>5.18</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>64.23</v>
+        <v>59.36</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-60.11</v>
+        <v>-54.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.23</v>
+        <v>-0.61</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>60.46</v>
+        <v>105.87</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-60.23</v>
+        <v>-106.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-0.19</v>
+        <v>-1.23</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>107.73</v>
+        <v>23.68</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-107.92</v>
+        <v>-24.91</v>
       </c>
     </row>
     <row r="35">
@@ -4913,70 +4913,70 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-2.41</v>
+        <v>-1.72</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>27.78</v>
+        <v>34.21</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-30.2</v>
+        <v>-35.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7658</v>
+        <v>10642</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-2.67</v>
+        <v>-4.4</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>28.2</v>
+        <v>39.69</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-30.87</v>
+        <v>-44.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>9549</v>
+        <v>904</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-3.41</v>
+        <v>-4.89</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>46.86</v>
+        <v>63.41</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-50.27</v>
+        <v>-68.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>9549</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-3.62</v>
+        <v>-5.04</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>45.62</v>
+        <v>62.26</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-49.25</v>
+        <v>-67.3</v>
       </c>
     </row>
     <row r="39">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-8.81</v>
+        <v>-10.51</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>123.5</v>
+        <v>118.28</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-132.31</v>
+        <v>-128.78</v>
       </c>
     </row>
     <row r="40">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-29.97</v>
+        <v>-30.65</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>53.62</v>
+        <v>49.31</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-83.59</v>
+        <v>-79.95999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5082,24 +5082,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -5107,24 +5107,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -5157,11 +5157,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2075</v>
+        <v>10633</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2</v>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -5207,15 +5207,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -5357,24 +5357,24 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7289</v>
+        <v>858</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -5382,11 +5382,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>858</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -5407,24 +5407,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7808</v>
+        <v>9756</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -5432,11 +5432,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9756</v>
+        <v>7808</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -5457,11 +5457,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9206</v>
+        <v>7289</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -5482,24 +5482,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8423</v>
+        <v>9206</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -5507,15 +5507,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>6081</v>
+        <v>8767</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>4</v>
@@ -5524,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -5532,11 +5532,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8767</v>
+        <v>8423</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>4</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -5643,13 +5643,13 @@
         <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -5857,18 +5857,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>9549</v>
+        <v>7818</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
@@ -5882,11 +5882,11 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7818</v>
+        <v>9549</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -5932,24 +5932,24 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>904</v>
+        <v>7809</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -5957,11 +5957,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7809</v>
+        <v>9671</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -5982,24 +5982,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -6007,15 +6007,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>9671</v>
+        <v>8285</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>7</v>
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -6032,24 +6032,24 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8285</v>
+        <v>7658</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>190.62</v>
+        <v>197.56</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.27</v>
+        <v>19.53</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>174.35</v>
+        <v>178.03</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>181.7</v>
+        <v>181.24</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-17.86</v>
+        <v>-22.29</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>199.56</v>
+        <v>203.53</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>158.02</v>
+        <v>151.84</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>59.14</v>
+        <v>65.48</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>98.88</v>
+        <v>86.36</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6194,13 +6194,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>130.02</v>
+        <v>131.61</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>35.69</v>
+        <v>28.77</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>94.33</v>
+        <v>102.84</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>128.02</v>
+        <v>130.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.83</v>
+        <v>28.77</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>96.19</v>
+        <v>101.83</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6240,13 +6240,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>126.2</v>
+        <v>127.36</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48.5</v>
+        <v>40.82</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>77.7</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>125.06</v>
+        <v>126.85</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>49.06</v>
+        <v>51.73</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>76</v>
+        <v>75.12</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>122.56</v>
+        <v>118.36</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>69.53</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>53.03</v>
+        <v>23.14</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>115.72</v>
+        <v>115.95</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-7.64</v>
+        <v>-0.96</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>123.37</v>
+        <v>116.91</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>100.26</v>
+        <v>102.87</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>27.09</v>
+        <v>43.34</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>90.05</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-14.17</v>
+        <v>-2.84</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>104.21</v>
+        <v>99.77</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>43.58</v>
+        <v>47.84</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>68.84999999999999</v>
+        <v>71.72</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68.3</v>
+        <v>56.6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>15.12</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>65.12</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14.01</v>
+        <v>34.84</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>51.1</v>
+        <v>29.9</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>60.73</v>
+        <v>58.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>47.94</v>
+        <v>45.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>55.81</v>
+        <v>55.23</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>164.72</v>
+        <v>162.55</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-108.91</v>
+        <v>-107.32</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6485,21 +6485,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7289</v>
+        <v>9685</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44.97</v>
+        <v>48.93</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-1.26</v>
+        <v>22.08</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46.22</v>
+        <v>26.85</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6508,21 +6508,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9685</v>
+        <v>7289</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40.79</v>
+        <v>42.23</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>18.67</v>
+        <v>16.75</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>22.12</v>
+        <v>25.48</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6539,13 +6539,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.95</v>
+        <v>34.28</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>146.99</v>
+        <v>150.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-110.03</v>
+        <v>-115.89</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.65</v>
+        <v>32.98</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>59.71</v>
+        <v>60.84</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-27.06</v>
+        <v>-27.87</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.94</v>
+        <v>32.65</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>33.62</v>
+        <v>25.37</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1.68</v>
+        <v>7.29</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.65</v>
+        <v>31.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>23.33</v>
+        <v>19.93</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>8.33</v>
+        <v>11.17</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.15</v>
+        <v>26.71</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>52.33</v>
+        <v>53.64</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-24.18</v>
+        <v>-26.93</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6654,13 +6654,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23.23</v>
+        <v>22.83</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>70.17</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-45.47</v>
+        <v>-47.34</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6669,21 +6669,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9206</v>
+        <v>8285</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.22</v>
+        <v>22</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>30.7</v>
+        <v>100.99</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-11.48</v>
+        <v>-78.98</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6692,21 +6692,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>18.26</v>
+        <v>13.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>122.36</v>
+        <v>54.23</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-104.1</v>
+        <v>-40.43</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>17.51</v>
+        <v>13.33</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>32.14</v>
+        <v>56.29</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-14.62</v>
+        <v>-42.96</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.76</v>
+        <v>11.58</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>76.87</v>
+        <v>71.08</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-65.11</v>
+        <v>-59.5</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11.43</v>
+        <v>9.85</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>94.45999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-83.03</v>
+        <v>-82.06</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>10</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-56.17</v>
+        <v>-55.91</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4.12</v>
+        <v>5.18</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>64.23</v>
+        <v>59.36</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-60.11</v>
+        <v>-54.18</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6830,21 +6830,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.23</v>
+        <v>-0.61</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>60.46</v>
+        <v>105.87</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-60.23</v>
+        <v>-106.48</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -6853,21 +6853,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7818</v>
+        <v>7658</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-0.19</v>
+        <v>-1.23</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>107.73</v>
+        <v>23.68</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-107.92</v>
+        <v>-24.91</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -6884,13 +6884,13 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-2.41</v>
+        <v>-1.72</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>27.78</v>
+        <v>34.21</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-30.2</v>
+        <v>-35.93</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -6899,21 +6899,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7658</v>
+        <v>10642</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-2.67</v>
+        <v>-4.4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>28.2</v>
+        <v>39.69</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-30.87</v>
+        <v>-44.09</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -6922,21 +6922,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>9549</v>
+        <v>904</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-3.41</v>
+        <v>-4.89</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46.86</v>
+        <v>63.41</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-50.27</v>
+        <v>-68.3</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -6945,21 +6945,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>10642</v>
+        <v>9549</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-3.62</v>
+        <v>-5.04</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>45.62</v>
+        <v>62.26</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-49.25</v>
+        <v>-67.3</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -6976,13 +6976,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-8.81</v>
+        <v>-10.51</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>123.5</v>
+        <v>118.28</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-132.31</v>
+        <v>-128.78</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-29.97</v>
+        <v>-30.65</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>53.62</v>
+        <v>49.31</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-83.59</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,37 +634,37 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>181.24</v>
+        <v>177.81</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-22.29</v>
+        <v>-2.62</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>203.53</v>
+        <v>180.43</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>130.31</v>
+        <v>132.42</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>130.31</v>
+        <v>132.42</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24.54</v>
+        <v>25.48</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>72.12</v>
+        <v>73.63</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33.64</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="3">
@@ -685,7 +685,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -694,37 +694,37 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>151.84</v>
+        <v>162.9</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>65.48</v>
+        <v>48.48</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>86.36</v>
+        <v>114.42</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>130.08</v>
+        <v>138.69</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>130.08</v>
+        <v>138.69</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1665</v>
+        <v>1676</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.8</v>
+        <v>30.97</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>20.18</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="4">
@@ -757,13 +757,13 @@
         <v>32</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96.93000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-2.84</v>
+        <v>-7.24</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>99.77</v>
+        <v>101.95</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>50.91</v>
@@ -789,23 +789,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bridgman, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2</v>
@@ -814,51 +814,51 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>197.56</v>
+        <v>134.03</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>19.53</v>
+        <v>34.99</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>178.03</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>45.8</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>145.8</v>
+        <v>129.77</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>145.8</v>
+        <v>129.77</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1686</v>
+        <v>1664</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>28.98</v>
+        <v>23.88</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>79.56</v>
+        <v>73.83</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>37.27</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5166</v>
+        <v>10633</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Bridgman, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -877,48 +877,48 @@
         <v>31</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>115.95</v>
+        <v>194.92</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.96</v>
+        <v>23.1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>116.91</v>
+        <v>171.83</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>71.68000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>111.29</v>
+        <v>145.8</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>111.29</v>
+        <v>145.8</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1640</v>
+        <v>1686</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>20.41</v>
+        <v>28.98</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>79.56</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>24.98</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2075</v>
+        <v>5166</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -937,34 +937,34 @@
         <v>31</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>126.85</v>
+        <v>115.71</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>51.73</v>
+        <v>-7.68</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>75.12</v>
+        <v>123.39</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>127.64</v>
+        <v>111.29</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>127.64</v>
+        <v>111.29</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1662</v>
+        <v>1640</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.67</v>
+        <v>20.41</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>72.75</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>30.22</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="8">
@@ -997,13 +997,13 @@
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>130.6</v>
+        <v>127.32</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28.77</v>
+        <v>33.74</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>101.83</v>
+        <v>93.59</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>50.66</v>
@@ -1045,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>3</v>
@@ -1054,157 +1054,157 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>131.61</v>
+        <v>126.87</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>28.77</v>
+        <v>45.02</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>102.84</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>112.25</v>
+        <v>114.36</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>112.25</v>
+        <v>114.36</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>23.83</v>
+        <v>24.77</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>61.46</v>
+        <v>62.97</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>26.96</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>127.36</v>
+        <v>98.88</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40.82</v>
+        <v>59.56</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>86.54000000000001</v>
+        <v>39.33</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>68.08</v>
+        <v>53.52</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>121.94</v>
+        <v>78.41</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>121.94</v>
+        <v>78.41</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1655</v>
+        <v>1575</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>22.35</v>
+        <v>6.05</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>51.16</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>24.99</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>102.87</v>
+        <v>134.58</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>59.53</v>
+        <v>55.24</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>43.34</v>
+        <v>79.34</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>53.52</v>
+        <v>68.08</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>78.41</v>
+        <v>123.57</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>78.41</v>
+        <v>123.57</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1575</v>
+        <v>1656</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.05</v>
+        <v>22.32</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>51.16</v>
+        <v>76.88</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.2</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="12">
@@ -1225,7 +1225,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>3</v>
@@ -1234,37 +1234,37 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32.65</v>
+        <v>31.52</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>25.37</v>
+        <v>41.02</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7.29</v>
+        <v>-9.5</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>58.78</v>
+        <v>60.89</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>58.78</v>
+        <v>60.89</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>15.53</v>
+        <v>16.47</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>30.88</v>
+        <v>32.38</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>12.36</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="13">
@@ -1297,13 +1297,13 @@
         <v>26</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>118.36</v>
+        <v>116.35</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>95.20999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>23.14</v>
+        <v>21.34</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>55.1</v>
@@ -1357,13 +1357,13 @@
         <v>23</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>71.72</v>
+        <v>74.69</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56.6</v>
+        <v>52.26</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>15.12</v>
+        <v>22.43</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>59.73</v>
@@ -1417,13 +1417,13 @@
         <v>23</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>74.97</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>27.12</v>
+        <v>29.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>47.84</v>
+        <v>41.67</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>29.21</v>
@@ -1477,13 +1477,13 @@
         <v>23</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13.33</v>
+        <v>12.77</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>56.29</v>
+        <v>51.26</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-42.96</v>
+        <v>-38.49</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>24.37</v>
@@ -1537,13 +1537,13 @@
         <v>23</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>42.23</v>
+        <v>39.41</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>16.75</v>
+        <v>16.34</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>25.48</v>
+        <v>23.07</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>33.29</v>
@@ -1569,16 +1569,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9206</v>
+        <v>8423</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1597,55 +1597,55 @@
         <v>24</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13.8</v>
+        <v>69.47</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>54.23</v>
+        <v>23.78</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-40.43</v>
+        <v>45.68</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>21.07</v>
+        <v>28.04</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>29.26</v>
+        <v>56.3</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>29.26</v>
+        <v>56.3</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1465</v>
+        <v>1530</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.8</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>18.07</v>
+        <v>30.07</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>10.39</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>4</v>
@@ -1654,51 +1654,51 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>31.1</v>
+        <v>16.64</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>19.93</v>
+        <v>51.48</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>11.17</v>
+        <v>-34.84</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.21</v>
+        <v>21.07</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>41.12</v>
+        <v>29.26</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>41.12</v>
+        <v>29.26</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1496</v>
+        <v>1465</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6.03</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.96</v>
+        <v>18.07</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11.13</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1714,37 +1714,37 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>64.73999999999999</v>
+        <v>33.24</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34.84</v>
+        <v>18.77</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>29.9</v>
+        <v>14.47</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>28.04</v>
+        <v>27.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>54.17</v>
+        <v>41.12</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>54.17</v>
+        <v>41.12</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1526</v>
+        <v>1496</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>9.91</v>
+        <v>6.03</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>28.99</v>
+        <v>23.96</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>15.27</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="21">
@@ -1777,13 +1777,13 @@
         <v>20</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.58</v>
+        <v>9.93</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>71.08</v>
+        <v>71.92</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-59.5</v>
+        <v>-61.99</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>23.74</v>
@@ -1837,13 +1837,13 @@
         <v>22</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>48.93</v>
+        <v>46.59</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>22.08</v>
+        <v>19.84</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>26.85</v>
+        <v>26.75</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>27.75</v>
@@ -1869,86 +1869,86 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>10642</v>
+        <v>5980</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-4.4</v>
+        <v>52.45</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>39.69</v>
+        <v>49.38</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-44.09</v>
+        <v>3.08</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>25.63</v>
+        <v>38.55</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>17.14</v>
+        <v>35.57</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>17.14</v>
+        <v>35.57</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1422</v>
+        <v>1483</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>5.54</v>
+        <v>8.58</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.84</v>
+        <v>19.82</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>5.76</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5980</v>
+        <v>3234</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Lowell, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -1957,48 +1957,48 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>58.38</v>
+        <v>22.54</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>45.38</v>
+        <v>65.59</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>13</v>
+        <v>-43.05</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>38.55</v>
+        <v>22.62</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>35.57</v>
+        <v>23.91</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>35.57</v>
+        <v>23.91</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1483</v>
+        <v>1448</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>8.58</v>
+        <v>5.22</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>19.82</v>
+        <v>13.58</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>7.18</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>3234</v>
+        <v>9638</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Lowell, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2008,103 +2008,103 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>22.83</v>
+        <v>46.57</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>70.17</v>
+        <v>38</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-47.34</v>
+        <v>8.57</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>22.62</v>
+        <v>22.93</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>23.91</v>
+        <v>32</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>23.91</v>
+        <v>32</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1448</v>
+        <v>1473</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>5.22</v>
+        <v>7.7</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>13.58</v>
+        <v>15.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>5.12</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4325</v>
+        <v>10642</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Cassopolis, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>55.23</v>
+        <v>-6.64</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>162.55</v>
+        <v>36.99</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-107.32</v>
+        <v>-43.63</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>32.52</v>
+        <v>25.63</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>40.01</v>
+        <v>13.71</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>40.01</v>
+        <v>13.71</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1494</v>
+        <v>1407</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>10.85</v>
+        <v>5.3</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>19.89</v>
+        <v>3.89</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>9.26</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="27">
@@ -2137,13 +2137,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>26.71</v>
+        <v>25.39</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>53.64</v>
+        <v>50.53</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-26.93</v>
+        <v>-25.13</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>23.43</v>
@@ -2169,16 +2169,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -2188,43 +2188,43 @@
         <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.85</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>91.91</v>
+        <v>47.95</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-82.06</v>
+        <v>-38.66</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>8.82</v>
+        <v>17.6</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>22.06</v>
+        <v>28.06</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>22.06</v>
+        <v>28.06</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1441</v>
+        <v>1462</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>6.01</v>
+        <v>7.25</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>7.88</v>
+        <v>13.73</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>8.17</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="29">
@@ -2248,57 +2248,57 @@
         <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.51</v>
+        <v>-1.54</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>118.28</v>
+        <v>127.71</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-128.78</v>
+        <v>-129.25</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>25.23</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>12.34</v>
+        <v>13.97</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.34</v>
+        <v>13.97</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.35</v>
+        <v>5.31</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.53</v>
+        <v>5.8</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>3.47</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9638</v>
+        <v>5256</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2317,108 +2317,108 @@
         <v>13</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.98</v>
+        <v>5.75</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>60.84</v>
+        <v>68.89</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-27.87</v>
+        <v>-63.14</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>22.93</v>
+        <v>35.18</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>23.39</v>
+        <v>17.69</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>23.39</v>
+        <v>17.69</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1446</v>
+        <v>1424</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>7.53</v>
+        <v>3.97</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>10.51</v>
+        <v>9.81</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>5.36</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>4325</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Cassopolis, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>51.47</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>64.28</v>
+        <v>161.15</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-55.91</v>
+        <v>-109.68</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>35.18</v>
+        <v>32.52</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>17.69</v>
+        <v>36.58</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>17.69</v>
+        <v>36.58</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1424</v>
+        <v>1485</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>3.97</v>
+        <v>10.62</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>9.81</v>
+        <v>17.94</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.91</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2428,64 +2428,64 @@
         <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5.18</v>
+        <v>5.84</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>59.36</v>
+        <v>24.98</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-54.18</v>
+        <v>-19.15</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>39.97</v>
+        <v>27.39</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>21.25</v>
+        <v>31.41</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>21.25</v>
+        <v>31.41</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1438</v>
+        <v>1471</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4.16</v>
+        <v>7.51</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>8.57</v>
+        <v>17.12</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>8.52</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>7221</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>7</v>
@@ -2494,58 +2494,58 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>-0.61</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>105.87</v>
+        <v>100.72</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-106.48</v>
+        <v>-92.42</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>32.45</v>
+        <v>8.82</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>22.68</v>
+        <v>21.13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>22.68</v>
+        <v>21.13</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6.57</v>
+        <v>6.02</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>6.27</v>
+        <v>7.09</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>9.84</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>7</v>
@@ -2554,61 +2554,61 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-5.04</v>
+        <v>2.64</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>62.26</v>
+        <v>55.49</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-67.3</v>
+        <v>-52.85</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>17.6</v>
+        <v>39.97</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19.45</v>
+        <v>17.83</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>19.45</v>
+        <v>17.83</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>7.08</v>
+        <v>3.92</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>3.34</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -2617,55 +2617,55 @@
         <v>11</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-30.65</v>
+        <v>-1.86</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>49.31</v>
+        <v>110.68</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-79.95999999999999</v>
+        <v>-112.54</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>21.7</v>
+        <v>32.45</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>17.3</v>
+        <v>22.68</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.3</v>
+        <v>22.68</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1423</v>
+        <v>1444</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6.79</v>
+        <v>6.57</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>7.73</v>
+        <v>6.27</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>2.78</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7809</v>
+        <v>10664</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bangor, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>7</v>
@@ -2674,51 +2674,51 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>-88.14</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>1429</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Q36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>150.17</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>-115.89</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>18.85</v>
-      </c>
       <c r="R36" s="2" t="n">
-        <v>15.57</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>9671</v>
+        <v>7809</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bangor, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2737,34 +2737,34 @@
         <v>10</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-1.72</v>
+        <v>30.65</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>34.21</v>
+        <v>148.07</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-35.93</v>
+        <v>-117.42</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>27.39</v>
+        <v>23.83</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>29.29</v>
+        <v>36.62</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>29.29</v>
+        <v>36.62</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1465</v>
+        <v>1485</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>16.04</v>
+        <v>18.85</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>4.94</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="38">
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
@@ -2797,34 +2797,34 @@
         <v>10</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-4.89</v>
+        <v>-8.43</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>63.41</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-68.3</v>
+        <v>-80.72</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>27.91</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>-4.9</v>
+        <v>-5.69</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-1.05</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="39">
@@ -2848,7 +2848,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2857,34 +2857,34 @@
         <v>9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>22</v>
+        <v>21.48</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>100.99</v>
+        <v>110.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-78.98</v>
+        <v>-88.70999999999999</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>39.07</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>20.23</v>
+        <v>19.31</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>20.23</v>
+        <v>19.31</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>12.84</v>
+        <v>12.06</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>6.06</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="40">
@@ -2917,13 +2917,13 @@
         <v>7</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-1.23</v>
+        <v>-4.59</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>23.68</v>
+        <v>23.83</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-24.91</v>
+        <v>-28.42</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>14.34</v>
@@ -3052,64 +3052,64 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3620</v>
+        <v>7220</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Average Joes</t>
+          <t>Steel Falcons</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>130.31</v>
+        <v>138.69</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>130.31</v>
+        <v>138.69</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>24.54</v>
+        <v>30.97</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>72.12</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>33.64</v>
+        <v>23.92</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1666</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7220</v>
+        <v>3620</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Steel Falcons</t>
+          <t>Average Joes</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.04</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>130.08</v>
+        <v>132.42</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>130.08</v>
+        <v>132.42</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>30.8</v>
+        <v>25.48</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>73.63</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20.18</v>
+        <v>33.31</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1665</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5">
@@ -3125,22 +3125,22 @@
         <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>127.64</v>
+        <v>129.77</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>127.64</v>
+        <v>129.77</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>24.67</v>
+        <v>23.88</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>72.75</v>
+        <v>73.83</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>30.22</v>
+        <v>32.06</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1662</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="6">
@@ -3156,22 +3156,22 @@
         <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>121.94</v>
+        <v>123.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>121.94</v>
+        <v>123.57</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.35</v>
+        <v>22.32</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>76.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24.99</v>
+        <v>24.37</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3187,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>112.25</v>
+        <v>114.36</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112.25</v>
+        <v>114.36</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.83</v>
+        <v>24.77</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>61.46</v>
+        <v>62.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>26.96</v>
+        <v>26.63</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="8">
@@ -3404,22 +3404,22 @@
         <v>44.43</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.78</v>
+        <v>60.89</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.78</v>
+        <v>60.89</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>15.53</v>
+        <v>16.47</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30.88</v>
+        <v>32.38</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.36</v>
+        <v>12.03</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1535</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="15">
@@ -3466,22 +3466,22 @@
         <v>28.04</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>54.17</v>
+        <v>56.3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.17</v>
+        <v>56.3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9.91</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.99</v>
+        <v>30.07</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.27</v>
+        <v>17.11</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="17">
@@ -3548,61 +3548,61 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>7809</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>23.83</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40.01</v>
+        <v>36.62</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40.01</v>
+        <v>36.62</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.85</v>
+        <v>2.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.89</v>
+        <v>18.85</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>9.26</v>
+        <v>15.57</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1494</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>4325</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>23.83</v>
+        <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>36.62</v>
+        <v>36.58</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.62</v>
+        <v>36.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.2</v>
+        <v>10.62</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.85</v>
+        <v>17.94</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>15.57</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>1485</v>
@@ -3703,247 +3703,247 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9671</v>
+        <v>9638</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>27.39</v>
+        <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>29.29</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.29</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>8.31</v>
+        <v>7.7</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>16.04</v>
+        <v>15.2</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4.94</v>
+        <v>9.1</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1465</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9206</v>
+        <v>9671</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>21.07</v>
+        <v>27.39</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>29.26</v>
+        <v>31.41</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>29.26</v>
+        <v>31.41</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.8</v>
+        <v>7.51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>18.07</v>
+        <v>17.12</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.39</v>
+        <v>6.78</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1465</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>11399</v>
+        <v>9206</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23.74</v>
+        <v>21.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.07</v>
+        <v>29.26</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.07</v>
+        <v>29.26</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.82</v>
+        <v>0.8</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15.23</v>
+        <v>18.07</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6.03</v>
+        <v>10.39</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1455</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>3234</v>
+        <v>9549</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>22.62</v>
+        <v>17.6</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>23.91</v>
+        <v>28.06</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>23.91</v>
+        <v>28.06</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.22</v>
+        <v>7.25</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13.58</v>
+        <v>13.73</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.12</v>
+        <v>7.08</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1448</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9638</v>
+        <v>11399</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>22.93</v>
+        <v>23.74</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>23.39</v>
+        <v>26.07</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>23.39</v>
+        <v>26.07</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7.53</v>
+        <v>4.82</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10.51</v>
+        <v>15.23</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.36</v>
+        <v>6.03</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1446</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7818</v>
+        <v>3234</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>32.45</v>
+        <v>22.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.68</v>
+        <v>23.91</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.68</v>
+        <v>23.91</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.57</v>
+        <v>5.22</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.27</v>
+        <v>13.58</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.84</v>
+        <v>5.12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1444</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7221</v>
+        <v>7818</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8.82</v>
+        <v>32.45</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.06</v>
+        <v>22.68</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.06</v>
+        <v>22.68</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6.01</v>
+        <v>6.57</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>7.88</v>
+        <v>6.27</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>8.17</v>
+        <v>9.84</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9566</v>
+        <v>7221</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>39.97</v>
+        <v>8.82</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.25</v>
+        <v>21.13</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>21.25</v>
+        <v>21.13</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.16</v>
+        <v>6.02</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.57</v>
+        <v>7.09</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8.52</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1438</v>
@@ -3951,30 +3951,30 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8285</v>
+        <v>10181</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>39.07</v>
+        <v>23.43</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.23</v>
+        <v>20.1</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.23</v>
+        <v>20.1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.33</v>
+        <v>6.27</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.06</v>
+        <v>5.28</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>1434</v>
@@ -3982,188 +3982,188 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10181</v>
+        <v>8285</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>23.43</v>
+        <v>39.07</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.1</v>
+        <v>19.31</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.1</v>
+        <v>19.31</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6.27</v>
+        <v>1.34</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>12.06</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>5.28</v>
+        <v>5.91</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>17.6</v>
+        <v>21.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.45</v>
+        <v>18.93</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.45</v>
+        <v>18.93</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7.08</v>
+        <v>6.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>10</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>3.34</v>
+        <v>2.17</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>5256</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>35.18</v>
+        <v>39.97</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>17.69</v>
+        <v>17.83</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.69</v>
+        <v>17.83</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9.81</v>
+        <v>6.62</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3.91</v>
+        <v>7.29</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10664</v>
+        <v>5256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>21.7</v>
+        <v>35.18</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.3</v>
+        <v>17.69</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.3</v>
+        <v>17.69</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>6.79</v>
+        <v>3.97</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.73</v>
+        <v>9.81</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>10642</v>
+        <v>7256</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>17.14</v>
+        <v>13.97</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>17.14</v>
+        <v>13.97</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.54</v>
+        <v>5.31</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>5.76</v>
+        <v>2.85</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1422</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7256</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.23</v>
+        <v>25.63</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>12.34</v>
+        <v>13.71</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>12.34</v>
+        <v>13.71</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.53</v>
+        <v>3.89</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.47</v>
+        <v>4.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1400</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="39">
@@ -4210,22 +4210,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>6.58</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-4.9</v>
+        <v>-5.69</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-1.05</v>
+        <v>-1.2</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1337</v>
+        <v>1331</v>
       </c>
     </row>
   </sheetData>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>197.56</v>
+        <v>194.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19.53</v>
+        <v>23.1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>178.03</v>
+        <v>171.83</v>
       </c>
     </row>
     <row r="3">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>181.24</v>
+        <v>177.81</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-22.29</v>
+        <v>-2.62</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>203.53</v>
+        <v>180.43</v>
       </c>
     </row>
     <row r="4">
@@ -4324,89 +4324,89 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>151.84</v>
+        <v>162.9</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>65.48</v>
+        <v>48.48</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>86.36</v>
+        <v>114.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>131.61</v>
+        <v>134.58</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>28.77</v>
+        <v>55.24</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>102.84</v>
+        <v>79.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3875</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>130.6</v>
+        <v>134.03</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>28.77</v>
+        <v>34.99</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>101.83</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>1023</v>
+        <v>3875</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>127.36</v>
+        <v>127.32</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>40.82</v>
+        <v>33.74</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>86.54000000000001</v>
+        <v>93.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2075</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>126.85</v>
+        <v>126.87</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>51.73</v>
+        <v>45.02</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75.12</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>118.36</v>
+        <v>116.35</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>95.20999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>23.14</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="10">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115.95</v>
+        <v>115.71</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.96</v>
+        <v>-7.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.91</v>
+        <v>123.39</v>
       </c>
     </row>
     <row r="11">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>102.87</v>
+        <v>98.88</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.53</v>
+        <v>59.56</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>43.34</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="12">
@@ -4476,51 +4476,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>96.93000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-2.84</v>
+        <v>-7.24</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>99.77</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>74.97</v>
+        <v>74.69</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>27.12</v>
+        <v>52.26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>47.84</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>71.72</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56.6</v>
+        <v>29.4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.12</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>64.73999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>34.84</v>
+        <v>23.78</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>29.9</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="16">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>58.38</v>
+        <v>52.45</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45.38</v>
+        <v>49.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="17">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>55.23</v>
+        <v>51.47</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>162.55</v>
+        <v>161.15</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-107.32</v>
+        <v>-109.68</v>
       </c>
     </row>
     <row r="18">
@@ -4590,70 +4590,70 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>48.93</v>
+        <v>46.59</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22.08</v>
+        <v>19.84</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>26.85</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>7289</v>
+        <v>9638</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>42.23</v>
+        <v>46.57</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16.75</v>
+        <v>38</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>25.48</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7809</v>
+        <v>7289</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>34.28</v>
+        <v>39.41</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>150.17</v>
+        <v>16.34</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-115.89</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>9638</v>
+        <v>8767</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>32.98</v>
+        <v>33.24</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>60.84</v>
+        <v>18.77</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-27.87</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="22">
@@ -4666,32 +4666,32 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>32.65</v>
+        <v>31.52</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>25.37</v>
+        <v>41.02</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7.29</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>31.1</v>
+        <v>30.65</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>19.93</v>
+        <v>148.07</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>11.17</v>
+        <v>-117.42</v>
       </c>
     </row>
     <row r="24">
@@ -4704,13 +4704,13 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>26.71</v>
+        <v>25.39</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>53.64</v>
+        <v>50.53</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-26.93</v>
+        <v>-25.13</v>
       </c>
     </row>
     <row r="25">
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>22.83</v>
+        <v>22.54</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>70.17</v>
+        <v>65.59</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-47.34</v>
+        <v>-43.05</v>
       </c>
     </row>
     <row r="26">
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22</v>
+        <v>21.48</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>100.99</v>
+        <v>110.2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-78.98</v>
+        <v>-88.70999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -4761,13 +4761,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.8</v>
+        <v>16.64</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>54.23</v>
+        <v>51.48</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-40.43</v>
+        <v>-34.84</v>
       </c>
     </row>
     <row r="28">
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13.33</v>
+        <v>12.77</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>56.29</v>
+        <v>51.26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-42.96</v>
+        <v>-38.49</v>
       </c>
     </row>
     <row r="29">
@@ -4799,203 +4799,203 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11.58</v>
+        <v>9.93</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>71.08</v>
+        <v>71.92</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-59.5</v>
+        <v>-61.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9.85</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>91.91</v>
+        <v>47.95</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-82.06</v>
+        <v>-38.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>64.28</v>
+        <v>100.72</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-55.91</v>
+        <v>-92.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5.18</v>
+        <v>5.84</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>59.36</v>
+        <v>24.98</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-54.18</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.61</v>
+        <v>5.75</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>105.87</v>
+        <v>68.89</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-106.48</v>
+        <v>-63.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7658</v>
+        <v>9566</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-1.23</v>
+        <v>2.64</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>23.68</v>
+        <v>55.49</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-24.91</v>
+        <v>-52.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9671</v>
+        <v>7256</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.54</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>34.21</v>
+        <v>127.71</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-35.93</v>
+        <v>-129.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-4.4</v>
+        <v>-1.86</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>39.69</v>
+        <v>110.68</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-44.09</v>
+        <v>-112.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-4.89</v>
+        <v>-4.59</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63.41</v>
+        <v>23.83</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-68.3</v>
+        <v>-28.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-5.04</v>
+        <v>-6.64</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>62.26</v>
+        <v>36.99</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-67.3</v>
+        <v>-43.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7256</v>
+        <v>904</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-10.51</v>
+        <v>-8.43</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>118.28</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-128.78</v>
+        <v>-80.72</v>
       </c>
     </row>
     <row r="40">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-30.65</v>
+        <v>-23.6</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>49.31</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-79.95999999999999</v>
+        <v>-88.14</v>
       </c>
     </row>
   </sheetData>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -5157,15 +5157,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10633</v>
+        <v>2075</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BeeBotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -5182,11 +5182,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5166</v>
+        <v>10633</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>BeeBotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -5207,11 +5207,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2075</v>
+        <v>5166</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>3</v>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -5282,24 +5282,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1023</v>
+        <v>2771</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -5307,24 +5307,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>3</v>
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -5482,11 +5482,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9206</v>
+        <v>8423</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -5507,15 +5507,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>4</v>
@@ -5524,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -5532,11 +5532,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8423</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5607,24 +5607,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10642</v>
+        <v>5980</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -5632,18 +5632,18 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5980</v>
+        <v>3234</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -5657,24 +5657,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3234</v>
+        <v>9638</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -5682,24 +5682,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4325</v>
+        <v>10642</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -5732,24 +5732,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -5768,13 +5768,13 @@
         <v>3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -5782,11 +5782,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9638</v>
+        <v>5256</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5807,24 +5807,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5256</v>
+        <v>4325</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -5832,24 +5832,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -5857,15 +5857,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7818</v>
+        <v>7221</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>7</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -5882,15 +5882,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9549</v>
+        <v>9566</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>7</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -5907,18 +5907,18 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -5932,15 +5932,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7809</v>
+        <v>10664</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>7</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -5957,11 +5957,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>9671</v>
+        <v>7809</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -5993,7 +5993,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
@@ -6018,7 +6018,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>197.56</v>
+        <v>194.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.53</v>
+        <v>23.1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>178.03</v>
+        <v>171.83</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>181.24</v>
+        <v>177.81</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-22.29</v>
+        <v>-2.62</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>203.53</v>
+        <v>180.43</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>151.84</v>
+        <v>162.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>65.48</v>
+        <v>48.48</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>86.36</v>
+        <v>114.42</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6186,21 +6186,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4967</v>
+        <v>1023</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>131.61</v>
+        <v>134.58</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>28.77</v>
+        <v>55.24</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>102.84</v>
+        <v>79.34</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6209,21 +6209,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3875</v>
+        <v>2075</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>130.6</v>
+        <v>134.03</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.77</v>
+        <v>34.99</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>101.83</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6232,21 +6232,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1023</v>
+        <v>3875</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127.36</v>
+        <v>127.32</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>40.82</v>
+        <v>33.74</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>86.54000000000001</v>
+        <v>93.59</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6255,21 +6255,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2075</v>
+        <v>4967</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>126.85</v>
+        <v>126.87</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>51.73</v>
+        <v>45.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>75.12</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>118.36</v>
+        <v>116.35</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>95.20999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>23.14</v>
+        <v>21.34</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>115.95</v>
+        <v>115.71</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.96</v>
+        <v>-7.68</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>116.91</v>
+        <v>123.39</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.87</v>
+        <v>98.88</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>59.53</v>
+        <v>59.56</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>43.34</v>
+        <v>39.33</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>96.93000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-2.84</v>
+        <v>-7.24</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>99.77</v>
+        <v>101.95</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6370,21 +6370,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9756</v>
+        <v>6081</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Digital Dislocators</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>74.97</v>
+        <v>74.69</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>27.12</v>
+        <v>52.26</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>47.84</v>
+        <v>22.43</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6393,21 +6393,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6081</v>
+        <v>9756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Digital Dislocators</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>71.72</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>56.6</v>
+        <v>29.4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>15.12</v>
+        <v>41.67</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>64.73999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>34.84</v>
+        <v>23.78</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>29.9</v>
+        <v>45.68</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58.38</v>
+        <v>52.45</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45.38</v>
+        <v>49.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>13</v>
+        <v>3.08</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>55.23</v>
+        <v>51.47</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>162.55</v>
+        <v>161.15</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-107.32</v>
+        <v>-109.68</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>48.93</v>
+        <v>46.59</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>22.08</v>
+        <v>19.84</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>26.85</v>
+        <v>26.75</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6508,21 +6508,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7289</v>
+        <v>9638</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>42.23</v>
+        <v>46.57</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>16.75</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>25.48</v>
+        <v>8.57</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6531,21 +6531,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7809</v>
+        <v>7289</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>FROST BYTE  Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>34.28</v>
+        <v>39.41</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>150.17</v>
+        <v>16.34</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-115.89</v>
+        <v>23.07</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6554,21 +6554,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>9638</v>
+        <v>8767</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.98</v>
+        <v>33.24</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>60.84</v>
+        <v>18.77</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-27.87</v>
+        <v>14.47</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32.65</v>
+        <v>31.52</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>25.37</v>
+        <v>41.02</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.29</v>
+        <v>-9.5</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6600,21 +6600,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>8767</v>
+        <v>7809</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>FROST BYTE  Robotics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>31.1</v>
+        <v>30.65</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>19.93</v>
+        <v>148.07</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.17</v>
+        <v>-117.42</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>26.71</v>
+        <v>25.39</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>53.64</v>
+        <v>50.53</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-26.93</v>
+        <v>-25.13</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6654,13 +6654,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>22.83</v>
+        <v>22.54</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>70.17</v>
+        <v>65.59</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-47.34</v>
+        <v>-43.05</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6677,13 +6677,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22</v>
+        <v>21.48</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>100.99</v>
+        <v>110.2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-78.98</v>
+        <v>-88.70999999999999</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>13.8</v>
+        <v>16.64</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>54.23</v>
+        <v>51.48</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-40.43</v>
+        <v>-34.84</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.33</v>
+        <v>12.77</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>56.29</v>
+        <v>51.26</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-42.96</v>
+        <v>-38.49</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.58</v>
+        <v>9.93</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>71.08</v>
+        <v>71.92</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-59.5</v>
+        <v>-61.99</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6761,21 +6761,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7221</v>
+        <v>9549</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9.85</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>91.91</v>
+        <v>47.95</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-82.06</v>
+        <v>-38.66</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6784,21 +6784,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5256</v>
+        <v>7221</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>64.28</v>
+        <v>100.72</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-55.91</v>
+        <v>-92.42</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6807,21 +6807,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9566</v>
+        <v>9671</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.18</v>
+        <v>5.84</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>59.36</v>
+        <v>24.98</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-54.18</v>
+        <v>-19.15</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6830,21 +6830,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>7818</v>
+        <v>5256</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-0.61</v>
+        <v>5.75</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>105.87</v>
+        <v>68.89</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-106.48</v>
+        <v>-63.14</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -6853,21 +6853,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7658</v>
+        <v>9566</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-1.23</v>
+        <v>2.64</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>23.68</v>
+        <v>55.49</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-24.91</v>
+        <v>-52.85</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -6876,21 +6876,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9671</v>
+        <v>7256</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.54</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>34.21</v>
+        <v>127.71</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-35.93</v>
+        <v>-129.25</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -6899,21 +6899,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>10642</v>
+        <v>7818</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-4.4</v>
+        <v>-1.86</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>39.69</v>
+        <v>110.68</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-44.09</v>
+        <v>-112.54</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -6922,21 +6922,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>904</v>
+        <v>7658</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-4.89</v>
+        <v>-4.59</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>63.41</v>
+        <v>23.83</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-68.3</v>
+        <v>-28.42</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -6945,21 +6945,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>9549</v>
+        <v>10642</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-5.04</v>
+        <v>-6.64</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>62.26</v>
+        <v>36.99</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-67.3</v>
+        <v>-43.63</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -6968,21 +6968,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7256</v>
+        <v>904</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-10.51</v>
+        <v>-8.43</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>118.28</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-128.78</v>
+        <v>-80.72</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-30.65</v>
+        <v>-23.6</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>49.31</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-79.95999999999999</v>
+        <v>-88.14</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -634,25 +634,25 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>175.88</v>
+        <v>174.09</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-5.47</v>
+        <v>-7.02</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>181.35</v>
+        <v>181.12</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>136.6</v>
+        <v>138.22</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>136.6</v>
+        <v>138.22</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1673</v>
@@ -661,10 +661,10 @@
         <v>25.3</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.14</v>
+        <v>78.3</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33.16</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="3">
@@ -697,13 +697,13 @@
         <v>46</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>170.14</v>
+        <v>169.29</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>33.12</v>
+        <v>33.97</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>137.02</v>
+        <v>135.32</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>45.04</v>
@@ -757,13 +757,13 @@
         <v>43</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>187.47</v>
+        <v>187.65</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>44.72</v>
+        <v>42.79</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>142.75</v>
+        <v>144.87</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>45.8</v>
@@ -817,13 +817,13 @@
         <v>43</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>139.14</v>
+        <v>138.34</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>33.39</v>
+        <v>33.43</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>105.75</v>
+        <v>104.9</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>88.79000000000001</v>
@@ -849,23 +849,23 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Belmont, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>3</v>
@@ -874,238 +874,238 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>124.04</v>
+        <v>117.55</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42.12</v>
+        <v>48.15</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>81.93000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>68.89</v>
+        <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>112.68</v>
+        <v>94.66</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>112.68</v>
+        <v>94.66</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1641</v>
+        <v>1607</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>23.79</v>
+        <v>13.11</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>60.45</v>
+        <v>58.71</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>28.44</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Grandville, Michigan</t>
+          <t>Temperance, Michigan</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>92.84</v>
+        <v>138.47</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>67.88</v>
+        <v>67.69</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>24.96</v>
+        <v>70.78</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>53.52</v>
+        <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>80.09</v>
+        <v>131.85</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>80.09</v>
+        <v>131.85</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1578</v>
+        <v>1667</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>7.65</v>
+        <v>24.01</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>51.35</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>21.09</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3875</v>
+        <v>5166</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Freeland, Michigan</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>119.38</v>
+        <v>107.06</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>47.13</v>
+        <v>13.81</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>72.25</v>
+        <v>93.25</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>50.66</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>94.66</v>
+        <v>102.78</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>94.66</v>
+        <v>102.78</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1607</v>
+        <v>1622</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>13.11</v>
+        <v>17.95</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>58.71</v>
+        <v>60.68</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>22.83</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Temperance, Michigan</t>
+          <t>Belmont, Michigan</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>132.96</v>
+        <v>127.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>64.18000000000001</v>
+        <v>42.8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>68.77</v>
+        <v>85.12</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>68.08</v>
+        <v>68.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>127.31</v>
+        <v>114.35</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>127.31</v>
+        <v>114.35</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1661</v>
+        <v>1643</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>22.88</v>
+        <v>23.61</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>78.59</v>
+        <v>61.44</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>25.84</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Michigan Center, Michigan</t>
+          <t>Grandville, Michigan</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
@@ -1114,51 +1114,51 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>106.93</v>
+        <v>90.75</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.69</v>
+        <v>69.13</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>21.62</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>50.91</v>
+        <v>53.52</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>96.15000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>96.15000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1610</v>
+        <v>1572</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>11.59</v>
+        <v>7.64</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>57.16</v>
+        <v>49.74</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>27.4</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Freeland, Michigan</t>
+          <t>Michigan Center, Michigan</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1174,37 +1174,37 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>107.89</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.28</v>
+        <v>32.71</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>94.61</v>
+        <v>67.28</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>102.78</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102.78</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1622</v>
+        <v>1606</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>17.95</v>
+        <v>10.97</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>60.68</v>
+        <v>57.49</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>24.15</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="12">
@@ -1237,13 +1237,13 @@
         <v>35</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.43</v>
+        <v>36.41</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>63.69</v>
+        <v>59.83</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-29.26</v>
+        <v>-23.42</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>44.43</v>
@@ -1269,23 +1269,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>858</v>
+        <v>9756</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Wyoming, Michigan</t>
+          <t>Hesperia, Michigan</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>5</v>
@@ -1294,51 +1294,51 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>112.9</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>75.79000000000001</v>
+        <v>22.26</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>37.11</v>
+        <v>44.45</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>55.1</v>
+        <v>29.21</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>77.95</v>
+        <v>56.29</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>77.95</v>
+        <v>56.29</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1573</v>
+        <v>1529</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>12.68</v>
+        <v>7.24</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>38.22</v>
+        <v>33.82</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>27.05</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9756</v>
+        <v>858</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Hesperia, Michigan</t>
+          <t>Wyoming, Michigan</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1348,43 +1348,43 @@
         <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>69.56</v>
+        <v>106.13</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.67</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>47.89</v>
+        <v>13.96</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>29.21</v>
+        <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>54.67</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>54.67</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1526</v>
+        <v>1569</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>7.24</v>
+        <v>12.05</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>33.67</v>
+        <v>38.55</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>13.76</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="15">
@@ -1417,13 +1417,13 @@
         <v>29</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>70.86</v>
+        <v>71.58</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>63.32</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>6.54</v>
+        <v>8.26</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>59.73</v>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>5</v>
@@ -1474,37 +1474,37 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>64.92</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26.84</v>
+        <v>32.26</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>38.09</v>
+        <v>36.76</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>28.04</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>55.69</v>
+        <v>60.23</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>55.69</v>
+        <v>60.23</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>9.26</v>
+        <v>10.4</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>30.52</v>
+        <v>33.36</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>15.9</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="17">
@@ -1525,7 +1525,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>5</v>
@@ -1534,51 +1534,51 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.45</v>
+        <v>15.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>58.04</v>
+        <v>56.52</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-45.59</v>
+        <v>-40.62</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>23.74</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>22.47</v>
+        <v>24.14</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.47</v>
+        <v>24.14</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>13.43</v>
+        <v>14.42</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.43</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9206</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>North Branch, Michigan</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1588,117 +1588,117 @@
         <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.93</v>
+        <v>36.46</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>47.48</v>
+        <v>27.89</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-31.55</v>
+        <v>8.57</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>21.07</v>
+        <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25.68</v>
+        <v>43.42</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>25.68</v>
+        <v>43.42</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1454</v>
+        <v>1501</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.97</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>16.21</v>
+        <v>25.18</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>8.77</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bay City, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>47.08</v>
+        <v>56.51</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>51.91</v>
+        <v>71.81</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-4.83</v>
+        <v>-15.3</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>27.75</v>
+        <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>54.37</v>
+        <v>45.18</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>54.37</v>
+        <v>45.18</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>21.64</v>
+        <v>6.98</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.09</v>
+        <v>26.54</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>18.64</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7289</v>
+        <v>10642</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fowler, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1708,117 +1708,117 @@
         <v>6</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37.73</v>
+        <v>-5.07</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-2.17</v>
+        <v>40.85</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>39.9</v>
+        <v>-45.92</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>33.29</v>
+        <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30.92</v>
+        <v>14.9</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>30.92</v>
+        <v>14.9</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1469</v>
+        <v>1411</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>12.05</v>
+        <v>4.13</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>7.63</v>
+        <v>5.22</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>11.23</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>5980</v>
+        <v>9685</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Bay City, Michigan</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>57.96</v>
+        <v>44.99</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>72.03</v>
+        <v>50.31</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-14.07</v>
+        <v>-5.32</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>38.55</v>
+        <v>27.75</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>45.18</v>
+        <v>51.91</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>45.18</v>
+        <v>51.91</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1505</v>
+        <v>1520</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6.98</v>
+        <v>21.63</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>26.54</v>
+        <v>12.48</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>11.65</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Lake Odessa, Michigan</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1834,51 +1834,51 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-4.65</v>
+        <v>14.24</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43.96</v>
+        <v>31.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-48.62</v>
+        <v>-16.86</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>25.63</v>
+        <v>35.18</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>14.9</v>
+        <v>21.96</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>14.9</v>
+        <v>21.96</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1411</v>
+        <v>1441</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>5.22</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>5.55</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>5256</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Lake Odessa, Michigan</t>
+          <t>Fowler, Michigan</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1897,55 +1897,55 @@
         <v>24</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>13.48</v>
+        <v>30.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>30.77</v>
+        <v>13.12</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-17.29</v>
+        <v>17.38</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>35.18</v>
+        <v>33.29</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>21.96</v>
+        <v>29.12</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>21.96</v>
+        <v>29.12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1441</v>
+        <v>1464</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.08</v>
+        <v>11.43</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>8.66</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>North Branch, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>6</v>
@@ -1954,37 +1954,37 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.51</v>
+        <v>19.35</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25.66</v>
+        <v>46.89</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3.85</v>
+        <v>-27.53</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>27.21</v>
+        <v>21.07</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>38.87</v>
+        <v>26.39</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>38.87</v>
+        <v>26.39</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>5.83</v>
+        <v>0.93</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>22.34</v>
+        <v>16.79</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>10.7</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="25">
@@ -2017,13 +2017,13 @@
         <v>23</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>82.8</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-80.44</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>25.23</v>
@@ -2077,13 +2077,13 @@
         <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14.76</v>
+        <v>15.26</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50.41</v>
+        <v>46.88</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-35.65</v>
+        <v>-31.62</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>24.37</v>
@@ -2137,13 +2137,13 @@
         <v>23</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>47.8</v>
+        <v>46.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-35.36</v>
+        <v>-34.08</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>22.62</v>
@@ -2197,13 +2197,13 @@
         <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>50.4</v>
+        <v>49.22</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>141.2</v>
+        <v>139.65</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>-90.8</v>
+        <v>-90.43000000000001</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>32.52</v>
@@ -2229,16 +2229,16 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>10181</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Michigan</t>
+          <t>Fife Lake, Michigan</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -2257,48 +2257,48 @@
         <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>12.71</v>
+        <v>20.4</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>92.14</v>
+        <v>54.49</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-79.44</v>
+        <v>-34.09</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.82</v>
+        <v>23.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>24.92</v>
+        <v>20.09</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>24.92</v>
+        <v>20.09</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1451</v>
+        <v>1433</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>4.78</v>
+        <v>5.46</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>12.55</v>
+        <v>7</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.58</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Gobles, Michigan</t>
+          <t>Jackson, Michigan</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -2308,57 +2308,57 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40.25</v>
+        <v>13.17</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>48.62</v>
+        <v>90.62</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>-8.380000000000001</v>
+        <v>-77.45</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>22.93</v>
+        <v>8.82</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31.39</v>
+        <v>24.92</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>31.39</v>
+        <v>24.92</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1471</v>
+        <v>1451</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>7.84</v>
+        <v>4.78</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>15.65</v>
+        <v>12.55</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>7.89</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Kentwood, Michigan</t>
+          <t>Gobles, Michigan</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -2377,48 +2377,48 @@
         <v>18</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.2</v>
+        <v>36.49</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>55.98</v>
+        <v>48.84</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-45.79</v>
+        <v>-12.35</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>39.97</v>
+        <v>22.93</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.04</v>
+        <v>28.93</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>19.04</v>
+        <v>28.93</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1429</v>
+        <v>1463</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4.24</v>
+        <v>7.84</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>7.98</v>
+        <v>14.04</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>6.82</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ravenna, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -2434,58 +2434,58 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.21</v>
+        <v>8.77</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>108.72</v>
+        <v>37.76</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-90.51000000000001</v>
+        <v>-28.99</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>39.07</v>
+        <v>27.39</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>21.36</v>
+        <v>29.5</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>21.36</v>
+        <v>29.5</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.92</v>
+        <v>7.22</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>11.25</v>
+        <v>16.25</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>9.19</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>10181</v>
+        <v>9566</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Fife Lake, Michigan</t>
+          <t>Kentwood, Michigan</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>8</v>
@@ -2494,111 +2494,111 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>23.51</v>
+        <v>10.64</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>55.33</v>
+        <v>54.15</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-31.82</v>
+        <v>-43.51</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>23.43</v>
+        <v>39.97</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.47</v>
+        <v>19.04</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>18.47</v>
+        <v>19.04</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.46</v>
+        <v>4.24</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>6.84</v>
+        <v>7.98</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>6.17</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9549</v>
+        <v>8285</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Covert, Michigan</t>
+          <t>Ravenna, Michigan</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.63</v>
+        <v>17.41</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>71.45</v>
+        <v>106.68</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-59.82</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>17.6</v>
+        <v>39.07</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5.49</v>
+        <v>0.92</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>11.41</v>
+        <v>11.25</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>4.81</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9671</v>
+        <v>9549</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Covert, Michigan</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2608,57 +2608,57 @@
         <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.97</v>
+        <v>12.11</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>39.33</v>
+        <v>68.97</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-35.36</v>
+        <v>-56.86</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>27.39</v>
+        <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>27.83</v>
+        <v>21.72</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>27.83</v>
+        <v>21.72</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1460</v>
+        <v>1439</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.41</v>
+        <v>5.49</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>15.26</v>
+        <v>11.41</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>5.16</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Grand Rapids, Michigan</t>
+          <t>Williamston, Michigan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2668,57 +2668,57 @@
         <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-15.91</v>
+        <v>1.34</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>52.78</v>
+        <v>83.34</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-68.69</v>
+        <v>-82</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>27.91</v>
+        <v>32.45</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-1.31</v>
+        <v>19.56</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.31</v>
+        <v>19.56</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1324</v>
+        <v>1431</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5.95</v>
+        <v>6.92</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>-6.49</v>
+        <v>4.65</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-0.77</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston, Michigan</t>
+          <t>Muskegon, Michigan</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2737,118 +2737,118 @@
         <v>14</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.65</v>
+        <v>-14.46</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>86.92</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-86.27</v>
+        <v>-82.47</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>32.45</v>
+        <v>21.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.56</v>
+        <v>19.12</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.56</v>
+        <v>19.12</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.92</v>
+        <v>4.84</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>4.65</v>
+        <v>11.44</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>7.99</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10664</v>
+        <v>7658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Muskegon, Michigan</t>
+          <t>Kalamazoo, Michigan</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-14.78</v>
+        <v>12.94</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>70.41</v>
+        <v>52.24</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-85.19</v>
+        <v>-39.3</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>21.7</v>
+        <v>14.34</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>19.12</v>
+        <v>21.13</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>19.12</v>
+        <v>21.13</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>4.84</v>
+        <v>2.83</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>11.44</v>
+        <v>12.4</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>2.83</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kalamazoo, Michigan</t>
+          <t>Grand Rapids, Michigan</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
         <v>38</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2857,34 +2857,34 @@
         <v>13</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.67</v>
+        <v>-12.13</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>54.65</v>
+        <v>53.52</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-41.98</v>
+        <v>-65.65000000000001</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>14.34</v>
+        <v>27.91</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>21.13</v>
+        <v>-0.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>21.13</v>
+        <v>-0.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1438</v>
+        <v>1329</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.83</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>12.4</v>
+        <v>-5.92</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>5.9</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="40">
@@ -2908,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         <v>10</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.91</v>
+        <v>32.49</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>110.62</v>
+        <v>114.22</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-80.70999999999999</v>
+        <v>-81.73</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>23.83</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32.05</v>
+        <v>32.76</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>32.05</v>
+        <v>32.76</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>16.69</v>
+        <v>17.26</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>12.49</v>
+        <v>12.39</v>
       </c>
     </row>
   </sheetData>
@@ -3094,19 +3094,19 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>136.6</v>
+        <v>138.22</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>136.6</v>
+        <v>138.22</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>25.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.14</v>
+        <v>78.3</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>33.16</v>
+        <v>34.62</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1673</v>
@@ -3156,22 +3156,22 @@
         <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>127.31</v>
+        <v>131.85</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>127.31</v>
+        <v>131.85</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22.88</v>
+        <v>24.01</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>78.59</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.84</v>
+        <v>26.41</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1661</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="7">
@@ -3187,22 +3187,22 @@
         <v>68.89</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>112.68</v>
+        <v>114.35</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112.68</v>
+        <v>114.35</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.79</v>
+        <v>23.61</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>60.45</v>
+        <v>61.44</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>28.44</v>
+        <v>29.3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="8">
@@ -3238,64 +3238,64 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7656</v>
+        <v>3875</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50.91</v>
+        <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>94.66</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>94.66</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>11.59</v>
+        <v>13.11</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.16</v>
+        <v>58.71</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>27.4</v>
+        <v>22.83</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3875</v>
+        <v>7656</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50.66</v>
+        <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>94.66</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.66</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13.11</v>
+        <v>10.97</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>58.71</v>
+        <v>57.49</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>22.83</v>
+        <v>25.89</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="11">
@@ -3311,22 +3311,22 @@
         <v>53.52</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>80.09</v>
+        <v>77.63</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>80.09</v>
+        <v>77.63</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>7.65</v>
+        <v>7.64</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.35</v>
+        <v>49.74</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>21.09</v>
+        <v>20.25</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1578</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="12">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>77.95</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>77.95</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.68</v>
+        <v>12.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.22</v>
+        <v>38.55</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>27.05</v>
+        <v>25.54</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1573</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="13">
@@ -3393,64 +3393,64 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9208</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Eddies Circuit</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44.43</v>
+        <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>58.59</v>
+        <v>60.23</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58.59</v>
+        <v>60.23</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14.44</v>
+        <v>10.4</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30.34</v>
+        <v>33.36</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>13.82</v>
+        <v>16.47</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9208</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Eddies Circuit</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>28.04</v>
+        <v>44.43</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>55.69</v>
+        <v>58.59</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>55.69</v>
+        <v>58.59</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9.26</v>
+        <v>14.44</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>30.52</v>
+        <v>30.34</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>15.9</v>
+        <v>13.82</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1528</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="16">
@@ -3466,22 +3466,22 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>54.67</v>
+        <v>56.29</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.67</v>
+        <v>56.29</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>7.24</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>33.67</v>
+        <v>33.82</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>13.76</v>
+        <v>15.22</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1526</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="17">
@@ -3497,22 +3497,22 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>54.37</v>
+        <v>51.91</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>54.37</v>
+        <v>51.91</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.64</v>
+        <v>21.63</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14.09</v>
+        <v>12.48</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.64</v>
+        <v>17.79</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="18">
@@ -3548,64 +3548,64 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4325</v>
+        <v>8767</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RoboRangers</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.52</v>
+        <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.4</v>
+        <v>43.42</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.4</v>
+        <v>43.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.04</v>
+        <v>6.97</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.5</v>
+        <v>25.18</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>11.27</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1492</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8767</v>
+        <v>4325</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>RoboRangers</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.21</v>
+        <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>38.87</v>
+        <v>39.4</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38.87</v>
+        <v>39.4</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.83</v>
+        <v>10.04</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>22.34</v>
+        <v>20.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.7</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="21">
@@ -3621,53 +3621,53 @@
         <v>23.83</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.05</v>
+        <v>32.76</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>32.05</v>
+        <v>32.76</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16.69</v>
+        <v>17.26</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.49</v>
+        <v>12.39</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9638</v>
+        <v>9671</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>22.93</v>
+        <v>27.39</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>31.39</v>
+        <v>29.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>31.39</v>
+        <v>29.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7.84</v>
+        <v>7.22</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15.65</v>
+        <v>16.25</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>7.89</v>
+        <v>6.03</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1471</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="23">
@@ -3683,84 +3683,84 @@
         <v>33.29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>30.92</v>
+        <v>29.12</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>30.92</v>
+        <v>29.12</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.05</v>
+        <v>11.43</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.63</v>
+        <v>7.97</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11.23</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1469</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7808</v>
+        <v>9638</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>24.37</v>
+        <v>22.93</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.23</v>
+        <v>28.93</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.23</v>
+        <v>28.93</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.23</v>
+        <v>7.84</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12.97</v>
+        <v>14.04</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.04</v>
+        <v>7.05</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>9671</v>
+        <v>7808</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>27.39</v>
+        <v>24.37</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>27.83</v>
+        <v>28.23</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>27.83</v>
+        <v>28.23</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7.41</v>
+        <v>5.23</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>15.26</v>
+        <v>12.97</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>5.16</v>
+        <v>10.04</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="26">
@@ -3776,22 +3776,22 @@
         <v>21.07</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>25.68</v>
+        <v>26.39</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.68</v>
+        <v>26.39</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>16.21</v>
+        <v>16.79</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>8.77</v>
+        <v>8.67</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="27">
@@ -3838,22 +3838,22 @@
         <v>23.74</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>22.47</v>
+        <v>24.14</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>22.47</v>
+        <v>24.14</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>13.43</v>
+        <v>14.42</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4.43</v>
+        <v>5.29</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="29">
@@ -3982,126 +3982,126 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7818</v>
+        <v>10181</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>32.45</v>
+        <v>23.43</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>19.56</v>
+        <v>20.09</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.56</v>
+        <v>20.09</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6.92</v>
+        <v>5.46</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.65</v>
+        <v>7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.99</v>
+        <v>7.63</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10664</v>
+        <v>7818</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>21.7</v>
+        <v>32.45</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.12</v>
+        <v>19.56</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.12</v>
+        <v>19.56</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4.84</v>
+        <v>6.92</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.44</v>
+        <v>4.65</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2.83</v>
+        <v>7.99</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>9566</v>
+        <v>10664</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>39.97</v>
+        <v>21.7</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.04</v>
+        <v>19.12</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.04</v>
+        <v>19.12</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.24</v>
+        <v>4.84</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>7.98</v>
+        <v>11.44</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6.82</v>
+        <v>2.83</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>10181</v>
+        <v>9566</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.43</v>
+        <v>39.97</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.47</v>
+        <v>19.04</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.47</v>
+        <v>19.04</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.46</v>
+        <v>4.24</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6.84</v>
+        <v>7.98</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6.17</v>
+        <v>6.82</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="37">
@@ -4210,22 +4210,22 @@
         <v>27.91</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-1.31</v>
+        <v>-0.6</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-1.31</v>
+        <v>-0.6</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>5.95</v>
+        <v>6.18</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-6.49</v>
+        <v>-5.92</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.87</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1324</v>
+        <v>1329</v>
       </c>
     </row>
   </sheetData>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>187.47</v>
+        <v>187.65</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44.72</v>
+        <v>42.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>142.75</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="3">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>175.88</v>
+        <v>174.09</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-5.47</v>
+        <v>-7.02</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>181.35</v>
+        <v>181.12</v>
       </c>
     </row>
     <row r="4">
@@ -4324,51 +4324,51 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>170.14</v>
+        <v>169.29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33.12</v>
+        <v>33.97</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>137.02</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>139.14</v>
+        <v>138.47</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>33.39</v>
+        <v>67.69</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>105.75</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>132.96</v>
+        <v>138.34</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>33.43</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>68.77</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="7">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>124.04</v>
+        <v>127.92</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42.12</v>
+        <v>42.8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>81.93000000000001</v>
+        <v>85.12</v>
       </c>
     </row>
     <row r="8">
@@ -4400,51 +4400,51 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>119.38</v>
+        <v>117.55</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>47.13</v>
+        <v>48.15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>72.25</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>112.9</v>
+        <v>107.06</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>75.79000000000001</v>
+        <v>13.81</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>37.11</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>107.89</v>
+        <v>106.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13.28</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.61</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="11">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>106.93</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16.69</v>
+        <v>32.71</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>90.23999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="12">
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>92.84</v>
+        <v>90.75</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>67.88</v>
+        <v>69.13</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24.96</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="13">
@@ -4495,51 +4495,51 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>70.86</v>
+        <v>71.58</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>63.32</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6.54</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>69.56</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21.67</v>
+        <v>32.26</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>47.89</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>64.92</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>26.84</v>
+        <v>22.26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>38.09</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="16">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>57.96</v>
+        <v>56.51</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>72.03</v>
+        <v>71.81</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-14.07</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="17">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>50.4</v>
+        <v>49.22</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>141.2</v>
+        <v>139.65</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-90.8</v>
+        <v>-90.43000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>47.08</v>
+        <v>44.99</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>51.91</v>
+        <v>50.31</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-4.83</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="19">
@@ -4609,32 +4609,32 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.25</v>
+        <v>36.49</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>48.62</v>
+        <v>48.84</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-12.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7289</v>
+        <v>8767</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>37.73</v>
+        <v>36.46</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-2.17</v>
+        <v>27.89</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.9</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="21">
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>34.43</v>
+        <v>36.41</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>63.69</v>
+        <v>59.83</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-29.26</v>
+        <v>-23.42</v>
       </c>
     </row>
     <row r="22">
@@ -4666,32 +4666,32 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>29.91</v>
+        <v>32.49</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>110.62</v>
+        <v>114.22</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-80.70999999999999</v>
+        <v>-81.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29.51</v>
+        <v>30.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>25.66</v>
+        <v>13.12</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.85</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="24">
@@ -4704,165 +4704,165 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.51</v>
+        <v>20.4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>55.33</v>
+        <v>54.49</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-31.82</v>
+        <v>-34.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>18.21</v>
+        <v>19.35</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>108.72</v>
+        <v>46.89</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-90.51000000000001</v>
+        <v>-27.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9206</v>
+        <v>8285</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>15.93</v>
+        <v>17.41</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>47.48</v>
+        <v>106.68</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-31.55</v>
+        <v>-89.26000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>14.76</v>
+        <v>15.9</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>50.41</v>
+        <v>56.52</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-35.65</v>
+        <v>-40.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5256</v>
+        <v>7808</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13.48</v>
+        <v>15.26</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>30.77</v>
+        <v>46.88</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-17.29</v>
+        <v>-31.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>7221</v>
+        <v>5256</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.71</v>
+        <v>14.24</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>92.14</v>
+        <v>31.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-79.44</v>
+        <v>-16.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>12.67</v>
+        <v>13.17</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>54.65</v>
+        <v>90.62</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-41.98</v>
+        <v>-77.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3234</v>
+        <v>7658</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>12.45</v>
+        <v>12.94</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>47.8</v>
+        <v>52.24</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-35.36</v>
+        <v>-39.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>58.04</v>
+        <v>46.5</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-45.59</v>
+        <v>-34.08</v>
       </c>
     </row>
     <row r="33">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>11.63</v>
+        <v>12.11</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>71.45</v>
+        <v>68.97</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-59.82</v>
+        <v>-56.86</v>
       </c>
     </row>
     <row r="34">
@@ -4894,13 +4894,13 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>55.98</v>
+        <v>54.15</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-45.79</v>
+        <v>-43.51</v>
       </c>
     </row>
     <row r="35">
@@ -4913,13 +4913,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>3.97</v>
+        <v>8.77</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>39.33</v>
+        <v>37.76</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-35.36</v>
+        <v>-28.99</v>
       </c>
     </row>
     <row r="36">
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>82.8</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-80.44</v>
+        <v>-78.29000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.65</v>
+        <v>1.34</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>86.92</v>
+        <v>83.34</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-86.27</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="38">
@@ -4970,51 +4970,51 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-4.65</v>
+        <v>-5.07</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>43.96</v>
+        <v>40.85</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-48.62</v>
+        <v>-45.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-14.78</v>
+        <v>-12.13</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>70.41</v>
+        <v>53.52</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-85.19</v>
+        <v>-65.65000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>904</v>
+        <v>10664</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-15.91</v>
+        <v>-14.46</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>52.78</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-68.69</v>
+        <v>-82.47</v>
       </c>
     </row>
   </sheetData>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -5182,15 +5182,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4967</v>
+        <v>3875</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>That ONE Team-OurNextEngineers</t>
+          <t>Red Storm Robotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>3</v>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -5207,24 +5207,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Code Red Robotics the Stray Dogs</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -5232,24 +5232,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3875</v>
+        <v>5166</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -5257,24 +5257,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>That ONE Team-OurNextEngineers</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -5282,15 +5282,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7656</v>
+        <v>2771</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MC Hammers</t>
+          <t>Code Red Robotics the Stray Dogs</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
@@ -5299,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -5307,11 +5307,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5166</v>
+        <v>7656</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>MC Hammers</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -5357,15 +5357,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>858</v>
+        <v>9756</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>5</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -5382,24 +5382,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9756</v>
+        <v>858</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>5</v>
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>5</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -5482,24 +5482,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9206</v>
+        <v>8767</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -5507,24 +5507,24 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9685</v>
+        <v>5980</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Crystal Oscillators</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -5532,24 +5532,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7289</v>
+        <v>10642</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -5557,24 +5557,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5980</v>
+        <v>9685</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Crystal Oscillators</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -5582,11 +5582,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10642</v>
+        <v>5256</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -5607,11 +5607,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5256</v>
+        <v>7289</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -5632,15 +5632,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8767</v>
+        <v>9206</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>6</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -5757,11 +5757,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7221</v>
+        <v>10181</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -5782,24 +5782,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tigers, Bro!</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -5807,11 +5807,11 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9566</v>
+        <v>9638</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Tigers, Bro!</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -5832,11 +5832,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8285</v>
+        <v>9671</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>Robosnacks</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -5857,15 +5857,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10181</v>
+        <v>9566</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>8</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -5882,24 +5882,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>9549</v>
+        <v>8285</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>The Mechadogs</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -5907,24 +5907,24 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>9671</v>
+        <v>9549</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Robosnacks</t>
+          <t>The Mechadogs</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -5932,24 +5932,24 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>904</v>
+        <v>7818</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Williamston High School Vespidae</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -5957,11 +5957,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>7818</v>
+        <v>10664</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Williamston High School Vespidae</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -5982,24 +5982,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>10664</v>
+        <v>7658</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -6007,18 +6007,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7658</v>
+        <v>904</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>187.47</v>
+        <v>187.65</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>44.72</v>
+        <v>42.79</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>142.75</v>
+        <v>144.87</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>175.88</v>
+        <v>174.09</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-5.47</v>
+        <v>-7.02</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>181.35</v>
+        <v>181.12</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>170.14</v>
+        <v>169.29</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.12</v>
+        <v>33.97</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>137.02</v>
+        <v>135.32</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
@@ -6186,21 +6186,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>139.14</v>
+        <v>138.47</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>33.39</v>
+        <v>67.69</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>105.75</v>
+        <v>70.78</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -6209,21 +6209,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>132.96</v>
+        <v>138.34</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>33.43</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>68.77</v>
+        <v>104.9</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
@@ -6240,13 +6240,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>124.04</v>
+        <v>127.92</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>42.12</v>
+        <v>42.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>81.93000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>119.38</v>
+        <v>117.55</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.13</v>
+        <v>48.15</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>72.25</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
@@ -6278,21 +6278,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>858</v>
+        <v>5166</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Demons Robotics</t>
+          <t>Fabricators</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>112.9</v>
+        <v>107.06</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>75.79000000000001</v>
+        <v>13.81</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>37.11</v>
+        <v>93.25</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -6301,21 +6301,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5166</v>
+        <v>858</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fabricators</t>
+          <t>Demons Robotics</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>107.89</v>
+        <v>106.13</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.28</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>94.61</v>
+        <v>13.96</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>106.93</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.69</v>
+        <v>32.71</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>90.23999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>92.84</v>
+        <v>90.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>67.88</v>
+        <v>69.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>24.96</v>
+        <v>21.62</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>70.86</v>
+        <v>71.58</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>63.32</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6.54</v>
+        <v>8.26</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -6393,21 +6393,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9756</v>
+        <v>8423</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Robo Panthers</t>
+          <t>Next Express</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>69.56</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21.67</v>
+        <v>32.26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>47.89</v>
+        <v>36.76</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
@@ -6416,21 +6416,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8423</v>
+        <v>9756</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Next Express</t>
+          <t>Robo Panthers</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>64.92</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>26.84</v>
+        <v>22.26</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>38.09</v>
+        <v>44.45</v>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>57.96</v>
+        <v>56.51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>72.03</v>
+        <v>71.81</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-14.07</v>
+        <v>-15.3</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50.4</v>
+        <v>49.22</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>141.2</v>
+        <v>139.65</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-90.8</v>
+        <v>-90.43000000000001</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>47.08</v>
+        <v>44.99</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>51.91</v>
+        <v>50.31</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4.83</v>
+        <v>-5.32</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
@@ -6516,13 +6516,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40.25</v>
+        <v>36.49</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>48.62</v>
+        <v>48.84</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-12.35</v>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
     </row>
@@ -6531,21 +6531,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7289</v>
+        <v>8767</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Blue Eagles</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.73</v>
+        <v>36.46</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-2.17</v>
+        <v>27.89</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>39.9</v>
+        <v>8.57</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>34.43</v>
+        <v>36.41</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>63.69</v>
+        <v>59.83</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-29.26</v>
+        <v>-23.42</v>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
     </row>
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>29.91</v>
+        <v>32.49</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>110.62</v>
+        <v>114.22</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-80.70999999999999</v>
+        <v>-81.73</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -6600,21 +6600,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>8767</v>
+        <v>7289</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>Blue Eagles</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>29.51</v>
+        <v>30.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>25.66</v>
+        <v>13.12</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.85</v>
+        <v>17.38</v>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
     </row>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>23.51</v>
+        <v>20.4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>55.33</v>
+        <v>54.49</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-31.82</v>
+        <v>-34.09</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6646,21 +6646,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>8285</v>
+        <v>9206</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Bionic Bulldogs</t>
+          <t>GRP Titans</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>18.21</v>
+        <v>19.35</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>108.72</v>
+        <v>46.89</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-90.51000000000001</v>
+        <v>-27.53</v>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
     </row>
@@ -6669,21 +6669,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>9206</v>
+        <v>8285</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GRP Titans</t>
+          <t>Bionic Bulldogs</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>15.93</v>
+        <v>17.41</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>47.48</v>
+        <v>106.68</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-31.55</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6692,21 +6692,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7808</v>
+        <v>11399</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kalkaska Dragoneers</t>
+          <t>Timber Tech</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>14.76</v>
+        <v>15.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>50.41</v>
+        <v>56.52</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-35.65</v>
+        <v>-40.62</v>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
     </row>
@@ -6715,21 +6715,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5256</v>
+        <v>7808</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Atomics</t>
+          <t>Kalkaska Dragoneers</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.48</v>
+        <v>15.26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>30.77</v>
+        <v>46.88</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-17.29</v>
+        <v>-31.62</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6738,21 +6738,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7221</v>
+        <v>5256</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Viking Robotics</t>
+          <t>Atomics</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.71</v>
+        <v>14.24</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>92.14</v>
+        <v>31.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-79.44</v>
+        <v>-16.86</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
     </row>
@@ -6761,21 +6761,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7658</v>
+        <v>7221</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>MagiTech</t>
+          <t>Viking Robotics</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12.67</v>
+        <v>13.17</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.65</v>
+        <v>90.62</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-41.98</v>
+        <v>-77.45</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
@@ -6784,21 +6784,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3234</v>
+        <v>7658</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>MagiTech</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>12.45</v>
+        <v>12.94</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>47.8</v>
+        <v>52.24</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-35.36</v>
+        <v>-39.3</v>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
     </row>
@@ -6807,21 +6807,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>11399</v>
+        <v>3234</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Timber Tech</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>58.04</v>
+        <v>46.5</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-45.59</v>
+        <v>-34.08</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
@@ -6838,13 +6838,13 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>11.63</v>
+        <v>12.11</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>71.45</v>
+        <v>68.97</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-59.82</v>
+        <v>-56.86</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
     </row>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>55.98</v>
+        <v>54.15</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-45.79</v>
+        <v>-43.51</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
@@ -6884,13 +6884,13 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3.97</v>
+        <v>8.77</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>39.33</v>
+        <v>37.76</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-35.36</v>
+        <v>-28.99</v>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
     </row>
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>82.8</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-80.44</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
@@ -6930,13 +6930,13 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.65</v>
+        <v>1.34</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>86.92</v>
+        <v>83.34</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-86.27</v>
+        <v>-82</v>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-4.65</v>
+        <v>-5.07</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>43.96</v>
+        <v>40.85</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-48.62</v>
+        <v>-45.92</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
@@ -6968,21 +6968,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>10664</v>
+        <v>904</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>D Cubed</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-14.78</v>
+        <v>-12.13</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>70.41</v>
+        <v>53.52</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-85.19</v>
+        <v>-65.65000000000001</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
     </row>
@@ -6991,21 +6991,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>904</v>
+        <v>10664</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>D Cubed</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-15.91</v>
+        <v>-14.46</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>52.78</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-68.69</v>
+        <v>-82.47</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
     </row>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>138.22</v>
+        <v>139.04</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>138.22</v>
+        <v>139.04</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.3</v>
+        <v>25.58</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.3</v>
+        <v>79.39</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.62</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>143.64</v>
+        <v>142.96</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>143.64</v>
+        <v>142.96</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.5</v>
+        <v>30.01</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>86.45999999999999</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>26.68</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>151.93</v>
+        <v>151.26</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>151.93</v>
+        <v>151.26</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>31.13</v>
+        <v>30.65</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.85</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="5">
@@ -889,22 +889,22 @@
         <v>50.66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>94.66</v>
+        <v>93.98</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>94.66</v>
+        <v>93.98</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>13.11</v>
+        <v>12.86</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>58.71</v>
+        <v>58.83</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>22.83</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="7">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>131.85</v>
+        <v>132.67</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>131.85</v>
+        <v>132.67</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>1667</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.01</v>
+        <v>24.28</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>81.43000000000001</v>
+        <v>82.52</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>26.41</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>102.78</v>
+        <v>103.73</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>102.78</v>
+        <v>103.73</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.95</v>
+        <v>17.6</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>60.68</v>
+        <v>61.02</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.15</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="9">
@@ -1189,22 +1189,22 @@
         <v>50.91</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>94.34999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>94.34999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.97</v>
+        <v>10.72</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>57.49</v>
+        <v>57.61</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.89</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="12">
@@ -1249,22 +1249,22 @@
         <v>44.43</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>58.59</v>
+        <v>57.51</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>58.59</v>
+        <v>57.51</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>14.44</v>
+        <v>14.51</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>30.34</v>
+        <v>29.41</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>13.82</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="13">
@@ -1309,22 +1309,22 @@
         <v>29.21</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>56.29</v>
+        <v>55.36</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>56.29</v>
+        <v>55.36</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7.24</v>
+        <v>7.43</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>33.82</v>
+        <v>32.99</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>15.22</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="14">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>12.05</v>
+        <v>11.7</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>38.55</v>
+        <v>38.9</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>25.54</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="15">
@@ -1489,22 +1489,22 @@
         <v>28.04</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>60.23</v>
+        <v>59.31</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>60.23</v>
+        <v>59.31</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>10.4</v>
+        <v>10.59</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>33.36</v>
+        <v>32.52</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>16.47</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="17">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>43.42</v>
+        <v>44.36</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>43.42</v>
+        <v>44.36</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.97</v>
+        <v>6.61</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>25.18</v>
+        <v>25.53</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.27</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="19">
@@ -1669,22 +1669,22 @@
         <v>38.55</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>45.18</v>
+        <v>44.09</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>45.18</v>
+        <v>44.09</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6.98</v>
+        <v>7.06</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>26.54</v>
+        <v>25.61</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11.65</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="20">
@@ -1729,22 +1729,22 @@
         <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14.9</v>
+        <v>14.22</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>14.9</v>
+        <v>14.22</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.13</v>
+        <v>3.65</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>5.22</v>
+        <v>4.81</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>5.55</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="21">
@@ -1789,22 +1789,22 @@
         <v>27.75</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>51.91</v>
+        <v>50.99</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>51.91</v>
+        <v>50.99</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>21.63</v>
+        <v>21.83</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>12.48</v>
+        <v>11.65</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>17.79</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="22">
@@ -2209,22 +2209,22 @@
         <v>32.52</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>39.4</v>
+        <v>38.72</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>39.4</v>
+        <v>38.72</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>10.04</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>20.5</v>
+        <v>20.61</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="29">
@@ -2269,22 +2269,22 @@
         <v>23.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>20.09</v>
+        <v>20.91</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>20.09</v>
+        <v>20.91</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.46</v>
+        <v>5.73</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>7</v>
+        <v>8.09</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.63</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="30">
@@ -2509,22 +2509,22 @@
         <v>39.97</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>19.04</v>
+        <v>17.96</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>19.04</v>
+        <v>17.96</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>7.98</v>
+        <v>7.05</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>6.82</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="34">
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>151.93</v>
+        <v>151.26</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.93</v>
+        <v>151.26</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.13</v>
+        <v>30.65</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>36.85</v>
+        <v>37.07</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>143.64</v>
+        <v>142.96</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>143.64</v>
+        <v>142.96</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.5</v>
+        <v>30.01</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>86.45999999999999</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>26.68</v>
+        <v>26.9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="4">
@@ -3094,22 +3094,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>138.22</v>
+        <v>139.04</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>138.22</v>
+        <v>139.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.3</v>
+        <v>25.58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.3</v>
+        <v>79.39</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.62</v>
+        <v>34.07</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1673</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="5">
@@ -3156,19 +3156,19 @@
         <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>131.85</v>
+        <v>132.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>131.85</v>
+        <v>132.67</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.01</v>
+        <v>24.28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>81.43000000000001</v>
+        <v>82.52</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26.41</v>
+        <v>25.86</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1667</v>
@@ -3218,22 +3218,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>102.78</v>
+        <v>103.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>102.78</v>
+        <v>103.73</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.95</v>
+        <v>17.6</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>60.68</v>
+        <v>61.02</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.15</v>
+        <v>25.11</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="9">
@@ -3249,22 +3249,22 @@
         <v>50.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>94.66</v>
+        <v>93.98</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>94.66</v>
+        <v>93.98</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>13.11</v>
+        <v>12.86</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>58.71</v>
+        <v>58.83</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>22.83</v>
+        <v>22.29</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="10">
@@ -3280,22 +3280,22 @@
         <v>50.91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.97</v>
+        <v>10.72</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>57.49</v>
+        <v>57.61</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.89</v>
+        <v>25.34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1606</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="11">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.05</v>
+        <v>11.7</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.55</v>
+        <v>38.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>25.54</v>
+        <v>26.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="13">
@@ -3404,22 +3404,22 @@
         <v>28.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>60.23</v>
+        <v>59.31</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60.23</v>
+        <v>59.31</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.4</v>
+        <v>10.59</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>33.36</v>
+        <v>32.52</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>16.47</v>
+        <v>16.19</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15">
@@ -3435,22 +3435,22 @@
         <v>44.43</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.59</v>
+        <v>57.51</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.59</v>
+        <v>57.51</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>14.44</v>
+        <v>14.51</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>30.34</v>
+        <v>29.41</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.82</v>
+        <v>13.59</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16">
@@ -3466,22 +3466,22 @@
         <v>29.21</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>56.29</v>
+        <v>55.36</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>56.29</v>
+        <v>55.36</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.24</v>
+        <v>7.43</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>33.82</v>
+        <v>32.99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.22</v>
+        <v>14.94</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="17">
@@ -3497,84 +3497,84 @@
         <v>27.75</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>51.91</v>
+        <v>50.99</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>51.91</v>
+        <v>50.99</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>21.63</v>
+        <v>21.83</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12.48</v>
+        <v>11.65</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.79</v>
+        <v>17.52</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5980</v>
+        <v>8767</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>East Grand Rapids Robotics</t>
+          <t>Dark Horse Robotics</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>38.55</v>
+        <v>27.21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45.18</v>
+        <v>44.36</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45.18</v>
+        <v>44.36</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.98</v>
+        <v>6.61</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>26.54</v>
+        <v>25.53</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.65</v>
+        <v>12.23</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>8767</v>
+        <v>5980</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Dark Horse Robotics</t>
+          <t>East Grand Rapids Robotics</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>27.21</v>
+        <v>38.55</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>43.42</v>
+        <v>44.09</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>43.42</v>
+        <v>44.09</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.97</v>
+        <v>7.06</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>25.18</v>
+        <v>25.61</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="20">
@@ -3590,22 +3590,22 @@
         <v>32.52</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>39.4</v>
+        <v>38.72</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.4</v>
+        <v>38.72</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10.04</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.5</v>
+        <v>20.61</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="21">
@@ -3993,22 +3993,22 @@
         <v>23.43</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.09</v>
+        <v>20.91</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20.09</v>
+        <v>20.91</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>5.46</v>
+        <v>5.73</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>7</v>
+        <v>8.09</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.63</v>
+        <v>7.08</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="34">
@@ -4075,64 +4075,64 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9566</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>39.97</v>
+        <v>25.23</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>19.04</v>
+        <v>18.28</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>19.04</v>
+        <v>18.28</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.24</v>
+        <v>5.52</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.98</v>
+        <v>9.99</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6.82</v>
+        <v>2.78</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>9566</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.23</v>
+        <v>39.97</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18.28</v>
+        <v>17.96</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>18.28</v>
+        <v>17.96</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.52</v>
+        <v>4.31</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>9.99</v>
+        <v>7.05</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.78</v>
+        <v>6.59</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="38">
@@ -4179,22 +4179,22 @@
         <v>25.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>14.9</v>
+        <v>14.22</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>14.9</v>
+        <v>14.22</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.13</v>
+        <v>3.65</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>5.22</v>
+        <v>4.81</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>5.55</v>
+        <v>5.77</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="40">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -649,22 +649,22 @@
         <v>75.04000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>137.64</v>
+        <v>134.99</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>137.64</v>
+        <v>134.99</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25.54</v>
+        <v>25.39</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>78.03</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.07</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>145.74</v>
+        <v>142.14</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>145.74</v>
+        <v>142.14</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1683</v>
+        <v>1677</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.72</v>
+        <v>30.51</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>87.59</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>27.43</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>154.04</v>
+        <v>150.44</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>154.04</v>
+        <v>150.44</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>31.35</v>
+        <v>31.14</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>85.09</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>37.59</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="5">
@@ -949,22 +949,22 @@
         <v>68.08</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>131.27</v>
+        <v>128.61</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>131.27</v>
+        <v>128.61</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>24.25</v>
+        <v>24.1</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>81.16</v>
+        <v>79.12</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.86</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="8">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>99.62</v>
+        <v>98.87</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>99.62</v>
+        <v>98.87</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.38</v>
+        <v>17.54</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>57.69</v>
+        <v>55.84</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>24.55</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>72.98</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>72.98</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.48</v>
+        <v>11.64</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>35.56</v>
+        <v>33.72</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>25.93</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40.25</v>
+        <v>39.51</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>40.25</v>
+        <v>39.51</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>22.19</v>
+        <v>20.35</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>11.66</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="19">
@@ -1729,22 +1729,22 @@
         <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>17</v>
+        <v>13.41</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>17</v>
+        <v>13.41</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1420</v>
+        <v>1404</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>6.35</v>
+        <v>4.44</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>6.29</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="21">
@@ -2269,22 +2269,22 @@
         <v>23.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>19.51</v>
+        <v>16.85</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.51</v>
+        <v>16.85</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>6.74</v>
+        <v>4.69</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.07</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="30">
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>154.04</v>
+        <v>150.44</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>154.04</v>
+        <v>150.44</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.35</v>
+        <v>31.14</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>85.09</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>37.59</v>
+        <v>36.12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1697</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>145.74</v>
+        <v>142.14</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>145.74</v>
+        <v>142.14</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.72</v>
+        <v>30.51</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>87.59</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>27.43</v>
+        <v>25.95</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1683</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="4">
@@ -3094,84 +3094,84 @@
         <v>75.04000000000001</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>137.64</v>
+        <v>134.99</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>137.64</v>
+        <v>134.99</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.54</v>
+        <v>25.39</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>78.03</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>34.07</v>
+        <v>33.6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1673</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>1023</v>
+        <v>2075</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bedford Express</t>
+          <t>Enigma Robotics</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68.08</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>131.27</v>
+        <v>129.64</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>131.27</v>
+        <v>129.64</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>24.25</v>
+        <v>23.77</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.16</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25.86</v>
+        <v>31.12</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2075</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Enigma Robotics</t>
+          <t>Bedford Express</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>88.79000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>129.64</v>
+        <v>128.61</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>129.64</v>
+        <v>128.61</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>23.77</v>
+        <v>24.1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>74.73999999999999</v>
+        <v>79.12</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31.12</v>
+        <v>25.39</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7">
@@ -3218,22 +3218,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>99.62</v>
+        <v>98.87</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>99.62</v>
+        <v>98.87</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.38</v>
+        <v>17.54</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.69</v>
+        <v>55.84</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24.55</v>
+        <v>25.49</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="9">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>72.98</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.98</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.48</v>
+        <v>11.64</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>35.56</v>
+        <v>33.72</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>25.93</v>
+        <v>26.88</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="13">
@@ -3559,22 +3559,22 @@
         <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40.25</v>
+        <v>39.51</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>40.25</v>
+        <v>39.51</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>22.19</v>
+        <v>20.35</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.66</v>
+        <v>12.61</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="20">
@@ -4013,30 +4013,30 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>10181</v>
+        <v>10664</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ProtoWarriors</t>
+          <t>Big Reds</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.43</v>
+        <v>21.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.51</v>
+        <v>19.12</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.51</v>
+        <v>19.12</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>5.7</v>
+        <v>4.84</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.74</v>
+        <v>11.44</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>7.07</v>
+        <v>2.83</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>1430</v>
@@ -4044,157 +4044,157 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>10664</v>
+        <v>9566</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Big Reds</t>
+          <t>Red Storm Rookies</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>21.7</v>
+        <v>39.97</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.12</v>
+        <v>18.67</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.84</v>
+        <v>4.77</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11.44</v>
+        <v>7.84</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.83</v>
+        <v>6.05</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>9566</v>
+        <v>7256</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Red Storm Rookies</t>
+          <t>Irish Robotics</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>39.97</v>
+        <v>25.23</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.67</v>
+        <v>18.28</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.67</v>
+        <v>18.28</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4.77</v>
+        <v>5.52</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7.84</v>
+        <v>9.99</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6.05</v>
+        <v>2.78</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7256</v>
+        <v>10181</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Irish Robotics</t>
+          <t>ProtoWarriors</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>25.23</v>
+        <v>23.43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>18.28</v>
+        <v>16.85</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>18.28</v>
+        <v>16.85</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>9.99</v>
+        <v>4.69</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.78</v>
+        <v>6.61</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1426</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Comstock Colts</t>
+          <t>Red Arrows</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.63</v>
+        <v>22.62</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17</v>
+        <v>16.41</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17</v>
+        <v>16.41</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4.36</v>
+        <v>4.06</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6.35</v>
+        <v>8.43</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6.29</v>
+        <v>3.91</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>3234</v>
+        <v>10642</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Red Arrows</t>
+          <t>Comstock Colts</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>22.62</v>
+        <v>25.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>16.41</v>
+        <v>13.41</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>16.41</v>
+        <v>13.41</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8.43</v>
+        <v>4.44</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.91</v>
+        <v>4.82</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1418</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="40">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -709,22 +709,22 @@
         <v>45.04</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>142.14</v>
+        <v>141.51</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>142.14</v>
+        <v>141.51</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.51</v>
+        <v>29.71</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>85.68000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>25.95</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="4">
@@ -769,22 +769,22 @@
         <v>45.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>150.44</v>
+        <v>149.8</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>150.44</v>
+        <v>149.8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>31.14</v>
+        <v>30.34</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>83.18000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.12</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="5">
@@ -1009,22 +1009,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>98.87</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>98.87</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>17.54</v>
+        <v>17.3</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>55.84</v>
+        <v>56.14</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>25.49</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1369,22 @@
         <v>55.1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>72.23999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>72.23999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>11.64</v>
+        <v>11.41</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>33.72</v>
+        <v>34.02</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.88</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="15">
@@ -1609,22 +1609,22 @@
         <v>27.21</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39.51</v>
+        <v>38.64</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>39.51</v>
+        <v>38.64</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6.55</v>
+        <v>6.32</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>20.35</v>
+        <v>20.65</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>12.61</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="19">
@@ -1729,22 +1729,22 @@
         <v>25.63</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13.41</v>
+        <v>12.77</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>13.41</v>
+        <v>12.77</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4.44</v>
+        <v>5.07</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>4.82</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="21">
@@ -3032,22 +3032,22 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>150.44</v>
+        <v>149.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>150.44</v>
+        <v>149.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.14</v>
+        <v>30.34</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>83.18000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>36.12</v>
+        <v>35.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="3">
@@ -3063,22 +3063,22 @@
         <v>45.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>142.14</v>
+        <v>141.51</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>142.14</v>
+        <v>141.51</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30.51</v>
+        <v>29.71</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>85.68000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>25.95</v>
+        <v>25.49</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="4">
@@ -3218,22 +3218,22 @@
         <v>71.68000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>98.87</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>98.87</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.54</v>
+        <v>17.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55.84</v>
+        <v>56.14</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25.49</v>
+        <v>24.56</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1613</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="9">
@@ -3342,22 +3342,22 @@
         <v>55.1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>72.23999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.23999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11.64</v>
+        <v>11.41</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>33.72</v>
+        <v>34.02</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26.88</v>
+        <v>25.94</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="13">
@@ -3559,22 +3559,22 @@
         <v>27.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>39.51</v>
+        <v>38.64</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.51</v>
+        <v>38.64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.55</v>
+        <v>6.32</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.35</v>
+        <v>20.65</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.61</v>
+        <v>11.67</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="20">
@@ -4179,22 +4179,22 @@
         <v>25.63</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.41</v>
+        <v>12.77</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.41</v>
+        <v>12.77</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.44</v>
+        <v>5.07</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.82</v>
+        <v>4.36</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="40">

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -655,7 +655,7 @@
         <v>134.99</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>25.39</v>
@@ -715,7 +715,7 @@
         <v>141.51</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>29.71</v>
@@ -775,7 +775,7 @@
         <v>149.8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>30.34</v>
@@ -835,7 +835,7 @@
         <v>129.64</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>23.77</v>
@@ -895,7 +895,7 @@
         <v>92.53</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>12.94</v>
@@ -955,7 +955,7 @@
         <v>128.61</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>24.1</v>
@@ -1015,7 +1015,7 @@
         <v>98.01000000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>17.3</v>
@@ -1075,7 +1075,7 @@
         <v>110.94</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>23.97</v>
@@ -1135,7 +1135,7 @@
         <v>76.73</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.82</v>
@@ -1195,7 +1195,7 @@
         <v>92.23</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>10.79</v>
@@ -1255,7 +1255,7 @@
         <v>58.22</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>14.97</v>
@@ -1315,7 +1315,7 @@
         <v>54.22</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>7.1</v>
@@ -1435,7 +1435,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>17.28</v>
@@ -1495,7 +1495,7 @@
         <v>58.16</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>10.26</v>
@@ -1555,7 +1555,7 @@
         <v>24.14</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>4.42</v>
@@ -1615,7 +1615,7 @@
         <v>38.64</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>6.32</v>
@@ -1795,7 +1795,7 @@
         <v>49.84</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>21.5</v>
@@ -1855,7 +1855,7 @@
         <v>21.96</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>4.08</v>
@@ -1915,7 +1915,7 @@
         <v>29.12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.43</v>
@@ -2035,7 +2035,7 @@
         <v>18.28</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>5.52</v>
@@ -2095,7 +2095,7 @@
         <v>28.23</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>5.23</v>
@@ -2155,7 +2155,7 @@
         <v>16.41</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>4.06</v>
@@ -2215,7 +2215,7 @@
         <v>37.27</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>9.869999999999999</v>
@@ -2275,7 +2275,7 @@
         <v>16.85</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>5.55</v>
@@ -2335,7 +2335,7 @@
         <v>24.92</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>4.78</v>
@@ -2575,7 +2575,7 @@
         <v>21.36</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>0.92</v>
@@ -2695,7 +2695,7 @@
         <v>19.56</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="P36" s="2" t="n">
         <v>6.92</v>
@@ -2755,7 +2755,7 @@
         <v>19.12</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>4.84</v>
@@ -2815,7 +2815,7 @@
         <v>21.13</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>2.83</v>
@@ -2875,7 +2875,7 @@
         <v>-0.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>6.18</v>
@@ -2935,7 +2935,7 @@
         <v>32.76</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>3.1</v>
@@ -3047,7 +3047,7 @@
         <v>35.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="3">
@@ -3078,7 +3078,7 @@
         <v>25.49</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="4">
@@ -3109,7 +3109,7 @@
         <v>33.6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5">
@@ -3140,7 +3140,7 @@
         <v>31.12</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="6">
@@ -3171,7 +3171,7 @@
         <v>25.39</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="7">
@@ -3202,7 +3202,7 @@
         <v>27.66</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="8">
@@ -3233,7 +3233,7 @@
         <v>24.56</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="9">
@@ -3264,7 +3264,7 @@
         <v>22.24</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="10">
@@ -3295,7 +3295,7 @@
         <v>25.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="11">
@@ -3326,7 +3326,7 @@
         <v>19.72</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="12">
@@ -3388,7 +3388,7 @@
         <v>18.53</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="14">
@@ -3419,7 +3419,7 @@
         <v>13.05</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="15">
@@ -3450,7 +3450,7 @@
         <v>16.11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>14.86</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="17">
@@ -3512,7 +3512,7 @@
         <v>17.44</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="18">
@@ -3574,7 +3574,7 @@
         <v>11.67</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="20">
@@ -3605,7 +3605,7 @@
         <v>8.26</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="21">
@@ -3636,7 +3636,7 @@
         <v>12.39</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="22">
@@ -3667,7 +3667,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="23">
@@ -3698,7 +3698,7 @@
         <v>10.04</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="24">
@@ -3822,7 +3822,7 @@
         <v>7.58</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="28">
@@ -3853,7 +3853,7 @@
         <v>5.29</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="29">
@@ -3884,7 +3884,7 @@
         <v>8.66</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="30">
@@ -3946,7 +3946,7 @@
         <v>9.19</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="32">
@@ -3977,7 +3977,7 @@
         <v>5.9</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33">
@@ -4008,7 +4008,7 @@
         <v>7.99</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="34">
@@ -4039,7 +4039,7 @@
         <v>2.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="35">
@@ -4101,7 +4101,7 @@
         <v>2.78</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="37">
@@ -4132,7 +4132,7 @@
         <v>6.61</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="38">
@@ -4163,7 +4163,7 @@
         <v>3.91</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="39">
@@ -4225,7 +4225,7 @@
         <v>-0.87</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
   </sheetData>

--- a/2026miken_scouting.xlsx
+++ b/2026miken_scouting.xlsx
@@ -1075,7 +1075,7 @@
         <v>110.94</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>23.97</v>
@@ -1375,7 +1375,7 @@
         <v>71.37</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>11.41</v>
@@ -3202,7 +3202,7 @@
         <v>27.66</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="8">
@@ -3357,7 +3357,7 @@
         <v>25.94</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="13">
